--- a/review/State-Not-Situation-French-review.xlsx
+++ b/review/State-Not-Situation-French-review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="French review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'French review'!$A$1:$F$279</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'French review'!$A$1:$F$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2112,7 +2112,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>“YOU KNOW THE DAY” — PAGES 12 TO 13</t>
+          <t>“YOU KNOW THE DAY” — PAGE 12, ABOVE THE THREE INSTRUCTIONS</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
@@ -2124,7 +2124,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -2145,137 +2145,137 @@
       <c r="E62" s="11" t="n"/>
       <c r="F62" s="11" t="n"/>
     </row>
-    <row r="63" ht="150" customHeight="1">
+    <row r="63" ht="30" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[0]</t>
+          <t>knowTheDay.moreLabel</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>The day I mean is the other kind. The day where nothing went wrong and everything felt off. It started before you noticed it starting. Somewhere between the alarm and the shower, between the shower and the kitchen, between the kitchen and the first sip of whatever you drink to become the person the morning requires. Something was already there. It felt more like texture. A drag in the limbs, a reluctance in the chest, a faint heaviness that sat behind your thoughts like rainy weather behind glass.</t>
+          <t>More from page 12</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>La journée dont je parle, c’est l’autre. La journée où rien ne s’est mal passé et où tout clochait. Elle a commencé avant que vous ne remarquiez qu’elle commençait. Quelque part entre le réveil et la douche, entre la douche et la cuisine, entre la cuisine et la première gorgée de ce que vous buvez pour devenir la personne que le matin exige. Quelque chose était déjà là. On aurait plutôt dit une texture. Une pesanteur dans les membres, une réticence dans la poitrine, une légère lourdeur posée derrière vos pensées comme un jour de pluie derrière une vitre.</t>
+          <t>Un autre passage de la page 12</t>
         </is>
       </c>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
     </row>
-    <row r="64" ht="60" customHeight="1">
+    <row r="64" ht="150" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[1]</t>
+          <t>knowTheDay.runs[0]</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>You have had this day. Everyone has had this day. You have had it dozens of times and you will have it again and each time the story will feel like the truth and each time the morning after will make the story dissolve.</t>
+          <t>The day I mean is the other kind. The day where nothing went wrong and everything felt off. It started before you noticed it starting. Somewhere between the alarm and the shower, between the shower and the kitchen, between the kitchen and the first sip of whatever you drink to become the person the morning requires. Something was already there. It felt more like texture. A drag in the limbs, a reluctance in the chest, a faint heaviness that sat behind your thoughts like rainy weather behind glass.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Vous avez eu cette journée. Tout le monde a eu cette journée. Vous l’avez eue des dizaines de fois et vous l’aurez encore et chaque fois l’histoire aura l’air vraie et chaque fois le lendemain matin dissoudra l’histoire.</t>
+          <t>La journée dont je parle, c’est l’autre. La journée où rien ne s’est mal passé et où tout clochait. Elle a commencé avant que vous ne remarquiez qu’elle commençait. Quelque part entre le réveil et la douche, entre la douche et la cuisine, entre la cuisine et la première gorgée de ce que vous buvez pour devenir la personne que le matin exige. Quelque chose était déjà là. On aurait plutôt dit une texture. Une pesanteur dans les membres, une réticence dans la poitrine, une légère lourdeur posée derrière vos pensées comme un jour de pluie derrière une vitre.</t>
         </is>
       </c>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="11" t="n"/>
     </row>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[2]</t>
+          <t>knowTheDay.runs[1]</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>The body spoke first. The mind explained second, and this explanation felt like the event.</t>
+          <t>You have had this day. Everyone has had this day. You have had it dozens of times and you will have it again and each time the story will feel like the truth and each time the morning after will make the story dissolve.</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Le corps a parlé d’abord. L’esprit a expliqué ensuite, et cette explication est passée pour l’événement.</t>
+          <t>Vous avez eu cette journée. Tout le monde a eu cette journée. Vous l’avez eue des dizaines de fois et vous l’aurez encore et chaque fois l’histoire aura l’air vraie et chaque fois le lendemain matin dissoudra l’histoire.</t>
         </is>
       </c>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
     </row>
-    <row r="66" ht="105" customHeight="1">
+    <row r="66" ht="30" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[3]</t>
+          <t>knowTheDay.runs[2]</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>This book is about that mistake. It is about that error as a daily, ambient, invisible feature of being alive in a body that is constantly producing signals, which your mind is constantly reading or misreading. Before any of that, before the science and the mechanism and the reason the instrument was miscalibrated yesterday, try something right now.</t>
+          <t>The body spoke first. The mind explained second, and this explanation felt like the event.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Ce livre parle de cette méprise. Il parle de cette erreur comme d’un aspect quotidien, ambiant, invisible de la vie dans un corps qui produit sans cesse des signaux, que votre esprit, sans cesse, lit ou lit de travers. Avant tout cela, avant la science et le mécanisme et la raison pour laquelle l’instrument était mal calibré hier, essayez quelque chose tout de suite.</t>
+          <t>Le corps a parlé d’abord. L’esprit a expliqué ensuite, et cette explication est passée pour l’événement.</t>
         </is>
       </c>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
     </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
+    <row r="67" ht="105" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>“You know the day” — page 12, above the three instructions</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>knowTheDay.runs[3]</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>This book is about that mistake. It is about that error as a daily, ambient, invisible feature of being alive in a body that is constantly producing signals, which your mind is constantly reading or misreading. Before any of that, before the science and the mechanism and the reason the instrument was miscalibrated yesterday, try something right now.</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Ce livre parle de cette méprise. Il parle de cette erreur comme d’un aspect quotidien, ambiant, invisible de la vie dans un corps qui produit sans cesse des signaux, que votre esprit, sans cesse, lit ou lit de travers. Avant tout cela, avant la science et le mécanisme et la raison pour laquelle l’instrument était mal calibré hier, essayez quelque chose tout de suite.</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
         </is>
       </c>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
-      <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>reading.eyebrow</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Try something right now</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Essayez quelque chose tout de suite</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="n"/>
-      <c r="F68" s="11" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
@@ -2285,17 +2285,17 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>reading.lead</t>
+          <t>reading.eyebrow</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Whatever you are feeling as you read this sentence.</t>
+          <t>Try something right now</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Quoi que vous ressentiez en lisant cette phrase.</t>
+          <t>Essayez quelque chose tout de suite</t>
         </is>
       </c>
       <c r="E69" s="11" t="n"/>
@@ -2309,17 +2309,17 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[0]</t>
+          <t>reading.lead</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Check your jaw.</t>
+          <t>Whatever you are feeling as you read this sentence.</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Observez votre mâchoire.</t>
+          <t>Quoi que vous ressentiez en lisant cette phrase.</t>
         </is>
       </c>
       <c r="E70" s="11" t="n"/>
@@ -2333,17 +2333,17 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[1]</t>
+          <t>reading.steps[0]</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Check your breath.</t>
+          <t>Check your jaw.</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Observez votre respiration.</t>
+          <t>Observez votre mâchoire.</t>
         </is>
       </c>
       <c r="E71" s="11" t="n"/>
@@ -2357,17 +2357,17 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[2]</t>
+          <t>reading.steps[1]</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Check your shoulders.</t>
+          <t>Check your breath.</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Observez vos épaules.</t>
+          <t>Observez votre respiration.</t>
         </is>
       </c>
       <c r="E72" s="11" t="n"/>
@@ -2381,23 +2381,23 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>reading.result</t>
+          <t>reading.steps[2]</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>What you found is a reading.</t>
+          <t>Check your shoulders.</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Ce que vous avez trouvé, c’est une lecture.</t>
+          <t>Observez vos épaules.</t>
         </is>
       </c>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
     </row>
-    <row r="74" ht="60" customHeight="1">
+    <row r="74" ht="30" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
           <t>“Try something right now” — the three instructions, page 13</t>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>reading.afterResult</t>
+          <t>reading.result</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
+          <t>What you found is a reading.</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Une lecture de l’instrument qui interprète tout ce qui vous entoure, en ce moment, y compris ces mots. La lecture est peut-être exacte. Peut-être pas. Vous ne pouvez pas le savoir tant que vous n’avez pas vu les réglages.</t>
+          <t>Ce que vous avez trouvé, c’est une lecture.</t>
         </is>
       </c>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
     </row>
-    <row r="75" ht="30" customHeight="1">
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
           <t>“Try something right now” — the three instructions, page 13</t>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>reading.question</t>
+          <t>reading.afterResult</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this the state?</t>
+          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>Est-ce la situation ? Ou est-ce l’état ?</t>
+          <t>Une lecture de l’instrument qui interprète tout ce qui vous entoure, en ce moment, y compris ces mots. La lecture est peut-être exacte. Peut-être pas. Vous ne pouvez pas le savoir tant que vous n’avez pas vu les réglages.</t>
         </is>
       </c>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="11" t="n"/>
     </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>“Try something right now” — the three instructions, page 13</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>reading.question</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Is this the situation? Or is this the state?</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Est-ce la situation ? Ou est-ce l’état ?</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="n"/>
+      <c r="F76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>THE BOOK — THE PAGE 20 HEADING, THE AUTHOR’S ACCOUNT, WHO IT IS FOR</t>
         </is>
       </c>
-      <c r="B76" s="8" t="n"/>
-      <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
-      <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>book.eyebrow</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>The book</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Le livre</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="n"/>
-      <c r="F77" s="11" t="n"/>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>book.heading</t>
+          <t>book.eyebrow</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Same morning. Same paragraph. Same Katrin. Different instrument settings.</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Même matin. Même paragraphe. Même Katrin. Instruments réglés autrement.</t>
+          <t>Le livre</t>
         </is>
       </c>
       <c r="E78" s="11" t="n"/>
@@ -2513,23 +2513,23 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>book.headingSource</t>
+          <t>book.heading</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>Same morning. Same paragraph. Same Katrin. Different instrument settings.</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>Même matin. Même paragraphe. Même Katrin. Instruments réglés autrement.</t>
         </is>
       </c>
       <c r="E79" s="11" t="n"/>
       <c r="F79" s="11" t="n"/>
     </row>
-    <row r="80" ht="135" customHeight="1">
+    <row r="80" ht="30" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
           <t>The book — the page 20 heading, the author’s account, who it is for</t>
@@ -2537,23 +2537,23 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>book.paragraphs[0]</t>
+          <t>book.headingSource</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Pendant seize jours, Katrin traverse des situations ordinaires où sa première lecture de ce qui se passe n’est pas toujours celle qui tient, à y regarder de plus près. Chaque chapitre suit l’un de ces moments jusque dans la psychologie qui le sous-tend, de l’attention et de la prédiction à la mémoire, à la menace, à l’incertitude et à l’inférence sociale. Le livre ne promet pas un meilleur instinct. Il demande ce qui devient possible quand nous apprenons d’où venait notre première lecture.</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="E80" s="11" t="n"/>
       <c r="F80" s="11" t="n"/>
     </row>
-    <row r="81" ht="45" customHeight="1">
+    <row r="81" ht="135" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
           <t>The book — the page 20 heading, the author’s account, who it is for</t>
@@ -2561,23 +2561,23 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>book.paragraphs[1]</t>
+          <t>book.paragraphs[0]</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
+          <t>Pendant seize jours, Katrin traverse des situations ordinaires où sa première lecture de ce qui se passe n’est pas toujours celle qui tient, à y regarder de plus près. Chaque chapitre suit l’un de ces moments jusque dans la psychologie qui le sous-tend, de l’attention et de la prédiction à la mémoire, à la menace, à l’incertitude et à l’inférence sociale. Le livre ne promet pas un meilleur instinct. Il demande ce qui devient possible quand nous apprenons d’où venait notre première lecture.</t>
         </is>
       </c>
       <c r="E81" s="11" t="n"/>
       <c r="F81" s="11" t="n"/>
     </row>
-    <row r="82" ht="30" customHeight="1">
+    <row r="82" ht="45" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
           <t>The book — the page 20 heading, the author’s account, who it is for</t>
@@ -2585,23 +2585,23 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>book.readersEyebrow</t>
+          <t>book.paragraphs[1]</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Who it is for</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>À qui il s’adresse</t>
+          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
         </is>
       </c>
       <c r="E82" s="11" t="n"/>
       <c r="F82" s="11" t="n"/>
     </row>
-    <row r="83" ht="75" customHeight="1">
+    <row r="83" ht="30" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
           <t>The book — the page 20 heading, the author’s account, who it is for</t>
@@ -2609,17 +2609,17 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>book.readersAnchor</t>
+          <t>book.readersEyebrow</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>This book does not replace professional support and it does not treat complex conditions as lifestyle problems. It works in the gap between fine and clinical, the space where most people live on most days.</t>
+          <t>Who it is for</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Ce livre ne remplace pas l’aide d’un professionnel et il ne traite pas les troubles complexes comme des problèmes d’hygiène de vie. Il travaille dans l’écart entre « ça va » et « clinique », l’espace où la plupart des gens vivent la plupart des jours.</t>
+          <t>À qui il s’adresse</t>
         </is>
       </c>
       <c r="E83" s="11" t="n"/>
@@ -2633,57 +2633,57 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>book.readers</t>
+          <t>book.readersAnchor</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+          <t>This book does not replace professional support and it does not treat complex conditions as lifestyle problems. It works in the gap between fine and clinical, the space where most people live on most days.</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Pour quiconque a déjà été certain du sens d’une situation, puis a découvert qu’il se passait autre chose. Et pour les lecteurs qui s’intéressent à la psychologie de notre façon de remarquer, d’interpréter et de revoir le monde qui nous entoure.</t>
+          <t>Ce livre ne remplace pas l’aide d’un professionnel et il ne traite pas les troubles complexes comme des problèmes d’hygiène de vie. Il travaille dans l’écart entre « ça va » et « clinique », l’espace où la plupart des gens vivent la plupart des jours.</t>
         </is>
       </c>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
     </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
+    <row r="85" ht="75" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>book.readers</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Pour quiconque a déjà été certain du sens d’une situation, puis a découvert qu’il se passait autre chose. Et pour les lecteurs qui s’intéressent à la psychologie de notre façon de remarquer, d’interpréter et de revoir le monde qui nous entoure.</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n"/>
+      <c r="F85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
         </is>
       </c>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
-    </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>excerpt.eyebrow</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t>Lire</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="n"/>
-      <c r="F86" s="11" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="8" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>excerpt.title</t>
+          <t>excerpt.eyebrow</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Before the chapters</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Avant les chapitres</t>
+          <t>Lire</t>
         </is>
       </c>
       <c r="E87" s="11" t="n"/>
@@ -2717,17 +2717,17 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>excerpt.sectionLabel</t>
+          <t>excerpt.title</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>The pilot</t>
+          <t>Before the chapters</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Le pilote</t>
+          <t>Avant les chapitres</t>
         </is>
       </c>
       <c r="E88" s="11" t="n"/>
@@ -2741,17 +2741,17 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>excerpt.runningHead</t>
+          <t>excerpt.sectionLabel</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>The pilot</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>Le pilote</t>
         </is>
       </c>
       <c r="E89" s="11" t="n"/>
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>excerpt.cta</t>
+          <t>excerpt.runningHead</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Lire un extrait</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="E90" s="11" t="n"/>
@@ -2789,17 +2789,17 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>excerpt.continueCta</t>
+          <t>excerpt.cta</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Continue reading</t>
+          <t>Read an extract</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Lire la suite</t>
+          <t>Lire un extrait</t>
         </is>
       </c>
       <c r="E91" s="11" t="n"/>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>excerpt.back</t>
+          <t>excerpt.continueCta</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Continue reading</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Retour au livre</t>
+          <t>Lire la suite</t>
         </is>
       </c>
       <c r="E92" s="11" t="n"/>
@@ -2837,23 +2837,23 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>excerpt.readingModeLabel</t>
+          <t>excerpt.back</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Reading mode</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Mode lecture</t>
+          <t>Retour au livre</t>
         </is>
       </c>
       <c r="E93" s="11" t="n"/>
       <c r="F93" s="11" t="n"/>
     </row>
-    <row r="94" ht="105" customHeight="1">
+    <row r="94" ht="30" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2861,23 +2861,23 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[0]</t>
+          <t>excerpt.readingModeLabel</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
+          <t>Reading mode</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Le soir du 16 juillet 1999, un petit avion monomoteur décolla du New Jersey. Il faisait route vers Martha’s Vineyard. Le pilote avait assez d’expérience pour être sûr de lui, et assez peu pour se tromper sur ce que valait cette assurance. Il avait environ 300 heures de vol. Il n’avait pas terminé la formation qui l’aurait qualifié pour voler aux seuls instruments.</t>
+          <t>Mode lecture</t>
         </is>
       </c>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
     </row>
-    <row r="95" ht="225" customHeight="1">
+    <row r="95" ht="105" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2885,23 +2885,23 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[1]</t>
+          <t>excerpt.paragraphs[0]</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
+          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Le ciel était dégagé au départ, alors il en conclut qu’il n’avait pas besoin d’instruments. Le temps qu’il atteigne la côte, il ne l’était plus. Une brume s’était posée sur l’eau. Le genre de brume qui efface la limite entre la mer et le ciel si progressivement que vous ne remarquez pas que l’horizon a disparu, jusqu’au moment où vous le cherchez et où il n’est plus là. Au-dessus des terres, cela n’a pas d’importance. Il y a des lumières en dessous. Vous voyez des routes, des bâtiments, une géométrie qui dit à vos yeux où est le bas. Au large, la nuit, avec la brume posée sur la surface comme une seconde obscurité, il n’y a rien. Hors du cockpit, le monde devient un gris uniforme dans toutes les directions. Le haut ressemble au bas. Un léger virage donne la sensation d’un vol en palier. Une descente lente donne la sensation de tenir l’altitude.</t>
+          <t>Le soir du 16 juillet 1999, un petit avion monomoteur décolla du New Jersey. Il faisait route vers Martha’s Vineyard. Le pilote avait assez d’expérience pour être sûr de lui, et assez peu pour se tromper sur ce que valait cette assurance. Il avait environ 300 heures de vol. Il n’avait pas terminé la formation qui l’aurait qualifié pour voler aux seuls instruments.</t>
         </is>
       </c>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
     </row>
-    <row r="96" ht="150" customHeight="1">
+    <row r="96" ht="225" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2909,17 +2909,17 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[2]</t>
+          <t>excerpt.paragraphs[1]</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>L’oreille interne du pilote, l’organe qui dit au cerveau dans quel sens le corps est orienté dans l’espace, fonctionne en détectant les changements de mouvement. Quand vous entrez en virage, le liquide à l’intérieur de l’oreille se déplace, et le cerveau enregistre une rotation. Mais si le virage se maintient pendant quinze ou vingt secondes, le liquide de l’oreille interne se stabilise. Il ne bouge plus. Le cerveau, qui suit le mouvement et non la position, en conclut que le virage est terminé. Vous vous sentez en palier, mais vous ne l’êtes pas.</t>
+          <t>Le ciel était dégagé au départ, alors il en conclut qu’il n’avait pas besoin d’instruments. Le temps qu’il atteigne la côte, il ne l’était plus. Une brume s’était posée sur l’eau. Le genre de brume qui efface la limite entre la mer et le ciel si progressivement que vous ne remarquez pas que l’horizon a disparu, jusqu’au moment où vous le cherchez et où il n’est plus là. Au-dessus des terres, cela n’a pas d’importance. Il y a des lumières en dessous. Vous voyez des routes, des bâtiments, une géométrie qui dit à vos yeux où est le bas. Au large, la nuit, avec la brume posée sur la surface comme une seconde obscurité, il n’y a rien. Hors du cockpit, le monde devient un gris uniforme dans toutes les directions. Le haut ressemble au bas. Un léger virage donne la sensation d’un vol en palier. Une descente lente donne la sensation de tenir l’altitude.</t>
         </is>
       </c>
       <c r="E96" s="11" t="n"/>
@@ -2933,23 +2933,23 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[3]</t>
+          <t>excerpt.paragraphs[2]</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
+          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Quelque part au-dessus de l’eau sombre, l’avion s’engagea dans un léger virage à gauche. Les instruments du pilote, les cadrans du tableau de bord devant lui, indiquaient le virage. L’horizon artificiel, un petit cadran gyroscopique qui montre l’angle de l’appareil par rapport au sol, lui disait qu’il s’inclinait. L’altimètre lui disait qu’il descendait. L’indicateur de vitesse lui disait qu’il accélérait. Son corps lui disait autre chose. Son corps lui disait qu’il volait droit et en palier. Son corps sonnait juste. Ses instruments sonnaient faux. Il fit confiance à son corps.</t>
+          <t>L’oreille interne du pilote, l’organe qui dit au cerveau dans quel sens le corps est orienté dans l’espace, fonctionne en détectant les changements de mouvement. Quand vous entrez en virage, le liquide à l’intérieur de l’oreille se déplace, et le cerveau enregistre une rotation. Mais si le virage se maintient pendant quinze ou vingt secondes, le liquide de l’oreille interne se stabilise. Il ne bouge plus. Le cerveau, qui suit le mouvement et non la position, en conclut que le virage est terminé. Vous vous sentez en palier, mais vous ne l’êtes pas.</t>
         </is>
       </c>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
     </row>
-    <row r="98" ht="120" customHeight="1">
+    <row r="98" ht="150" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2957,23 +2957,23 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[4]</t>
+          <t>excerpt.paragraphs[3]</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
+          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Le virage se resserra. Le nez tomba. La vitesse augmenta. Dans les dernières secondes, l’avion descendait à plus de 4 700 pieds par minute, près d’un kilomètre et demi toutes les soixante secondes, dans une spirale de plus en plus serrée que les pilotes appellent, avec la précision sinistre d’un métier qui a donné un nom aux façons dont il perd les siens, une spirale de la mort. Il percuta l’eau à pleine vitesse. Lui et ses deux passagers furent tués sur le coup.</t>
+          <t>Quelque part au-dessus de l’eau sombre, l’avion s’engagea dans un léger virage à gauche. Les instruments du pilote, les cadrans du tableau de bord devant lui, indiquaient le virage. L’horizon artificiel, un petit cadran gyroscopique qui montre l’angle de l’appareil par rapport au sol, lui disait qu’il s’inclinait. L’altimètre lui disait qu’il descendait. L’indicateur de vitesse lui disait qu’il accélérait. Son corps lui disait autre chose. Son corps lui disait qu’il volait droit et en palier. Son corps sonnait juste. Ses instruments sonnaient faux. Il fit confiance à son corps.</t>
         </is>
       </c>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
     </row>
-    <row r="99" ht="135" customHeight="1">
+    <row r="99" ht="120" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2981,23 +2981,23 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[5]</t>
+          <t>excerpt.paragraphs[4]</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
+          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>L’enquête ne releva aucune défaillance mécanique. Le moteur tournait. Les instruments fonctionnaient. Les données étaient là, sur le tableau de bord, à quinze centimètres de ses yeux, depuis le début, mais il ne les lut pas. Il lut son corps à la place. La consigne que la Federal Aviation Administration américaine donne aux pilotes qui se retrouvent dans cette situation tient en une phrase. C’est une consigne à prendre au pied de la lettre, et elle s’applique à votre vie aussi directement qu’à un cockpit :</t>
+          <t>Le virage se resserra. Le nez tomba. La vitesse augmenta. Dans les dernières secondes, l’avion descendait à plus de 4 700 pieds par minute, près d’un kilomètre et demi toutes les soixante secondes, dans une spirale de plus en plus serrée que les pilotes appellent, avec la précision sinistre d’un métier qui a donné un nom aux façons dont il perd les siens, une spirale de la mort. Il percuta l’eau à pleine vitesse. Lui et ses deux passagers furent tués sur le coup.</t>
         </is>
       </c>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
     </row>
-    <row r="100" ht="60" customHeight="1">
+    <row r="100" ht="135" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3005,23 +3005,23 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[6]</t>
+          <t>excerpt.paragraphs[5]</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
+          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Le pilote s’appelait John F. Kennedy Jr. C’était le fils d’un président américain. On lui avait déconseillé de voler ce soir-là sans son instructeur. Il avait dit à son instructeur qu’il voulait le faire seul. Il avait trente-huit ans.</t>
+          <t>L’enquête ne releva aucune défaillance mécanique. Le moteur tournait. Les instruments fonctionnaient. Les données étaient là, sur le tableau de bord, à quinze centimètres de ses yeux, depuis le début, mais il ne les lut pas. Il lut son corps à la place. La consigne que la Federal Aviation Administration américaine donne aux pilotes qui se retrouvent dans cette situation tient en une phrase. C’est une consigne à prendre au pied de la lettre, et elle s’applique à votre vie aussi directement qu’à un cockpit :</t>
         </is>
       </c>
       <c r="E100" s="11" t="n"/>
       <c r="F100" s="11" t="n"/>
     </row>
-    <row r="101" ht="240" customHeight="1">
+    <row r="101" ht="60" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3029,23 +3029,23 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[7]</t>
+          <t>excerpt.paragraphs[6]</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
+          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Vous pilotez un corps qui produit des signaux, et votre esprit prend souvent ces signaux pour la vérité. Les signaux se trompent parfois autant que le système vestibulaire de l’oreille interne au-dessus de l’eau sombre. La fatigue qui se présente comme une question sur votre carrière. Le pic de caféine qui se présente comme de l’anxiété à propos d’un e-mail. Le manque de sucre dans le sang qui se présente comme la preuve que votre relation est en train de se défaire. Votre corps parle d’abord et votre esprit explique ensuite. L’explication, parce qu’elle arrive avec tout le poids de la conviction physique, la mâchoire serrée, le cœur qui bat vite, la chaleur derrière les oreilles, donne l’impression d’un savoir profond. Vous avez l’impression de lire la situation. Mais vous ne lisez que l’instrument qui lit la situation, et les réglages de l’instrument étaient faussés avant que la situation n’arrive. Ces instruments existent. Vous les avez. Le rythme cardiaque, la tension de la mâchoire, la profondeur de la respiration, la position des épaules, la vitesse de vos pensées. Ils produisent des données en ce moment même, pendant que vous lisez cette phrase. Mais le bulletin météo plein d’assurance que le corps établit sur le monde n’est qu’un brouillon.</t>
+          <t>Le pilote s’appelait John F. Kennedy Jr. C’était le fils d’un président américain. On lui avait déconseillé de voler ce soir-là sans son instructeur. Il avait dit à son instructeur qu’il voulait le faire seul. Il avait trente-huit ans.</t>
         </is>
       </c>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
     </row>
-    <row r="102" ht="30" customHeight="1">
+    <row r="102" ht="240" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3053,23 +3053,23 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>excerpt.quote</t>
+          <t>excerpt.paragraphs[7]</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
+          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>« ayez confiance en vos instruments et ne tenez aucun compte des signaux contradictoires que vous envoie votre corps. »</t>
+          <t>Vous pilotez un corps qui produit des signaux, et votre esprit prend souvent ces signaux pour la vérité. Les signaux se trompent parfois autant que le système vestibulaire de l’oreille interne au-dessus de l’eau sombre. La fatigue qui se présente comme une question sur votre carrière. Le pic de caféine qui se présente comme de l’anxiété à propos d’un e-mail. Le manque de sucre dans le sang qui se présente comme la preuve que votre relation est en train de se défaire. Votre corps parle d’abord et votre esprit explique ensuite. L’explication, parce qu’elle arrive avec tout le poids de la conviction physique, la mâchoire serrée, le cœur qui bat vite, la chaleur derrière les oreilles, donne l’impression d’un savoir profond. Vous avez l’impression de lire la situation. Mais vous ne lisez que l’instrument qui lit la situation, et les réglages de l’instrument étaient faussés avant que la situation n’arrive. Ces instruments existent. Vous les avez. Le rythme cardiaque, la tension de la mâchoire, la profondeur de la respiration, la position des épaules, la vitesse de vos pensées. Ils produisent des données en ce moment même, pendant que vous lisez cette phrase. Mais le bulletin météo plein d’assurance que le corps établit sur le monde n’est qu’un brouillon.</t>
         </is>
       </c>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
     </row>
-    <row r="103" ht="135" customHeight="1">
+    <row r="103" ht="30" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3077,23 +3077,23 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closing</t>
+          <t>excerpt.quote</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
+          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Ce livre parle de la même erreur à l’échelle de la cuisine. La version qui arrive tous les mardis. La version où votre corps écrit une histoire à propos d’un message, d’un silence, d’un regard, et où votre esprit retouche cette histoire sous la supervision de ce que votre corps ressent à ce moment-là. Personne ne meurt, mais des décisions se prennent. Des relations changent. Des jugements sur soi se forment. Et rien de tout cela n’avait à se passer ainsi, parce que les données étaient là depuis le début.</t>
+          <t>« ayez confiance en vos instruments et ne tenez aucun compte des signaux contradictoires que vous envoie votre corps. »</t>
         </is>
       </c>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
     </row>
-    <row r="104" ht="30" customHeight="1">
+    <row r="104" ht="135" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3101,17 +3101,17 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closingSource</t>
+          <t>excerpt.closing</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>Ce livre parle de la même erreur à l’échelle de la cuisine. La version qui arrive tous les mardis. La version où votre corps écrit une histoire à propos d’un message, d’un silence, d’un regard, et où votre esprit retouche cette histoire sous la supervision de ce que votre corps ressent à ce moment-là. Personne ne meurt, mais des décisions se prennent. Des relations changent. Des jugements sur soi se forment. Et rien de tout cela n’avait à se passer ainsi, parce que les données étaient là depuis le début.</t>
         </is>
       </c>
       <c r="E104" s="11" t="n"/>
@@ -3125,17 +3125,17 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>excerpt.endNote</t>
+          <t>excerpt.closingSource</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Vient ensuite le chapitre zéro : Une journée qui aurait dû bien se passer.</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="E105" s="11" t="n"/>
@@ -3149,17 +3149,17 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>excerpt.unavailable</t>
+          <t>excerpt.endNote</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>The extract in this language will follow.</t>
+          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>L’extrait en français est à venir.</t>
+          <t>Vient ensuite le chapitre zéro : Une journée qui aurait dû bien se passer.</t>
         </is>
       </c>
       <c r="E106" s="11" t="n"/>
@@ -3173,17 +3173,17 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[0]</t>
+          <t>excerpt.unavailable</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>The extract in this language will follow.</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>L’extrait en français est à venir.</t>
         </is>
       </c>
       <c r="E107" s="11" t="n"/>
@@ -3197,17 +3197,17 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[1]</t>
+          <t>excerpt.folios[0]</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E108" s="11" t="n"/>
@@ -3221,57 +3221,57 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[2]</t>
+          <t>excerpt.folios[1]</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
     </row>
-    <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.folios[2]</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="n"/>
+      <c r="F110" s="11" t="n"/>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>CASE EVIDENCE CARDS</t>
         </is>
       </c>
-      <c r="B110" s="8" t="n"/>
-      <c r="C110" s="8" t="n"/>
-      <c r="D110" s="8" t="n"/>
-      <c r="E110" s="8" t="n"/>
-      <c r="F110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>cases.eyebrow</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>Case evidence</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>Pièces du dossier</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="n"/>
-      <c r="F111" s="11" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>cases.pageLabel</t>
+          <t>cases.eyebrow</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Case evidence</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Pièces du dossier</t>
         </is>
       </c>
       <c r="E112" s="11" t="n"/>
@@ -3305,17 +3305,17 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].quote</t>
+          <t>cases.pageLabel</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>“Something is off.”</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>« Quelque chose cloche. »</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="E113" s="11" t="n"/>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].inputLabel</t>
+          <t>cases.items[0].quote</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>“Something is off.”</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>« Quelque chose cloche. »</t>
         </is>
       </c>
       <c r="E114" s="11" t="n"/>
@@ -3353,17 +3353,17 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].input</t>
+          <t>cases.items[0].inputLabel</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Two minutes before the alarm.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Deux minutes avant le réveil.</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E115" s="11" t="n"/>
@@ -3377,17 +3377,17 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verifiedLabel</t>
+          <t>cases.items[0].input</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Verified event</t>
+          <t>Two minutes before the alarm.</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Événement vérifié</t>
+          <t>Deux minutes avant le réveil.</t>
         </is>
       </c>
       <c r="E116" s="11" t="n"/>
@@ -3401,17 +3401,17 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verified</t>
+          <t>cases.items[0].verifiedLabel</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Nothing has happened.</t>
+          <t>Verified event</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Il ne s’est rien passé.</t>
+          <t>Événement vérifié</t>
         </is>
       </c>
       <c r="E117" s="11" t="n"/>
@@ -3425,17 +3425,17 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].quote</t>
+          <t>cases.items[0].verified</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>“ok.”</t>
+          <t>Nothing has happened.</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>« ok. »</t>
+          <t>Il ne s’est rien passé.</t>
         </is>
       </c>
       <c r="E118" s="11" t="n"/>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].inputLabel</t>
+          <t>cases.items[1].quote</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>“ok.”</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>« ok. »</t>
         </is>
       </c>
       <c r="E119" s="11" t="n"/>
@@ -3473,17 +3473,17 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].input</t>
+          <t>cases.items[1].inputLabel</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Two letters. One full stop.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Deux lettres. Un point.</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E120" s="11" t="n"/>
@@ -3497,17 +3497,17 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verifiedLabel</t>
+          <t>cases.items[1].input</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Verified tone</t>
+          <t>Two letters. One full stop.</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Ton vérifié</t>
+          <t>Deux lettres. Un point.</t>
         </is>
       </c>
       <c r="E121" s="11" t="n"/>
@@ -3521,17 +3521,17 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verified</t>
+          <t>cases.items[1].verifiedLabel</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Verified tone</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Aucun.</t>
+          <t>Ton vérifié</t>
         </is>
       </c>
       <c r="E122" s="11" t="n"/>
@@ -3545,17 +3545,17 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].quote</t>
+          <t>cases.items[1].verified</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>“Something is wrong with my life.”</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>« Quelque chose ne va pas dans ma vie. »</t>
+          <t>Aucun.</t>
         </is>
       </c>
       <c r="E123" s="11" t="n"/>
@@ -3569,17 +3569,17 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].inputLabel</t>
+          <t>cases.items[2].quote</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>“Something is wrong with my life.”</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>« Quelque chose ne va pas dans ma vie. »</t>
         </is>
       </c>
       <c r="E124" s="11" t="n"/>
@@ -3593,17 +3593,17 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].input</t>
+          <t>cases.items[2].inputLabel</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Six ordinary events. One depleted day.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>Six événements ordinaires. Une journée à plat.</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E125" s="11" t="n"/>
@@ -3617,17 +3617,17 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verifiedLabel</t>
+          <t>cases.items[2].input</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Verified crisis</t>
+          <t>Six ordinary events. One depleted day.</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Crise vérifiée</t>
+          <t>Six événements ordinaires. Une journée à plat.</t>
         </is>
       </c>
       <c r="E126" s="11" t="n"/>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verified</t>
+          <t>cases.items[2].verifiedLabel</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Verified crisis</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Aucune.</t>
+          <t>Crise vérifiée</t>
         </is>
       </c>
       <c r="E127" s="11" t="n"/>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].quote</t>
+          <t>cases.items[2].verified</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>“This is state, not situation.”</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>« C’est l’état, pas la situation. »</t>
+          <t>Aucune.</t>
         </is>
       </c>
       <c r="E128" s="11" t="n"/>
@@ -3689,17 +3689,17 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].inputLabel</t>
+          <t>cases.items[3].quote</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>“This is state, not situation.”</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>« C’est l’état, pas la situation. »</t>
         </is>
       </c>
       <c r="E129" s="11" t="n"/>
@@ -3713,17 +3713,17 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].input</t>
+          <t>cases.items[3].inputLabel</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Low fuel. Dead light. A sound on grit.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Réservoir bas. Néon mort. Un bruit sur le gravier.</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E130" s="11" t="n"/>
@@ -3737,17 +3737,17 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verifiedLabel</t>
+          <t>cases.items[3].input</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Verified threat</t>
+          <t>Low fuel. Dead light. A sound on grit.</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Menace vérifiée</t>
+          <t>Réservoir bas. Néon mort. Un bruit sur le gravier.</t>
         </is>
       </c>
       <c r="E131" s="11" t="n"/>
@@ -3761,17 +3761,17 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verified</t>
+          <t>cases.items[3].verifiedLabel</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Not yet visible.</t>
+          <t>Verified threat</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Pas encore visible.</t>
+          <t>Menace vérifiée</t>
         </is>
       </c>
       <c r="E132" s="11" t="n"/>
@@ -3785,17 +3785,17 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>cases.closing</t>
+          <t>cases.items[3].verified</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>It said I am failing; the data was I am tired.</t>
+          <t>Not yet visible.</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>Ça disait je suis en train d’échouer ; les données, c’était je suis fatiguée.</t>
+          <t>Pas encore visible.</t>
         </is>
       </c>
       <c r="E133" s="11" t="n"/>
@@ -3809,57 +3809,57 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>cases.closingSource</t>
+          <t>cases.closing</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>It said I am failing; the data was I am tired.</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>Ça disait je suis en train d’échouer ; les données, c’était je suis fatiguée.</t>
         </is>
       </c>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
     </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Case evidence cards</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>cases.closingSource</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>Page 20</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Page 20</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="n"/>
+      <c r="F135" s="11" t="n"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
         </is>
       </c>
-      <c r="B135" s="8" t="n"/>
-      <c r="C135" s="8" t="n"/>
-      <c r="D135" s="8" t="n"/>
-      <c r="E135" s="8" t="n"/>
-      <c r="F135" s="8" t="n"/>
-    </row>
-    <row r="136" ht="30" customHeight="1">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>Audio player (hidden until a recording exists)</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="inlineStr">
-        <is>
-          <t>listen.eyebrow</t>
-        </is>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>Listen</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Écouter</t>
-        </is>
-      </c>
-      <c r="E136" s="11" t="n"/>
-      <c r="F136" s="11" t="n"/>
+      <c r="B136" s="8" t="n"/>
+      <c r="C136" s="8" t="n"/>
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="8" t="n"/>
+      <c r="F136" s="8" t="n"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>listen.title</t>
+          <t>listen.eyebrow</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Listen to an extract</t>
+          <t>Listen</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Écouter un extrait</t>
+          <t>Écouter</t>
         </is>
       </c>
       <c r="E137" s="11" t="n"/>
@@ -3893,17 +3893,17 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>listen.subtitle</t>
+          <t>listen.title</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Read by the author</t>
+          <t>Listen to an extract</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Lu par l’autrice</t>
+          <t>Écouter un extrait</t>
         </is>
       </c>
       <c r="E138" s="11" t="n"/>
@@ -3917,17 +3917,17 @@
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>listen.play</t>
+          <t>listen.subtitle</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Read by the author</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Écouter</t>
+          <t>Lu par l’autrice</t>
         </is>
       </c>
       <c r="E139" s="11" t="n"/>
@@ -3941,17 +3941,17 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>listen.pause</t>
+          <t>listen.play</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Écouter</t>
         </is>
       </c>
       <c r="E140" s="11" t="n"/>
@@ -3965,17 +3965,17 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>listen.progress</t>
+          <t>listen.pause</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Playback position</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Position dans l’enregistrement</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="E141" s="11" t="n"/>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>listen.elapsed</t>
+          <t>listen.progress</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Elapsed</t>
+          <t>Playback position</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Écoulé</t>
+          <t>Position dans l’enregistrement</t>
         </is>
       </c>
       <c r="E142" s="11" t="n"/>
@@ -4013,17 +4013,17 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>listen.duration</t>
+          <t>listen.elapsed</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Elapsed</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>Durée</t>
+          <t>Écoulé</t>
         </is>
       </c>
       <c r="E143" s="11" t="n"/>
@@ -4037,77 +4037,77 @@
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>listen.unavailable</t>
+          <t>listen.duration</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>The recording will be added here.</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>L’enregistrement sera ajouté ici.</t>
+          <t>Durée</t>
         </is>
       </c>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
     </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>A MAP OF THE BOOK — THE THREE SYSTEMS, THE EVIDENCE MARKERS, THE SIXTEEN CHAPTERS, THE SCIENTIFIC HEARTBEAT</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="n"/>
-      <c r="C145" s="8" t="n"/>
-      <c r="D145" s="8" t="n"/>
-      <c r="E145" s="8" t="n"/>
-      <c r="F145" s="8" t="n"/>
-    </row>
-    <row r="146" ht="30" customHeight="1">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="inlineStr">
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>Audio player (hidden until a recording exists)</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>listen.unavailable</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>The recording will be added here.</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>L’enregistrement sera ajouté ici.</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="n"/>
+      <c r="F145" s="11" t="n"/>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>“BEFORE WE BEGIN” (PAGE 13 MARKERS) AND THE MAP — THE THREE SYSTEMS, THE SIXTEEN CHAPTERS, PAGE 226</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="n"/>
+      <c r="C146" s="8" t="n"/>
+      <c r="D146" s="8" t="n"/>
+      <c r="E146" s="8" t="n"/>
+      <c r="F146" s="8" t="n"/>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
         <is>
           <t>map.eyebrow</t>
         </is>
       </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>A map of the book</t>
         </is>
       </c>
-      <c r="D146" s="10" t="inlineStr">
+      <c r="D147" s="10" t="inlineStr">
         <is>
           <t>Une carte du livre</t>
-        </is>
-      </c>
-      <c r="E146" s="11" t="n"/>
-      <c r="F146" s="11" t="n"/>
-    </row>
-    <row r="147" ht="90" customHeight="1">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>map.systemsIntro</t>
-        </is>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>Three systems ran through Katrin’s morning. Time started at 06:38 and never stopped. Attention took the phone at 06:52. Safety wrote the email’s meaning at 07:25. She can name none of them. The only thing she can name is David, and David is the smallest part of it.</t>
-        </is>
-      </c>
-      <c r="D147" s="10" t="inlineStr">
-        <is>
-          <t>Trois systèmes ont tourné pendant toute la matinée de Katrin. Le Temps a démarré à 06:38 et ne s’est jamais arrêté. L’Attention a pris le téléphone à 06:52. La Sécurité a écrit le sens de l’e-mail à 07:25. Elle ne peut en nommer aucun. La seule chose qu’elle peut nommer, c’est David, et David en est la plus petite part.</t>
         </is>
       </c>
       <c r="E147" s="11" t="n"/>
@@ -4116,262 +4116,262 @@
     <row r="148" ht="90" customHeight="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>map.sortingTool</t>
+          <t>map.systemsIntro</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
+          <t>Three systems ran through Katrin’s morning. Time started at 06:38 and never stopped. Attention took the phone at 06:52. Safety wrote the email’s meaning at 07:25. She can name none of them. The only thing she can name is David, and David is the smallest part of it.</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>Les chapitres qui suivent sont organisés autour de trois systèmes qui règlent le poids que prennent les signaux de votre corps avant que votre esprit ne construise une histoire. Ce ne sont pas des régions du cerveau ni des voies neuronales. C’est un outil de tri, une façon de poser trois questions quand tout semble aller de travers en même temps.</t>
+          <t>Trois systèmes ont tourné pendant toute la matinée de Katrin. Le Temps a démarré à 06:38 et ne s’est jamais arrêté. L’Attention a pris le téléphone à 06:52. La Sécurité a écrit le sens de l’e-mail à 07:25. Elle ne peut en nommer aucun. La seule chose qu’elle peut nommer, c’est David, et David en est la plus petite part.</t>
         </is>
       </c>
       <c r="E148" s="11" t="n"/>
       <c r="F148" s="11" t="n"/>
     </row>
-    <row r="149" ht="30" customHeight="1">
+    <row r="149" ht="90" customHeight="1">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].name</t>
+          <t>map.sortingTool</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Temps</t>
+          <t>Les chapitres qui suivent sont organisés autour de trois systèmes qui règlent le poids que prennent les signaux de votre corps avant que votre esprit ne construise une histoire. Ce ne sont pas des régions du cerveau ni des voies neuronales. C’est un outil de tri, une façon de poser trois questions quand tout semble aller de travers en même temps.</t>
         </is>
       </c>
       <c r="E149" s="11" t="n"/>
       <c r="F149" s="11" t="n"/>
     </row>
-    <row r="150" ht="45" customHeight="1">
+    <row r="150" ht="30" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].body</t>
+          <t>map.loops[0].name</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>Sommeil, alimentation, caféine, phase circadienne, récupération. Quand le rythme est décalé, la sensibilité de base augmente. Le même monde paraît plus dur.</t>
+          <t>Temps</t>
         </is>
       </c>
       <c r="E150" s="11" t="n"/>
       <c r="F150" s="11" t="n"/>
     </row>
-    <row r="151" ht="30" customHeight="1">
+    <row r="151" ht="45" customHeight="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].name</t>
+          <t>map.loops[0].body</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Sommeil, alimentation, caféine, phase circadienne, récupération. Quand le rythme est décalé, la sensibilité de base augmente. Le même monde paraît plus dur.</t>
         </is>
       </c>
       <c r="E151" s="11" t="n"/>
       <c r="F151" s="11" t="n"/>
     </row>
-    <row r="152" ht="60" customHeight="1">
+    <row r="152" ht="30" customHeight="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].body</t>
+          <t>map.loops[1].name</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Le système qui suit la récompense, la nouveauté et le prochain déclencheur. Quand il est accaparé, l’attention se resserre sur ce qu’il y a de moins exigeant à portée de main, et le travail exigeant paraît difficile.</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="E152" s="11" t="n"/>
       <c r="F152" s="11" t="n"/>
     </row>
-    <row r="153" ht="30" customHeight="1">
+    <row r="153" ht="60" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].name</t>
+          <t>map.loops[1].body</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Le système qui suit la récompense, la nouveauté et le prochain déclencheur. Quand il est accaparé, l’attention se resserre sur ce qu’il y a de moins exigeant à portée de main, et le travail exigeant paraît difficile.</t>
         </is>
       </c>
       <c r="E153" s="11" t="n"/>
       <c r="F153" s="11" t="n"/>
     </row>
-    <row r="154" ht="75" customHeight="1">
+    <row r="154" ht="30" customHeight="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].body</t>
+          <t>map.loops[2].name</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Le système qui surveille la menace, et surtout la menace sociale. Des choses comme l’évaluation sociale, l’exclusion, l’ambiguïté, le statut. Il est rapide, il est ancien, et il penche du côté des fausses alertes. Il produit des interprétations qui ressemblent à des faits.</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="E154" s="11" t="n"/>
       <c r="F154" s="11" t="n"/>
     </row>
-    <row r="155" ht="30" customHeight="1">
+    <row r="155" ht="75" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceEyebrow</t>
+          <t>map.loops[2].body</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Before we begin</t>
+          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Avant de commencer</t>
+          <t>Le système qui surveille la menace, et surtout la menace sociale. Des choses comme l’évaluation sociale, l’exclusion, l’ambiguïté, le statut. Il est rapide, il est ancien, et il penche du côté des fausses alertes. Il produit des interprétations qui ressemblent à des faits.</t>
         </is>
       </c>
       <c r="E155" s="11" t="n"/>
       <c r="F155" s="11" t="n"/>
     </row>
-    <row r="156" ht="120" customHeight="1">
+    <row r="156" ht="30" customHeight="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceIntro</t>
+          <t>map.evidenceEyebrow</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
+          <t>Before we begin</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Ce livre avance des affirmations sur le cerveau et sur le corps, et ces affirmations ne sont pas toutes également étayées. Certaines s’appuient sur des décennies de recherches répliquées. Certaines s’appuient sur des résultats plus récents, prometteurs mais pas encore consolidés. Certaines sont des prolongements plausibles d’une science établie, qui n’ont pas été testés directement sous la forme précise que décrit ce livre. Vous devriez savoir lesquelles sont lesquelles.</t>
+          <t>Avant de commencer</t>
         </is>
       </c>
       <c r="E156" s="11" t="n"/>
       <c r="F156" s="11" t="n"/>
     </row>
-    <row r="157" ht="180" customHeight="1">
+    <row r="157" ht="120" customHeight="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceMarkers</t>
+          <t>map.evidenceIntro</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
+          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Tout au long du livre, les affirmations scientifiques portent un marqueur de confiance. Quand un résultat est solidement étayé et répliqué, vous verrez un repère indiquant un niveau de preuve élevé, sous la forme d’un pouls rouge profond dans la marge. Quand les preuves vont dans le sens de l’affirmation mais restent incomplètes, le niveau de preuve est noté moyen, avec un pouls orange. Quand une affirmation est une hypothèse plausible qui demande des tests plus poussés, elle est marquée faible, en gris délavé. Ces marqueurs existent parce que le risque que court ce livre est celui-là même qu’il décrit. Il ne veut pas traiter une histoire plausible comme une vérité établie. Ces marqueurs sont un frein à cela.</t>
+          <t>Ce livre avance des affirmations sur le cerveau et sur le corps, et ces affirmations ne sont pas toutes également étayées. Certaines s’appuient sur des décennies de recherches répliquées. Certaines s’appuient sur des résultats plus récents, prometteurs mais pas encore consolidés. Certaines sont des prolongements plausibles d’une science établie, qui n’ont pas été testés directement sous la forme précise que décrit ce livre. Vous devriez savoir lesquelles sont lesquelles.</t>
         </is>
       </c>
       <c r="E157" s="11" t="n"/>
       <c r="F157" s="11" t="n"/>
     </row>
-    <row r="158" ht="30" customHeight="1">
+    <row r="158" ht="180" customHeight="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>map.grades[0].label</t>
+          <t>map.evidenceMarkers</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>Élevé</t>
+          <t>Tout au long du livre, les affirmations scientifiques portent un marqueur de confiance. Quand un résultat est solidement étayé et répliqué, vous verrez un repère indiquant un niveau de preuve élevé, sous la forme d’un pouls rouge profond dans la marge. Quand les preuves vont dans le sens de l’affirmation mais restent incomplètes, le niveau de preuve est noté moyen, avec un pouls orange. Quand une affirmation est une hypothèse plausible qui demande des tests plus poussés, elle est marquée faible, en gris délavé. Ces marqueurs existent parce que le risque que court ce livre est celui-là même qu’il décrit. Il ne veut pas traiter une histoire plausible comme une vérité établie. Ces marqueurs sont un frein à cela.</t>
         </is>
       </c>
       <c r="E158" s="11" t="n"/>
@@ -4380,22 +4380,22 @@
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>map.grades[1].label</t>
+          <t>map.grades[0].label</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Élevé</t>
         </is>
       </c>
       <c r="E159" s="11" t="n"/>
@@ -4404,22 +4404,22 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>map.grades[2].label</t>
+          <t>map.grades[1].label</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Faible</t>
+          <t>Moyen</t>
         </is>
       </c>
       <c r="E160" s="11" t="n"/>
@@ -4428,22 +4428,22 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>map.investigationTitle</t>
+          <t>map.grades[2].label</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>The Investigation</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>L’enquête</t>
+          <t>Faible</t>
         </is>
       </c>
       <c r="E161" s="11" t="n"/>
@@ -4452,22 +4452,22 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>map.mapLine</t>
+          <t>map.investigationTitle</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>The Investigation</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
+          <t>L’enquête</t>
         </is>
       </c>
       <c r="E162" s="11" t="n"/>
@@ -4476,22 +4476,22 @@
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>map.pageColumn</t>
+          <t>map.mapLine</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
         </is>
       </c>
       <c r="E163" s="11" t="n"/>
@@ -4500,22 +4500,22 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[0].title</t>
+          <t>map.pageColumn</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>A Day That Should Have Been Fine</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>Une journée qui aurait dû bien se passer</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="E164" s="11" t="n"/>
@@ -4524,22 +4524,22 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[1].title</t>
+          <t>map.chapters[0].title</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>The Radar Was Right</t>
+          <t>A Day That Should Have Been Fine</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Le radar avait raison</t>
+          <t>Une journée qui aurait dû bien se passer</t>
         </is>
       </c>
       <c r="E165" s="11" t="n"/>
@@ -4548,22 +4548,22 @@
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[2].title</t>
+          <t>map.chapters[1].title</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
+          <t>The Radar Was Right</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi le manque de sommeil fait paraître hostile ce qui est neutre</t>
+          <t>Le radar avait raison</t>
         </is>
       </c>
       <c r="E166" s="11" t="n"/>
@@ -4572,22 +4572,22 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[3].title</t>
+          <t>map.chapters[2].title</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>The Relief That Becomes Itch</t>
+          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Le soulagement qui tourne à la démangeaison</t>
+          <t>Pourquoi le manque de sommeil fait paraître hostile ce qui est neutre</t>
         </is>
       </c>
       <c r="E167" s="11" t="n"/>
@@ -4596,22 +4596,22 @@
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[4].title</t>
+          <t>map.chapters[3].title</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>The Predictable Cue</t>
+          <t>The Relief That Becomes Itch</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>Le déclencheur prévisible</t>
+          <t>Le soulagement qui tourne à la démangeaison</t>
         </is>
       </c>
       <c r="E168" s="11" t="n"/>
@@ -4620,22 +4620,22 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[5].title</t>
+          <t>map.chapters[4].title</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Why Evenings Stretch and Mornings Shrink</t>
+          <t>The Predictable Cue</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi les soirées s’étirent et les matins rétrécissent</t>
+          <t>Le déclencheur prévisible</t>
         </is>
       </c>
       <c r="E169" s="11" t="n"/>
@@ -4644,22 +4644,22 @@
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[6].title</t>
+          <t>map.chapters[5].title</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>Why Rest Doesn’t Always Restore</t>
+          <t>Why Evenings Stretch and Mornings Shrink</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi le repos ne ressource pas toujours</t>
+          <t>Pourquoi les soirées s’étirent et les matins rétrécissent</t>
         </is>
       </c>
       <c r="E170" s="11" t="n"/>
@@ -4668,22 +4668,22 @@
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[7].title</t>
+          <t>map.chapters[6].title</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Why You Cannot Start the Thing That Matters</t>
+          <t>Why Rest Doesn’t Always Restore</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi vous n’arrivez pas à commencer ce qui compte</t>
+          <t>Pourquoi le repos ne ressource pas toujours</t>
         </is>
       </c>
       <c r="E171" s="11" t="n"/>
@@ -4692,22 +4692,22 @@
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[8].title</t>
+          <t>map.chapters[7].title</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>The Open File</t>
+          <t>Why You Cannot Start the Thing That Matters</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Le dossier ouvert</t>
+          <t>Pourquoi vous n’arrivez pas à commencer ce qui compte</t>
         </is>
       </c>
       <c r="E172" s="11" t="n"/>
@@ -4716,22 +4716,22 @@
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[9].title</t>
+          <t>map.chapters[8].title</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Two Nervous Systems Walk Into a Kitchen</t>
+          <t>The Open File</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>Deux systèmes nerveux entrent dans une cuisine</t>
+          <t>Le dossier ouvert</t>
         </is>
       </c>
       <c r="E173" s="11" t="n"/>
@@ -4740,22 +4740,22 @@
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[10].title</t>
+          <t>map.chapters[9].title</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>The Argument That Was Tuesday</t>
+          <t>Two Nervous Systems Walk Into a Kitchen</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>La dispute qui était mardi</t>
+          <t>Deux systèmes nerveux entrent dans une cuisine</t>
         </is>
       </c>
       <c r="E174" s="11" t="n"/>
@@ -4764,22 +4764,22 @@
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[11].title</t>
+          <t>map.chapters[10].title</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>The Thursday That Was Wednesday Night</t>
+          <t>The Argument That Was Tuesday</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>Le jeudi qui était mercredi soir</t>
+          <t>La dispute qui était mardi</t>
         </is>
       </c>
       <c r="E175" s="11" t="n"/>
@@ -4788,22 +4788,22 @@
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[12].title</t>
+          <t>map.chapters[11].title</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>The Clean Panel</t>
+          <t>The Thursday That Was Wednesday Night</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>Le tableau de bord au vert</t>
+          <t>Le jeudi qui était mercredi soir</t>
         </is>
       </c>
       <c r="E176" s="11" t="n"/>
@@ -4812,22 +4812,22 @@
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[13].title</t>
+          <t>map.chapters[12].title</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>The Time the Body Was Right</t>
+          <t>The Clean Panel</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>La fois où le corps avait raison</t>
+          <t>Le tableau de bord au vert</t>
         </is>
       </c>
       <c r="E177" s="11" t="n"/>
@@ -4836,22 +4836,22 @@
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[14].title</t>
+          <t>map.chapters[13].title</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>Not About Me</t>
+          <t>The Time the Body Was Right</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>Rien à voir avec moi</t>
+          <t>La fois où le corps avait raison</t>
         </is>
       </c>
       <c r="E178" s="11" t="n"/>
@@ -4860,22 +4860,22 @@
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[15].title</t>
+          <t>map.chapters[14].title</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>The Forecast</t>
+          <t>Not About Me</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>La prévision</t>
+          <t>Rien à voir avec moi</t>
         </is>
       </c>
       <c r="E179" s="11" t="n"/>
@@ -4884,70 +4884,70 @@
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
         <is>
-          <t>map.mapFooter</t>
+          <t>map.chapters[15].title</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>The Scientific Heartbeat follows the chapters.</t>
+          <t>The Forecast</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>Le pouls scientifique suit les chapitres.</t>
+          <t>La prévision</t>
         </is>
       </c>
       <c r="E180" s="11" t="n"/>
       <c r="F180" s="11" t="n"/>
     </row>
-    <row r="181" ht="75" customHeight="1">
+    <row r="181" ht="30" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[0]</t>
+          <t>map.mapFooter</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>The Scientific Heartbeat follows the chapters.</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
+          <t>Le pouls scientifique suit les chapitres.</t>
         </is>
       </c>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
     </row>
-    <row r="182" ht="30" customHeight="1">
+    <row r="182" ht="75" customHeight="1">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[1]</t>
+          <t>map.heartbeat[0]</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
+          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
         </is>
       </c>
       <c r="E182" s="11" t="n"/>
@@ -4956,62 +4956,62 @@
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeatSource</t>
+          <t>map.heartbeat[1]</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
         </is>
       </c>
       <c r="E183" s="11" t="n"/>
       <c r="F183" s="11" t="n"/>
     </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>map.heartbeatSource</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>Page 226</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="inlineStr">
+        <is>
+          <t>Page 226</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="n"/>
+      <c r="F184" s="11" t="n"/>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t>ABOUT THE AUTHOR</t>
         </is>
       </c>
-      <c r="B184" s="8" t="n"/>
-      <c r="C184" s="8" t="n"/>
-      <c r="D184" s="8" t="n"/>
-      <c r="E184" s="8" t="n"/>
-      <c r="F184" s="8" t="n"/>
-    </row>
-    <row r="185" ht="30" customHeight="1">
-      <c r="A185" s="9" t="inlineStr">
-        <is>
-          <t>About the author</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="inlineStr">
-        <is>
-          <t>author.eyebrow</t>
-        </is>
-      </c>
-      <c r="C185" s="10" t="inlineStr">
-        <is>
-          <t>The author</t>
-        </is>
-      </c>
-      <c r="D185" s="10" t="inlineStr">
-        <is>
-          <t>L’autrice</t>
-        </is>
-      </c>
-      <c r="E185" s="11" t="n"/>
-      <c r="F185" s="11" t="n"/>
+      <c r="B185" s="8" t="n"/>
+      <c r="C185" s="8" t="n"/>
+      <c r="D185" s="8" t="n"/>
+      <c r="E185" s="8" t="n"/>
+      <c r="F185" s="8" t="n"/>
     </row>
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="9" t="inlineStr">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>author.title</t>
+          <t>author.eyebrow</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>The author</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>L’autrice</t>
         </is>
       </c>
       <c r="E186" s="11" t="n"/>
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>author.photoAlt</t>
+          <t>author.title</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographed against a dark grey background.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographiée sur fond gris foncé.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E187" s="11" t="n"/>
@@ -5069,17 +5069,17 @@
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>author.photoPlaceholder</t>
+          <t>author.photoAlt</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Author photograph to follow</t>
+          <t>Ivana Budišin, photographed against a dark grey background.</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice à venir</t>
+          <t>Ivana Budišin, photographiée sur fond gris foncé.</t>
         </is>
       </c>
       <c r="E188" s="11" t="n"/>
@@ -5093,17 +5093,17 @@
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>author.bio</t>
+          <t>author.photoPlaceholder</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Author photograph to follow</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
+          <t>Photographie de l’autrice à venir</t>
         </is>
       </c>
       <c r="E189" s="11" t="n"/>
@@ -5117,17 +5117,17 @@
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>author.websiteLabel</t>
+          <t>author.bio</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Practice website</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Site du cabinet</t>
+          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
         </is>
       </c>
       <c r="E190" s="11" t="n"/>
@@ -5141,17 +5141,17 @@
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>author.contactLabel</t>
+          <t>author.websiteLabel</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Practice website</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Site du cabinet</t>
         </is>
       </c>
       <c r="E191" s="11" t="n"/>
@@ -5165,57 +5165,57 @@
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>author.pressLabel</t>
+          <t>author.contactLabel</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Dossier de presse</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E192" s="11" t="n"/>
       <c r="F192" s="11" t="n"/>
     </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="7" t="inlineStr">
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>About the author</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="inlineStr">
+        <is>
+          <t>author.pressLabel</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>Press materials</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>Dossier de presse</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="n"/>
+      <c r="F193" s="11" t="n"/>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
         </is>
       </c>
-      <c r="B193" s="8" t="n"/>
-      <c r="C193" s="8" t="n"/>
-      <c r="D193" s="8" t="n"/>
-      <c r="E193" s="8" t="n"/>
-      <c r="F193" s="8" t="n"/>
-    </row>
-    <row r="194" ht="30" customHeight="1">
-      <c r="A194" s="9" t="inlineStr">
-        <is>
-          <t>The book’s last sentence, above the notify form</t>
-        </is>
-      </c>
-      <c r="B194" s="9" t="inlineStr">
-        <is>
-          <t>closing.question</t>
-        </is>
-      </c>
-      <c r="C194" s="10" t="inlineStr">
-        <is>
-          <t>Is this the situation? Or is this their state?</t>
-        </is>
-      </c>
-      <c r="D194" s="10" t="inlineStr">
-        <is>
-          <t>Est-ce la situation ? Ou est-ce leur état ?</t>
-        </is>
-      </c>
-      <c r="E194" s="11" t="n"/>
-      <c r="F194" s="11" t="n"/>
+      <c r="B194" s="8" t="n"/>
+      <c r="C194" s="8" t="n"/>
+      <c r="D194" s="8" t="n"/>
+      <c r="E194" s="8" t="n"/>
+      <c r="F194" s="8" t="n"/>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="9" t="inlineStr">
@@ -5225,93 +5225,93 @@
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>closing.source</t>
+          <t>closing.question</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>Is this the situation? Or is this their state?</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>Est-ce la situation ? Ou est-ce leur état ?</t>
         </is>
       </c>
       <c r="E195" s="11" t="n"/>
       <c r="F195" s="11" t="n"/>
     </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="7" t="inlineStr">
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>The book’s last sentence, above the notify form</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
+        <is>
+          <t>closing.source</t>
+        </is>
+      </c>
+      <c r="C196" s="10" t="inlineStr">
+        <is>
+          <t>Page 225</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <t>Page 225</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="n"/>
+      <c r="F196" s="11" t="n"/>
+    </row>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="7" t="inlineStr">
         <is>
           <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="n"/>
-      <c r="C196" s="8" t="n"/>
-      <c r="D196" s="8" t="n"/>
-      <c r="E196" s="8" t="n"/>
-      <c r="F196" s="8" t="n"/>
-    </row>
-    <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="9" t="inlineStr">
+      <c r="B197" s="8" t="n"/>
+      <c r="C197" s="8" t="n"/>
+      <c r="D197" s="8" t="n"/>
+      <c r="E197" s="8" t="n"/>
+      <c r="F197" s="8" t="n"/>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="9" t="inlineStr">
         <is>
           <t>Companion tool (currently hidden)</t>
         </is>
       </c>
-      <c r="B197" s="9" t="inlineStr">
+      <c r="B198" s="9" t="inlineStr">
         <is>
           <t>companion.eyebrow</t>
         </is>
       </c>
-      <c r="C197" s="10" t="inlineStr">
+      <c r="C198" s="10" t="inlineStr">
         <is>
           <t>Alongside the book</t>
         </is>
       </c>
-      <c r="D197" s="10" t="inlineStr">
+      <c r="D198" s="10" t="inlineStr">
         <is>
           <t>En complément du livre</t>
         </is>
       </c>
-      <c r="E197" s="11" t="n"/>
-      <c r="F197" s="11" t="n"/>
-    </row>
-    <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="7" t="inlineStr">
+      <c r="E198" s="11" t="n"/>
+      <c r="F198" s="11" t="n"/>
+    </row>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
         <is>
           <t>PRESS PAGE</t>
         </is>
       </c>
-      <c r="B198" s="8" t="n"/>
-      <c r="C198" s="8" t="n"/>
-      <c r="D198" s="8" t="n"/>
-      <c r="E198" s="8" t="n"/>
-      <c r="F198" s="8" t="n"/>
-    </row>
-    <row r="199" ht="30" customHeight="1">
-      <c r="A199" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B199" s="9" t="inlineStr">
-        <is>
-          <t>press.eyebrow</t>
-        </is>
-      </c>
-      <c r="C199" s="10" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
-      <c r="D199" s="10" t="inlineStr">
-        <is>
-          <t>Presse</t>
-        </is>
-      </c>
-      <c r="E199" s="11" t="n"/>
-      <c r="F199" s="11" t="n"/>
+      <c r="B199" s="8" t="n"/>
+      <c r="C199" s="8" t="n"/>
+      <c r="D199" s="8" t="n"/>
+      <c r="E199" s="8" t="n"/>
+      <c r="F199" s="8" t="n"/>
     </row>
     <row r="200" ht="30" customHeight="1">
       <c r="A200" s="9" t="inlineStr">
@@ -5321,23 +5321,23 @@
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>press.title</t>
+          <t>press.eyebrow</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>Dossier de presse</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E200" s="11" t="n"/>
       <c r="F200" s="11" t="n"/>
     </row>
-    <row r="201" ht="45" customHeight="1">
+    <row r="201" ht="30" customHeight="1">
       <c r="A201" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5345,23 +5345,23 @@
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>press.intro</t>
+          <t>press.title</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>Des exemplaires de presse, papier et numérique, sont disponibles sur demande. Reproduction d’extraits, entretiens et rencontres à convenir.</t>
+          <t>Dossier de presse</t>
         </is>
       </c>
       <c r="E201" s="11" t="n"/>
       <c r="F201" s="11" t="n"/>
     </row>
-    <row r="202" ht="30" customHeight="1">
+    <row r="202" ht="45" customHeight="1">
       <c r="A202" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>press.contactHeading</t>
+          <t>press.intro</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Des exemplaires de presse, papier et numérique, sont disponibles sur demande. Reproduction d’extraits, entretiens et rencontres à convenir.</t>
         </is>
       </c>
       <c r="E202" s="11" t="n"/>
@@ -5393,17 +5393,17 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>press.assetsHeading</t>
+          <t>press.contactHeading</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>Téléchargements</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E203" s="11" t="n"/>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].label</t>
+          <t>press.assetsHeading</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>Front cover, high resolution</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>Première de couverture, haute résolution</t>
+          <t>Téléchargements</t>
         </is>
       </c>
       <c r="E204" s="11" t="n"/>
@@ -5441,17 +5441,17 @@
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].note</t>
+          <t>press.assets[0].label</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px wide</t>
+          <t>Front cover, high resolution</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px de large</t>
+          <t>Première de couverture, haute résolution</t>
         </is>
       </c>
       <c r="E205" s="11" t="n"/>
@@ -5465,17 +5465,17 @@
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].label</t>
+          <t>press.assets[0].note</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>Author photograph</t>
+          <t>JPEG, 2400 px wide</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice</t>
+          <t>JPEG, 2400 px de large</t>
         </is>
       </c>
       <c r="E206" s="11" t="n"/>
@@ -5489,17 +5489,17 @@
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].note</t>
+          <t>press.assets[1].label</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>Author photograph</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>Photographie de l’autrice</t>
         </is>
       </c>
       <c r="E207" s="11" t="n"/>
@@ -5513,17 +5513,17 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].label</t>
+          <t>press.assets[1].note</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>Book render, transparent background</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>Rendu du livre, fond transparent</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="E208" s="11" t="n"/>
@@ -5537,17 +5537,17 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].note</t>
+          <t>press.assets[2].label</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Book render, transparent background</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Rendu du livre, fond transparent</t>
         </is>
       </c>
       <c r="E209" s="11" t="n"/>
@@ -5561,17 +5561,17 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].label</t>
+          <t>press.assets[2].note</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>Web banner</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>Bannière web</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="E210" s="11" t="n"/>
@@ -5585,17 +5585,17 @@
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].note</t>
+          <t>press.assets[3].label</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Web banner</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Bannière web</t>
         </is>
       </c>
       <c r="E211" s="11" t="n"/>
@@ -5609,17 +5609,17 @@
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].label</t>
+          <t>press.assets[3].note</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>Social image, square</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, carrée</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="E212" s="11" t="n"/>
@@ -5633,17 +5633,17 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].note</t>
+          <t>press.assets[4].label</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Social image, square</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Image pour les réseaux, carrée</t>
         </is>
       </c>
       <c r="E213" s="11" t="n"/>
@@ -5657,17 +5657,17 @@
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].label</t>
+          <t>press.assets[4].note</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>Social image, portrait</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, portrait</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="E214" s="11" t="n"/>
@@ -5681,17 +5681,17 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].note</t>
+          <t>press.assets[5].label</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>Social image, portrait</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>Image pour les réseaux, portrait</t>
         </is>
       </c>
       <c r="E215" s="11" t="n"/>
@@ -5705,17 +5705,17 @@
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].label</t>
+          <t>press.assets[5].note</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>Social image, landscape</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, paysage</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="E216" s="11" t="n"/>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].note</t>
+          <t>press.assets[6].label</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Social image, landscape</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Image pour les réseaux, paysage</t>
         </is>
       </c>
       <c r="E217" s="11" t="n"/>
@@ -5753,17 +5753,17 @@
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].label</t>
+          <t>press.assets[6].note</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>The opening extract</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>L’extrait d’ouverture</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="E218" s="11" t="n"/>
@@ -5777,17 +5777,17 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].note</t>
+          <t>press.assets[7].label</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>PDF, four pages</t>
+          <t>The opening extract</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>PDF, quatre pages</t>
+          <t>L’extrait d’ouverture</t>
         </is>
       </c>
       <c r="E219" s="11" t="n"/>
@@ -5801,17 +5801,17 @@
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>press.photoUnavailable</t>
+          <t>press.assets[7].note</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>Author photograph available on request.</t>
+          <t>PDF, four pages</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice disponible sur demande.</t>
+          <t>PDF, quatre pages</t>
         </is>
       </c>
       <c r="E220" s="11" t="n"/>
@@ -5825,17 +5825,17 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>press.bioHeading</t>
+          <t>press.photoUnavailable</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Author photograph available on request.</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>Biographie</t>
+          <t>Photographie de l’autrice disponible sur demande.</t>
         </is>
       </c>
       <c r="E221" s="11" t="n"/>
@@ -5849,17 +5849,17 @@
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].label</t>
+          <t>press.bioHeading</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>Courte</t>
+          <t>Biographie</t>
         </is>
       </c>
       <c r="E222" s="11" t="n"/>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].text</t>
+          <t>press.bios[0].label</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
+          <t>Courte</t>
         </is>
       </c>
       <c r="E223" s="11" t="n"/>
@@ -5897,17 +5897,17 @@
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>press.bios[1].label</t>
+          <t>press.bios[0].text</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>Longue</t>
+          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
         </is>
       </c>
       <c r="E224" s="11" t="n"/>
@@ -5921,17 +5921,17 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>press.factsHeading</t>
+          <t>press.bios[1].label</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Longue</t>
         </is>
       </c>
       <c r="E225" s="11" t="n"/>
@@ -5945,17 +5945,17 @@
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].label</t>
+          <t>press.factsHeading</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>Titre</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="E226" s="11" t="n"/>
@@ -5969,17 +5969,17 @@
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].value</t>
+          <t>press.facts[0].label</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>Titre</t>
         </is>
       </c>
       <c r="E227" s="11" t="n"/>
@@ -5993,17 +5993,17 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].label</t>
+          <t>press.facts[0].value</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>Subtitle</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>Sous-titre</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="E228" s="11" t="n"/>
@@ -6017,17 +6017,17 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].value</t>
+          <t>press.facts[1].label</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>Subtitle</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité</t>
+          <t>Sous-titre</t>
         </is>
       </c>
       <c r="E229" s="11" t="n"/>
@@ -6041,17 +6041,17 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].label</t>
+          <t>press.facts[1].value</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>Autrice</t>
+          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité</t>
         </is>
       </c>
       <c r="E230" s="11" t="n"/>
@@ -6065,17 +6065,17 @@
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].value</t>
+          <t>press.facts[2].label</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Autrice</t>
         </is>
       </c>
       <c r="E231" s="11" t="n"/>
@@ -6089,17 +6089,17 @@
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].label</t>
+          <t>press.facts[2].value</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>Éditeur</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E232" s="11" t="n"/>
@@ -6113,17 +6113,17 @@
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].value</t>
+          <t>press.facts[3].label</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>Éditeur</t>
         </is>
       </c>
       <c r="E233" s="11" t="n"/>
@@ -6137,17 +6137,17 @@
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].label</t>
+          <t>press.facts[3].value</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Budisin Publishing, Luxembourg</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>Parution</t>
+          <t>Budisin Publishing, Luxembourg</t>
         </is>
       </c>
       <c r="E234" s="11" t="n"/>
@@ -6161,17 +6161,17 @@
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].value</t>
+          <t>press.facts[4].label</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Parution</t>
         </is>
       </c>
       <c r="E235" s="11" t="n"/>
@@ -6185,17 +6185,17 @@
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].label</t>
+          <t>press.facts[4].value</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" s="11" t="n"/>
@@ -6209,17 +6209,17 @@
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].value</t>
+          <t>press.facts[5].label</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 in</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>Broché, 15,2 × 22,9 cm (6 × 9 pouces)</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="E237" s="11" t="n"/>
@@ -6233,17 +6233,17 @@
       </c>
       <c r="B238" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].label</t>
+          <t>press.facts[5].value</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
         <is>
-          <t>Extent</t>
+          <t>Paperback, 6 × 9 in</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Broché, 15,2 × 22,9 cm (6 × 9 pouces)</t>
         </is>
       </c>
       <c r="E238" s="11" t="n"/>
@@ -6257,17 +6257,17 @@
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].value</t>
+          <t>press.facts[6].label</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Extent</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E239" s="11" t="n"/>
@@ -6281,17 +6281,17 @@
       </c>
       <c r="B240" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].label</t>
+          <t>press.facts[6].value</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>278 pages</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>278 pages</t>
         </is>
       </c>
       <c r="E240" s="11" t="n"/>
@@ -6305,17 +6305,17 @@
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].value</t>
+          <t>press.facts[7].label</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="E241" s="11" t="n"/>
@@ -6329,17 +6329,17 @@
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].label</t>
+          <t>press.facts[7].value</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>Catégorie</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="E242" s="11" t="n"/>
@@ -6353,17 +6353,17 @@
       </c>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].value</t>
+          <t>press.facts[8].label</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t>Psychology / Cognitive psychology</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>Psychologie / Psychologie cognitive</t>
+          <t>Catégorie</t>
         </is>
       </c>
       <c r="E243" s="11" t="n"/>
@@ -6377,17 +6377,17 @@
       </c>
       <c r="B244" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].label</t>
+          <t>press.facts[8].value</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Psychology / Cognitive psychology</t>
         </is>
       </c>
       <c r="D244" s="10" t="inlineStr">
         <is>
-          <t>Langue</t>
+          <t>Psychologie / Psychologie cognitive</t>
         </is>
       </c>
       <c r="E244" s="11" t="n"/>
@@ -6401,17 +6401,17 @@
       </c>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].value</t>
+          <t>press.facts[9].label</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
         <is>
-          <t>English. French and German editions to follow.</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>Anglais. Éditions française et allemande à venir.</t>
+          <t>Langue</t>
         </is>
       </c>
       <c r="E245" s="11" t="n"/>
@@ -6425,17 +6425,17 @@
       </c>
       <c r="B246" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].label</t>
+          <t>press.facts[9].value</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
         <is>
-          <t>Legal deposit</t>
+          <t>English. French and German editions to follow.</t>
         </is>
       </c>
       <c r="D246" s="10" t="inlineStr">
         <is>
-          <t>Dépôt légal</t>
+          <t>Anglais. Éditions française et allemande à venir.</t>
         </is>
       </c>
       <c r="E246" s="11" t="n"/>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="B247" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].value</t>
+          <t>press.facts[10].label</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
         <is>
-          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
+          <t>Legal deposit</t>
         </is>
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>Une notice CIP est disponible à la Bibliothèque nationale du Luxembourg.</t>
+          <t>Dépôt légal</t>
         </is>
       </c>
       <c r="E247" s="11" t="n"/>
@@ -6473,23 +6473,23 @@
       </c>
       <c r="B248" s="9" t="inlineStr">
         <is>
-          <t>press.descriptionHeading</t>
+          <t>press.facts[10].value</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
         <is>
-          <t>About the book</t>
+          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>À propos du livre</t>
+          <t>Une notice CIP est disponible à la Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="E248" s="11" t="n"/>
       <c r="F248" s="11" t="n"/>
     </row>
-    <row r="249" ht="135" customHeight="1">
+    <row r="249" ht="30" customHeight="1">
       <c r="A249" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6497,23 +6497,23 @@
       </c>
       <c r="B249" s="9" t="inlineStr">
         <is>
-          <t>press.description[0]</t>
+          <t>press.descriptionHeading</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
         <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
+          <t>About the book</t>
         </is>
       </c>
       <c r="D249" s="10" t="inlineStr">
         <is>
-          <t>Pendant seize jours, Katrin traverse des situations ordinaires où sa première lecture de ce qui se passe n’est pas toujours celle qui tient, à y regarder de plus près. Chaque chapitre suit l’un de ces moments jusque dans la psychologie qui le sous-tend, de l’attention et de la prédiction à la mémoire, à la menace, à l’incertitude et à l’inférence sociale. Le livre ne promet pas un meilleur instinct. Il demande ce qui devient possible quand nous apprenons d’où venait notre première lecture.</t>
+          <t>À propos du livre</t>
         </is>
       </c>
       <c r="E249" s="11" t="n"/>
       <c r="F249" s="11" t="n"/>
     </row>
-    <row r="250" ht="45" customHeight="1">
+    <row r="250" ht="135" customHeight="1">
       <c r="A250" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6521,23 +6521,23 @@
       </c>
       <c r="B250" s="9" t="inlineStr">
         <is>
-          <t>press.description[1]</t>
+          <t>press.description[0]</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
         </is>
       </c>
       <c r="D250" s="10" t="inlineStr">
         <is>
-          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
+          <t>Pendant seize jours, Katrin traverse des situations ordinaires où sa première lecture de ce qui se passe n’est pas toujours celle qui tient, à y regarder de plus près. Chaque chapitre suit l’un de ces moments jusque dans la psychologie qui le sous-tend, de l’attention et de la prédiction à la mémoire, à la menace, à l’incertitude et à l’inférence sociale. Le livre ne promet pas un meilleur instinct. Il demande ce qui devient possible quand nous apprenons d’où venait notre première lecture.</t>
         </is>
       </c>
       <c r="E250" s="11" t="n"/>
       <c r="F250" s="11" t="n"/>
     </row>
-    <row r="251" ht="30" customHeight="1">
+    <row r="251" ht="45" customHeight="1">
       <c r="A251" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6545,23 +6545,23 @@
       </c>
       <c r="B251" s="9" t="inlineStr">
         <is>
-          <t>press.description[2]</t>
+          <t>press.description[1]</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
+          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
         </is>
       </c>
       <c r="E251" s="11" t="n"/>
       <c r="F251" s="11" t="n"/>
     </row>
-    <row r="252" ht="75" customHeight="1">
+    <row r="252" ht="30" customHeight="1">
       <c r="A252" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6569,23 +6569,23 @@
       </c>
       <c r="B252" s="9" t="inlineStr">
         <is>
-          <t>press.description[3]</t>
+          <t>press.description[2]</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D252" s="10" t="inlineStr">
         <is>
-          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
+          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
         </is>
       </c>
       <c r="E252" s="11" t="n"/>
       <c r="F252" s="11" t="n"/>
     </row>
-    <row r="253" ht="30" customHeight="1">
+    <row r="253" ht="75" customHeight="1">
       <c r="A253" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6593,17 +6593,17 @@
       </c>
       <c r="B253" s="9" t="inlineStr">
         <is>
-          <t>press.description[4]</t>
+          <t>press.description[3]</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
+          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
         </is>
       </c>
       <c r="E253" s="11" t="n"/>
@@ -6617,17 +6617,17 @@
       </c>
       <c r="B254" s="9" t="inlineStr">
         <is>
-          <t>press.creditsHeading</t>
+          <t>press.description[4]</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D254" s="10" t="inlineStr">
         <is>
-          <t>Crédits</t>
+          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
         </is>
       </c>
       <c r="E254" s="11" t="n"/>
@@ -6641,17 +6641,17 @@
       </c>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].label</t>
+          <t>press.creditsHeading</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
         <is>
-          <t>Cover design</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>Conception de la couverture</t>
+          <t>Crédits</t>
         </is>
       </c>
       <c r="E255" s="11" t="n"/>
@@ -6665,17 +6665,17 @@
       </c>
       <c r="B256" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].value</t>
+          <t>press.credits[0].label</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Cover design</t>
         </is>
       </c>
       <c r="D256" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Conception de la couverture</t>
         </is>
       </c>
       <c r="E256" s="11" t="n"/>
@@ -6689,17 +6689,17 @@
       </c>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>press.credits[1].label</t>
+          <t>press.credits[0].value</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
         <is>
-          <t>Book design and typesetting</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>Conception graphique et mise en page</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="E257" s="11" t="n"/>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="B258" s="9" t="inlineStr">
         <is>
-          <t>press.credits[1].value</t>
+          <t>press.credits[1].label</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Book design and typesetting</t>
         </is>
       </c>
       <c r="D258" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Conception graphique et mise en page</t>
         </is>
       </c>
       <c r="E258" s="11" t="n"/>
@@ -6737,17 +6737,17 @@
       </c>
       <c r="B259" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].label</t>
+          <t>press.credits[1].value</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
         <is>
-          <t>Published by</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D259" s="10" t="inlineStr">
         <is>
-          <t>Publié par</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E259" s="11" t="n"/>
@@ -6761,17 +6761,17 @@
       </c>
       <c r="B260" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].value</t>
+          <t>press.credits[2].label</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>Published by</t>
         </is>
       </c>
       <c r="D260" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>Publié par</t>
         </is>
       </c>
       <c r="E260" s="11" t="n"/>
@@ -6785,57 +6785,57 @@
       </c>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>press.back</t>
+          <t>press.credits[2].value</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>Retour au livre</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="E261" s="11" t="n"/>
       <c r="F261" s="11" t="n"/>
     </row>
-    <row r="262" ht="22" customHeight="1">
-      <c r="A262" s="7" t="inlineStr">
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B262" s="9" t="inlineStr">
+        <is>
+          <t>press.back</t>
+        </is>
+      </c>
+      <c r="C262" s="10" t="inlineStr">
+        <is>
+          <t>Back to the book</t>
+        </is>
+      </c>
+      <c r="D262" s="10" t="inlineStr">
+        <is>
+          <t>Retour au livre</t>
+        </is>
+      </c>
+      <c r="E262" s="11" t="n"/>
+      <c r="F262" s="11" t="n"/>
+    </row>
+    <row r="263" ht="22" customHeight="1">
+      <c r="A263" s="7" t="inlineStr">
         <is>
           <t>FOOT OF EVERY PAGE</t>
         </is>
       </c>
-      <c r="B262" s="8" t="n"/>
-      <c r="C262" s="8" t="n"/>
-      <c r="D262" s="8" t="n"/>
-      <c r="E262" s="8" t="n"/>
-      <c r="F262" s="8" t="n"/>
-    </row>
-    <row r="263" ht="30" customHeight="1">
-      <c r="A263" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B263" s="9" t="inlineStr">
-        <is>
-          <t>footer.band</t>
-        </is>
-      </c>
-      <c r="C263" s="10" t="inlineStr">
-        <is>
-          <t>Before you believe the story.</t>
-        </is>
-      </c>
-      <c r="D263" s="10" t="inlineStr">
-        <is>
-          <t>Avant de croire l’histoire.</t>
-        </is>
-      </c>
-      <c r="E263" s="11" t="n"/>
-      <c r="F263" s="11" t="n"/>
+      <c r="B263" s="8" t="n"/>
+      <c r="C263" s="8" t="n"/>
+      <c r="D263" s="8" t="n"/>
+      <c r="E263" s="8" t="n"/>
+      <c r="F263" s="8" t="n"/>
     </row>
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="9" t="inlineStr">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B264" s="9" t="inlineStr">
         <is>
-          <t>footer.method[0]</t>
+          <t>footer.band</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
         <is>
-          <t>Read the dashboard.</t>
+          <t>Before you believe the story.</t>
         </is>
       </c>
       <c r="D264" s="10" t="inlineStr">
         <is>
-          <t>Lisez le tableau de bord.</t>
+          <t>Avant de croire l’histoire.</t>
         </is>
       </c>
       <c r="E264" s="11" t="n"/>
@@ -6869,17 +6869,17 @@
       </c>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>footer.method[1]</t>
+          <t>footer.method[0]</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
         <is>
-          <t>Delay the story.</t>
+          <t>Read the dashboard.</t>
         </is>
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>Différez l’histoire.</t>
+          <t>Lisez le tableau de bord.</t>
         </is>
       </c>
       <c r="E265" s="11" t="n"/>
@@ -6893,17 +6893,17 @@
       </c>
       <c r="B266" s="9" t="inlineStr">
         <is>
-          <t>footer.method[2]</t>
+          <t>footer.method[1]</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
         <is>
-          <t>Take the reading again.</t>
+          <t>Delay the story.</t>
         </is>
       </c>
       <c r="D266" s="10" t="inlineStr">
         <is>
-          <t>Refaites la lecture.</t>
+          <t>Différez l’histoire.</t>
         </is>
       </c>
       <c r="E266" s="11" t="n"/>
@@ -6917,17 +6917,17 @@
       </c>
       <c r="B267" s="9" t="inlineStr">
         <is>
-          <t>footer.rights</t>
+          <t>footer.method[2]</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Take the reading again.</t>
         </is>
       </c>
       <c r="D267" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Refaites la lecture.</t>
         </is>
       </c>
       <c r="E267" s="11" t="n"/>
@@ -6941,17 +6941,17 @@
       </c>
       <c r="B268" s="9" t="inlineStr">
         <is>
-          <t>footer.pressLink</t>
+          <t>footer.rights</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="D268" s="10" t="inlineStr">
         <is>
-          <t>Presse</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="E268" s="11" t="n"/>
@@ -6965,17 +6965,17 @@
       </c>
       <c r="B269" s="9" t="inlineStr">
         <is>
-          <t>footer.contactLink</t>
+          <t>footer.pressLink</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D269" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E269" s="11" t="n"/>
@@ -6989,57 +6989,57 @@
       </c>
       <c r="B270" s="9" t="inlineStr">
         <is>
-          <t>footer.madeLine</t>
+          <t>footer.contactLink</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
         <is>
-          <t>Same life. Different instrument settings.</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D270" s="10" t="inlineStr">
         <is>
-          <t>Même vie. Instruments réglés autrement.</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E270" s="11" t="n"/>
       <c r="F270" s="11" t="n"/>
     </row>
-    <row r="271" ht="22" customHeight="1">
-      <c r="A271" s="7" t="inlineStr">
+    <row r="271" ht="30" customHeight="1">
+      <c r="A271" s="9" t="inlineStr">
+        <is>
+          <t>Foot of every page</t>
+        </is>
+      </c>
+      <c r="B271" s="9" t="inlineStr">
+        <is>
+          <t>footer.madeLine</t>
+        </is>
+      </c>
+      <c r="C271" s="10" t="inlineStr">
+        <is>
+          <t>Same life. Different instrument settings.</t>
+        </is>
+      </c>
+      <c r="D271" s="10" t="inlineStr">
+        <is>
+          <t>Même vie. Instruments réglés autrement.</t>
+        </is>
+      </c>
+      <c r="E271" s="11" t="n"/>
+      <c r="F271" s="11" t="n"/>
+    </row>
+    <row r="272" ht="22" customHeight="1">
+      <c r="A272" s="7" t="inlineStr">
         <is>
           <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
         </is>
       </c>
-      <c r="B271" s="8" t="n"/>
-      <c r="C271" s="8" t="n"/>
-      <c r="D271" s="8" t="n"/>
-      <c r="E271" s="8" t="n"/>
-      <c r="F271" s="8" t="n"/>
-    </row>
-    <row r="272" ht="30" customHeight="1">
-      <c r="A272" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B272" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mainLandmark</t>
-        </is>
-      </c>
-      <c r="C272" s="10" t="inlineStr">
-        <is>
-          <t>Main content</t>
-        </is>
-      </c>
-      <c r="D272" s="10" t="inlineStr">
-        <is>
-          <t>Contenu principal</t>
-        </is>
-      </c>
-      <c r="E272" s="11" t="n"/>
-      <c r="F272" s="11" t="n"/>
+      <c r="B272" s="8" t="n"/>
+      <c r="C272" s="8" t="n"/>
+      <c r="D272" s="8" t="n"/>
+      <c r="E272" s="8" t="n"/>
+      <c r="F272" s="8" t="n"/>
     </row>
     <row r="273" ht="30" customHeight="1">
       <c r="A273" s="9" t="inlineStr">
@@ -7049,17 +7049,17 @@
       </c>
       <c r="B273" s="9" t="inlineStr">
         <is>
-          <t>a11y.coverFigure</t>
+          <t>a11y.mainLandmark</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>Main content</t>
         </is>
       </c>
       <c r="D273" s="10" t="inlineStr">
         <is>
-          <t>Le livre</t>
+          <t>Contenu principal</t>
         </is>
       </c>
       <c r="E273" s="11" t="n"/>
@@ -7073,17 +7073,17 @@
       </c>
       <c r="B274" s="9" t="inlineStr">
         <is>
-          <t>a11y.languageSwitcher</t>
+          <t>a11y.coverFigure</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
         <is>
-          <t>Choose language</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D274" s="10" t="inlineStr">
         <is>
-          <t>Choisir la langue</t>
+          <t>Le livre</t>
         </is>
       </c>
       <c r="E274" s="11" t="n"/>
@@ -7097,17 +7097,17 @@
       </c>
       <c r="B275" s="9" t="inlineStr">
         <is>
-          <t>a11y.languageComing</t>
+          <t>a11y.languageSwitcher</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
         <is>
-          <t>edition to follow</t>
+          <t>Choose language</t>
         </is>
       </c>
       <c r="D275" s="10" t="inlineStr">
         <is>
-          <t>édition à venir</t>
+          <t>Choisir la langue</t>
         </is>
       </c>
       <c r="E275" s="11" t="n"/>
@@ -7121,17 +7121,17 @@
       </c>
       <c r="B276" s="9" t="inlineStr">
         <is>
-          <t>a11y.casesRegion</t>
+          <t>a11y.languageComing</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
         <is>
-          <t>Case evidence pages from the book</t>
+          <t>edition to follow</t>
         </is>
       </c>
       <c r="D276" s="10" t="inlineStr">
         <is>
-          <t>Pièces du dossier tirées du livre</t>
+          <t>édition à venir</t>
         </is>
       </c>
       <c r="E276" s="11" t="n"/>
@@ -7145,17 +7145,17 @@
       </c>
       <c r="B277" s="9" t="inlineStr">
         <is>
-          <t>a11y.bookOpening</t>
+          <t>a11y.casesRegion</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
         <is>
-          <t>The book, opening</t>
+          <t>Case evidence pages from the book</t>
         </is>
       </c>
       <c r="D277" s="10" t="inlineStr">
         <is>
-          <t>Le livre qui s’ouvre</t>
+          <t>Pièces du dossier tirées du livre</t>
         </is>
       </c>
       <c r="E277" s="11" t="n"/>
@@ -7169,17 +7169,17 @@
       </c>
       <c r="B278" s="9" t="inlineStr">
         <is>
-          <t>a11y.misreadingRegion</t>
+          <t>a11y.bookOpening</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
         <is>
-          <t>Page 10 of the book</t>
+          <t>The book, opening</t>
         </is>
       </c>
       <c r="D278" s="10" t="inlineStr">
         <is>
-          <t>Page 10 du livre</t>
+          <t>Le livre qui s’ouvre</t>
         </is>
       </c>
       <c r="E278" s="11" t="n"/>
@@ -7193,24 +7193,72 @@
       </c>
       <c r="B279" s="9" t="inlineStr">
         <is>
-          <t>a11y.mapRegion</t>
+          <t>a11y.misreadingRegion</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
         <is>
-          <t>A map of the book</t>
+          <t>Page 10 of the book</t>
         </is>
       </c>
       <c r="D279" s="10" t="inlineStr">
         <is>
-          <t>Une carte du livre</t>
+          <t>Page 10 du livre</t>
         </is>
       </c>
       <c r="E279" s="11" t="n"/>
       <c r="F279" s="11" t="n"/>
     </row>
+    <row r="280" ht="30" customHeight="1">
+      <c r="A280" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B280" s="9" t="inlineStr">
+        <is>
+          <t>a11y.mapRegion</t>
+        </is>
+      </c>
+      <c r="C280" s="10" t="inlineStr">
+        <is>
+          <t>A map of the book</t>
+        </is>
+      </c>
+      <c r="D280" s="10" t="inlineStr">
+        <is>
+          <t>Une carte du livre</t>
+        </is>
+      </c>
+      <c r="E280" s="11" t="n"/>
+      <c r="F280" s="11" t="n"/>
+    </row>
+    <row r="281" ht="30" customHeight="1">
+      <c r="A281" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B281" s="9" t="inlineStr">
+        <is>
+          <t>a11y.evidenceRegion</t>
+        </is>
+      </c>
+      <c r="C281" s="10" t="inlineStr">
+        <is>
+          <t>Confidence markers, page 13</t>
+        </is>
+      </c>
+      <c r="D281" s="10" t="inlineStr">
+        <is>
+          <t>Marqueurs de confiance, page 13</t>
+        </is>
+      </c>
+      <c r="E281" s="11" t="n"/>
+      <c r="F281" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F279"/>
+  <autoFilter ref="A1:F281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/State-Not-Situation-French-review.xlsx
+++ b/review/State-Not-Situation-French-review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="French review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'French review'!$A$1:$F$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'French review'!$A$1:$F$268</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2112,7 +2112,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>“YOU KNOW THE DAY” — PAGE 12, ABOVE THE THREE INSTRUCTIONS</t>
+          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
@@ -2124,22 +2124,22 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.eyebrow</t>
+          <t>reading.eyebrow</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>You know the day</t>
+          <t>Try something right now</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Vous connaissez cette journée</t>
+          <t>Essayez quelque chose tout de suite</t>
         </is>
       </c>
       <c r="E62" s="11" t="n"/>
@@ -2148,70 +2148,70 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.moreLabel</t>
+          <t>reading.lead</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>More from page 12</t>
+          <t>Whatever you are feeling as you read this sentence.</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Un autre passage de la page 12</t>
+          <t>Quoi que vous ressentiez en lisant cette phrase.</t>
         </is>
       </c>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
     </row>
-    <row r="64" ht="150" customHeight="1">
+    <row r="64" ht="30" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[0]</t>
+          <t>reading.steps[0]</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>The day I mean is the other kind. The day where nothing went wrong and everything felt off. It started before you noticed it starting. Somewhere between the alarm and the shower, between the shower and the kitchen, between the kitchen and the first sip of whatever you drink to become the person the morning requires. Something was already there. It felt more like texture. A drag in the limbs, a reluctance in the chest, a faint heaviness that sat behind your thoughts like rainy weather behind glass.</t>
+          <t>Check your jaw.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>La journée dont je parle, c’est l’autre. La journée où rien ne s’est mal passé et où tout clochait. Elle a commencé avant que vous ne remarquiez qu’elle commençait. Quelque part entre le réveil et la douche, entre la douche et la cuisine, entre la cuisine et la première gorgée de ce que vous buvez pour devenir la personne que le matin exige. Quelque chose était déjà là. On aurait plutôt dit une texture. Une pesanteur dans les membres, une réticence dans la poitrine, une légère lourdeur posée derrière vos pensées comme un jour de pluie derrière une vitre.</t>
+          <t>Observez votre mâchoire.</t>
         </is>
       </c>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="11" t="n"/>
     </row>
-    <row r="65" ht="60" customHeight="1">
+    <row r="65" ht="30" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[1]</t>
+          <t>reading.steps[1]</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>You have had this day. Everyone has had this day. You have had it dozens of times and you will have it again and each time the story will feel like the truth and each time the morning after will make the story dissolve.</t>
+          <t>Check your breath.</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Vous avez eu cette journée. Tout le monde a eu cette journée. Vous l’avez eue des dizaines de fois et vous l’aurez encore et chaque fois l’histoire aura l’air vraie et chaque fois le lendemain matin dissoudra l’histoire.</t>
+          <t>Observez votre respiration.</t>
         </is>
       </c>
       <c r="E65" s="11" t="n"/>
@@ -2220,62 +2220,74 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[2]</t>
+          <t>reading.steps[2]</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>The body spoke first. The mind explained second, and this explanation felt like the event.</t>
+          <t>Check your shoulders.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Le corps a parlé d’abord. L’esprit a expliqué ensuite, et cette explication est passée pour l’événement.</t>
+          <t>Observez vos épaules.</t>
         </is>
       </c>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
     </row>
-    <row r="67" ht="105" customHeight="1">
+    <row r="67" ht="30" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[3]</t>
+          <t>reading.result</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>This book is about that mistake. It is about that error as a daily, ambient, invisible feature of being alive in a body that is constantly producing signals, which your mind is constantly reading or misreading. Before any of that, before the science and the mechanism and the reason the instrument was miscalibrated yesterday, try something right now.</t>
+          <t>What you found is a reading.</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Ce livre parle de cette méprise. Il parle de cette erreur comme d’un aspect quotidien, ambiant, invisible de la vie dans un corps qui produit sans cesse des signaux, que votre esprit, sans cesse, lit ou lit de travers. Avant tout cela, avant la science et le mécanisme et la raison pour laquelle l’instrument était mal calibré hier, essayez quelque chose tout de suite.</t>
+          <t>Ce que vous avez trouvé, c’est une lecture.</t>
         </is>
       </c>
       <c r="E67" s="11" t="n"/>
       <c r="F67" s="11" t="n"/>
     </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>“Try something right now” — the three instructions, page 13</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>reading.afterResult</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Une lecture de l’instrument qui interprète tout ce qui vous entoure, en ce moment, y compris ces mots. La lecture est peut-être exacte. Peut-être pas. Vous ne pouvez pas le savoir tant que vous n’avez pas vu les réglages.</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="11" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
@@ -2285,89 +2297,77 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>reading.eyebrow</t>
+          <t>reading.question</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Try something right now</t>
+          <t>Is this the situation? Or is this the state?</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Essayez quelque chose tout de suite</t>
+          <t>Est-ce la situation ? Ou est-ce l’état ?</t>
         </is>
       </c>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>reading.lead</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>Whatever you are feeling as you read this sentence.</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>Quoi que vous ressentiez en lisant cette phrase.</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="n"/>
-      <c r="F70" s="11" t="n"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>THE BOOK — THE AUTHOR’S LINE, WHO IT IS FOR</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The book — the author’s line, who it is for</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[0]</t>
+          <t>book.eyebrow</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Check your jaw.</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Observez votre mâchoire.</t>
+          <t>Le livre</t>
         </is>
       </c>
       <c r="E71" s="11" t="n"/>
       <c r="F71" s="11" t="n"/>
     </row>
-    <row r="72" ht="30" customHeight="1">
+    <row r="72" ht="45" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The book — the author’s line, who it is for</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[1]</t>
+          <t>book.paragraphs[0]</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Check your breath.</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Observez votre respiration.</t>
+          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
         </is>
       </c>
       <c r="E72" s="11" t="n"/>
@@ -2376,130 +2376,130 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The book — the author’s line, who it is for</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[2]</t>
+          <t>book.readersEyebrow</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Check your shoulders.</t>
+          <t>Who it is for</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Observez vos épaules.</t>
+          <t>À qui il s’adresse</t>
         </is>
       </c>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
     </row>
-    <row r="74" ht="30" customHeight="1">
+    <row r="74" ht="75" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The book — the author’s line, who it is for</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>reading.result</t>
+          <t>book.readers</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>What you found is a reading.</t>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Ce que vous avez trouvé, c’est une lecture.</t>
+          <t>Pour quiconque a déjà été certain du sens d’une situation, puis a découvert qu’il se passait autre chose. Et pour les lecteurs qui s’intéressent à la psychologie de notre façon de remarquer, d’interpréter et de revoir le monde qui nous entoure.</t>
         </is>
       </c>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>reading.afterResult</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>Une lecture de l’instrument qui interprète tout ce qui vous entoure, en ce moment, y compris ces mots. La lecture est peut-être exacte. Peut-être pas. Vous ne pouvez pas le savoir tant que vous n’avez pas vu les réglages.</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="n"/>
-      <c r="F75" s="11" t="n"/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>reading.question</t>
+          <t>excerpt.eyebrow</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this the state?</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Est-ce la situation ? Ou est-ce l’état ?</t>
+          <t>Lire</t>
         </is>
       </c>
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="11" t="n"/>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>THE BOOK — THE PAGE 20 HEADING, THE AUTHOR’S ACCOUNT, WHO IT IS FOR</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.title</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Before the chapters</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Avant les chapitres</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n"/>
+      <c r="F77" s="11" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>book.eyebrow</t>
+          <t>excerpt.sectionLabel</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>The pilot</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Le livre</t>
+          <t>Le pilote</t>
         </is>
       </c>
       <c r="E78" s="11" t="n"/>
@@ -2508,22 +2508,22 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>book.heading</t>
+          <t>excerpt.runningHead</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Same morning. Same paragraph. Same Katrin. Different instrument settings.</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Même matin. Même paragraphe. Même Katrin. Instruments réglés autrement.</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="E79" s="11" t="n"/>
@@ -2532,70 +2532,70 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>book.headingSource</t>
+          <t>excerpt.cta</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>Read an extract</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>Lire un extrait</t>
         </is>
       </c>
       <c r="E80" s="11" t="n"/>
       <c r="F80" s="11" t="n"/>
     </row>
-    <row r="81" ht="135" customHeight="1">
+    <row r="81" ht="30" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>book.paragraphs[0]</t>
+          <t>excerpt.continueCta</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
+          <t>Continue reading</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Pendant seize jours, Katrin traverse des situations ordinaires où sa première lecture de ce qui se passe n’est pas toujours celle qui tient, à y regarder de plus près. Chaque chapitre suit l’un de ces moments jusque dans la psychologie qui le sous-tend, de l’attention et de la prédiction à la mémoire, à la menace, à l’incertitude et à l’inférence sociale. Le livre ne promet pas un meilleur instinct. Il demande ce qui devient possible quand nous apprenons d’où venait notre première lecture.</t>
+          <t>Lire la suite</t>
         </is>
       </c>
       <c r="E81" s="11" t="n"/>
       <c r="F81" s="11" t="n"/>
     </row>
-    <row r="82" ht="45" customHeight="1">
+    <row r="82" ht="30" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>book.paragraphs[1]</t>
+          <t>excerpt.back</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
+          <t>Retour au livre</t>
         </is>
       </c>
       <c r="E82" s="11" t="n"/>
@@ -2604,88 +2604,100 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>book.readersEyebrow</t>
+          <t>excerpt.readingModeLabel</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Who it is for</t>
+          <t>Reading mode</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>À qui il s’adresse</t>
+          <t>Mode lecture</t>
         </is>
       </c>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
     </row>
-    <row r="84" ht="75" customHeight="1">
+    <row r="84" ht="105" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>book.readersAnchor</t>
+          <t>excerpt.paragraphs[0]</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>This book does not replace professional support and it does not treat complex conditions as lifestyle problems. It works in the gap between fine and clinical, the space where most people live on most days.</t>
+          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Ce livre ne remplace pas l’aide d’un professionnel et il ne traite pas les troubles complexes comme des problèmes d’hygiène de vie. Il travaille dans l’écart entre « ça va » et « clinique », l’espace où la plupart des gens vivent la plupart des jours.</t>
+          <t>Le soir du 16 juillet 1999, un petit avion monomoteur décolla du New Jersey. Il faisait route vers Martha’s Vineyard. Le pilote avait assez d’expérience pour être sûr de lui, et assez peu pour se tromper sur ce que valait cette assurance. Il avait environ 300 heures de vol. Il n’avait pas terminé la formation qui l’aurait qualifié pour voler aux seuls instruments.</t>
         </is>
       </c>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
     </row>
-    <row r="85" ht="75" customHeight="1">
+    <row r="85" ht="225" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>book.readers</t>
+          <t>excerpt.paragraphs[1]</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Pour quiconque a déjà été certain du sens d’une situation, puis a découvert qu’il se passait autre chose. Et pour les lecteurs qui s’intéressent à la psychologie de notre façon de remarquer, d’interpréter et de revoir le monde qui nous entoure.</t>
+          <t>Le ciel était dégagé au départ, alors il en conclut qu’il n’avait pas besoin d’instruments. Le temps qu’il atteigne la côte, il ne l’était plus. Une brume s’était posée sur l’eau. Le genre de brume qui efface la limite entre la mer et le ciel si progressivement que vous ne remarquez pas que l’horizon a disparu, jusqu’au moment où vous le cherchez et où il n’est plus là. Au-dessus des terres, cela n’a pas d’importance. Il y a des lumières en dessous. Vous voyez des routes, des bâtiments, une géométrie qui dit à vos yeux où est le bas. Au large, la nuit, avec la brume posée sur la surface comme une seconde obscurité, il n’y a rien. Hors du cockpit, le monde devient un gris uniforme dans toutes les directions. Le haut ressemble au bas. Un léger virage donne la sensation d’un vol en palier. Une descente lente donne la sensation de tenir l’altitude.</t>
         </is>
       </c>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
+    <row r="86" ht="150" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.paragraphs[2]</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>L’oreille interne du pilote, l’organe qui dit au cerveau dans quel sens le corps est orienté dans l’espace, fonctionne en détectant les changements de mouvement. Quand vous entrez en virage, le liquide à l’intérieur de l’oreille se déplace, et le cerveau enregistre une rotation. Mais si le virage se maintient pendant quinze ou vingt secondes, le liquide de l’oreille interne se stabilise. Il ne bouge plus. Le cerveau, qui suit le mouvement et non la position, en conclut que le virage est terminé. Vous vous sentez en palier, mais vous ne l’êtes pas.</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="n"/>
+      <c r="F86" s="11" t="n"/>
+    </row>
+    <row r="87" ht="150" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2693,23 +2705,23 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>excerpt.eyebrow</t>
+          <t>excerpt.paragraphs[3]</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Lire</t>
+          <t>Quelque part au-dessus de l’eau sombre, l’avion s’engagea dans un léger virage à gauche. Les instruments du pilote, les cadrans du tableau de bord devant lui, indiquaient le virage. L’horizon artificiel, un petit cadran gyroscopique qui montre l’angle de l’appareil par rapport au sol, lui disait qu’il s’inclinait. L’altimètre lui disait qu’il descendait. L’indicateur de vitesse lui disait qu’il accélérait. Son corps lui disait autre chose. Son corps lui disait qu’il volait droit et en palier. Son corps sonnait juste. Ses instruments sonnaient faux. Il fit confiance à son corps.</t>
         </is>
       </c>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="11" t="n"/>
     </row>
-    <row r="88" ht="30" customHeight="1">
+    <row r="88" ht="120" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2717,23 +2729,23 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>excerpt.title</t>
+          <t>excerpt.paragraphs[4]</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Before the chapters</t>
+          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Avant les chapitres</t>
+          <t>Le virage se resserra. Le nez tomba. La vitesse augmenta. Dans les dernières secondes, l’avion descendait à plus de 4 700 pieds par minute, près d’un kilomètre et demi toutes les soixante secondes, dans une spirale de plus en plus serrée que les pilotes appellent, avec la précision sinistre d’un métier qui a donné un nom aux façons dont il perd les siens, une spirale de la mort. Il percuta l’eau à pleine vitesse. Lui et ses deux passagers furent tués sur le coup.</t>
         </is>
       </c>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
     </row>
-    <row r="89" ht="30" customHeight="1">
+    <row r="89" ht="135" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2741,23 +2753,23 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>excerpt.sectionLabel</t>
+          <t>excerpt.paragraphs[5]</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>The pilot</t>
+          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Le pilote</t>
+          <t>L’enquête ne releva aucune défaillance mécanique. Le moteur tournait. Les instruments fonctionnaient. Les données étaient là, sur le tableau de bord, à quinze centimètres de ses yeux, depuis le début, mais il ne les lut pas. Il lut son corps à la place. La consigne que la Federal Aviation Administration américaine donne aux pilotes qui se retrouvent dans cette situation tient en une phrase. C’est une consigne à prendre au pied de la lettre, et elle s’applique à votre vie aussi directement qu’à un cockpit :</t>
         </is>
       </c>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
     </row>
-    <row r="90" ht="30" customHeight="1">
+    <row r="90" ht="60" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2765,23 +2777,23 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>excerpt.runningHead</t>
+          <t>excerpt.paragraphs[6]</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>Le pilote s’appelait John F. Kennedy Jr. C’était le fils d’un président américain. On lui avait déconseillé de voler ce soir-là sans son instructeur. Il avait dit à son instructeur qu’il voulait le faire seul. Il avait trente-huit ans.</t>
         </is>
       </c>
       <c r="E90" s="11" t="n"/>
       <c r="F90" s="11" t="n"/>
     </row>
-    <row r="91" ht="30" customHeight="1">
+    <row r="91" ht="240" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2789,17 +2801,17 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>excerpt.cta</t>
+          <t>excerpt.paragraphs[7]</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Lire un extrait</t>
+          <t>Vous pilotez un corps qui produit des signaux, et votre esprit prend souvent ces signaux pour la vérité. Les signaux se trompent parfois autant que le système vestibulaire de l’oreille interne au-dessus de l’eau sombre. La fatigue qui se présente comme une question sur votre carrière. Le pic de caféine qui se présente comme de l’anxiété à propos d’un e-mail. Le manque de sucre dans le sang qui se présente comme la preuve que votre relation est en train de se défaire. Votre corps parle d’abord et votre esprit explique ensuite. L’explication, parce qu’elle arrive avec tout le poids de la conviction physique, la mâchoire serrée, le cœur qui bat vite, la chaleur derrière les oreilles, donne l’impression d’un savoir profond. Vous avez l’impression de lire la situation. Mais vous ne lisez que l’instrument qui lit la situation, et les réglages de l’instrument étaient faussés avant que la situation n’arrive. Ces instruments existent. Vous les avez. Le rythme cardiaque, la tension de la mâchoire, la profondeur de la respiration, la position des épaules, la vitesse de vos pensées. Ils produisent des données en ce moment même, pendant que vous lisez cette phrase. Mais le bulletin météo plein d’assurance que le corps établit sur le monde n’est qu’un brouillon.</t>
         </is>
       </c>
       <c r="E91" s="11" t="n"/>
@@ -2813,23 +2825,23 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>excerpt.continueCta</t>
+          <t>excerpt.quote</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Continue reading</t>
+          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Lire la suite</t>
+          <t>« ayez confiance en vos instruments et ne tenez aucun compte des signaux contradictoires que vous envoie votre corps. »</t>
         </is>
       </c>
       <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
     </row>
-    <row r="93" ht="30" customHeight="1">
+    <row r="93" ht="135" customHeight="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2837,17 +2849,17 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>excerpt.back</t>
+          <t>excerpt.closing</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Retour au livre</t>
+          <t>Ce livre parle de la même erreur à l’échelle de la cuisine. La version qui arrive tous les mardis. La version où votre corps écrit une histoire à propos d’un message, d’un silence, d’un regard, et où votre esprit retouche cette histoire sous la supervision de ce que votre corps ressent à ce moment-là. Personne ne meurt, mais des décisions se prennent. Des relations changent. Des jugements sur soi se forment. Et rien de tout cela n’avait à se passer ainsi, parce que les données étaient là depuis le début.</t>
         </is>
       </c>
       <c r="E93" s="11" t="n"/>
@@ -2861,23 +2873,23 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>excerpt.readingModeLabel</t>
+          <t>excerpt.closingSource</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Reading mode</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Mode lecture</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
     </row>
-    <row r="95" ht="105" customHeight="1">
+    <row r="95" ht="30" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2885,23 +2897,23 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[0]</t>
+          <t>excerpt.endNote</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
+          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Le soir du 16 juillet 1999, un petit avion monomoteur décolla du New Jersey. Il faisait route vers Martha’s Vineyard. Le pilote avait assez d’expérience pour être sûr de lui, et assez peu pour se tromper sur ce que valait cette assurance. Il avait environ 300 heures de vol. Il n’avait pas terminé la formation qui l’aurait qualifié pour voler aux seuls instruments.</t>
+          <t>Vient ensuite le chapitre zéro : Une journée qui aurait dû bien se passer.</t>
         </is>
       </c>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
     </row>
-    <row r="96" ht="225" customHeight="1">
+    <row r="96" ht="30" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2909,23 +2921,23 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[1]</t>
+          <t>excerpt.unavailable</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
+          <t>The extract in this language will follow.</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Le ciel était dégagé au départ, alors il en conclut qu’il n’avait pas besoin d’instruments. Le temps qu’il atteigne la côte, il ne l’était plus. Une brume s’était posée sur l’eau. Le genre de brume qui efface la limite entre la mer et le ciel si progressivement que vous ne remarquez pas que l’horizon a disparu, jusqu’au moment où vous le cherchez et où il n’est plus là. Au-dessus des terres, cela n’a pas d’importance. Il y a des lumières en dessous. Vous voyez des routes, des bâtiments, une géométrie qui dit à vos yeux où est le bas. Au large, la nuit, avec la brume posée sur la surface comme une seconde obscurité, il n’y a rien. Hors du cockpit, le monde devient un gris uniforme dans toutes les directions. Le haut ressemble au bas. Un léger virage donne la sensation d’un vol en palier. Une descente lente donne la sensation de tenir l’altitude.</t>
+          <t>L’extrait en français est à venir.</t>
         </is>
       </c>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
     </row>
-    <row r="97" ht="150" customHeight="1">
+    <row r="97" ht="30" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2933,23 +2945,23 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[2]</t>
+          <t>excerpt.folios[0]</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>L’oreille interne du pilote, l’organe qui dit au cerveau dans quel sens le corps est orienté dans l’espace, fonctionne en détectant les changements de mouvement. Quand vous entrez en virage, le liquide à l’intérieur de l’oreille se déplace, et le cerveau enregistre une rotation. Mais si le virage se maintient pendant quinze ou vingt secondes, le liquide de l’oreille interne se stabilise. Il ne bouge plus. Le cerveau, qui suit le mouvement et non la position, en conclut que le virage est terminé. Vous vous sentez en palier, mais vous ne l’êtes pas.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
     </row>
-    <row r="98" ht="150" customHeight="1">
+    <row r="98" ht="30" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2957,23 +2969,23 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[3]</t>
+          <t>excerpt.folios[1]</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Quelque part au-dessus de l’eau sombre, l’avion s’engagea dans un léger virage à gauche. Les instruments du pilote, les cadrans du tableau de bord devant lui, indiquaient le virage. L’horizon artificiel, un petit cadran gyroscopique qui montre l’angle de l’appareil par rapport au sol, lui disait qu’il s’inclinait. L’altimètre lui disait qu’il descendait. L’indicateur de vitesse lui disait qu’il accélérait. Son corps lui disait autre chose. Son corps lui disait qu’il volait droit et en palier. Son corps sonnait juste. Ses instruments sonnaient faux. Il fit confiance à son corps.</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
     </row>
-    <row r="99" ht="120" customHeight="1">
+    <row r="99" ht="30" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2981,89 +2993,77 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[4]</t>
+          <t>excerpt.folios[2]</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Le virage se resserra. Le nez tomba. La vitesse augmenta. Dans les dernières secondes, l’avion descendait à plus de 4 700 pieds par minute, près d’un kilomètre et demi toutes les soixante secondes, dans une spirale de plus en plus serrée que les pilotes appellent, avec la précision sinistre d’un métier qui a donné un nom aux façons dont il perd les siens, une spirale de la mort. Il percuta l’eau à pleine vitesse. Lui et ses deux passagers furent tués sur le coup.</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
     </row>
-    <row r="100" ht="135" customHeight="1">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>excerpt.paragraphs[5]</t>
-        </is>
-      </c>
-      <c r="C100" s="10" t="inlineStr">
-        <is>
-          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>L’enquête ne releva aucune défaillance mécanique. Le moteur tournait. Les instruments fonctionnaient. Les données étaient là, sur le tableau de bord, à quinze centimètres de ses yeux, depuis le début, mais il ne les lut pas. Il lut son corps à la place. La consigne que la Federal Aviation Administration américaine donne aux pilotes qui se retrouvent dans cette situation tient en une phrase. C’est une consigne à prendre au pied de la lettre, et elle s’applique à votre vie aussi directement qu’à un cockpit :</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="n"/>
-      <c r="F100" s="11" t="n"/>
-    </row>
-    <row r="101" ht="60" customHeight="1">
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>CASE EVIDENCE CARDS</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[6]</t>
+          <t>cases.eyebrow</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
+          <t>Case evidence</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Le pilote s’appelait John F. Kennedy Jr. C’était le fils d’un président américain. On lui avait déconseillé de voler ce soir-là sans son instructeur. Il avait dit à son instructeur qu’il voulait le faire seul. Il avait trente-huit ans.</t>
+          <t>Pièces du dossier</t>
         </is>
       </c>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
     </row>
-    <row r="102" ht="240" customHeight="1">
+    <row r="102" ht="30" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[7]</t>
+          <t>cases.pageLabel</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Vous pilotez un corps qui produit des signaux, et votre esprit prend souvent ces signaux pour la vérité. Les signaux se trompent parfois autant que le système vestibulaire de l’oreille interne au-dessus de l’eau sombre. La fatigue qui se présente comme une question sur votre carrière. Le pic de caféine qui se présente comme de l’anxiété à propos d’un e-mail. Le manque de sucre dans le sang qui se présente comme la preuve que votre relation est en train de se défaire. Votre corps parle d’abord et votre esprit explique ensuite. L’explication, parce qu’elle arrive avec tout le poids de la conviction physique, la mâchoire serrée, le cœur qui bat vite, la chaleur derrière les oreilles, donne l’impression d’un savoir profond. Vous avez l’impression de lire la situation. Mais vous ne lisez que l’instrument qui lit la situation, et les réglages de l’instrument étaient faussés avant que la situation n’arrive. Ces instruments existent. Vous les avez. Le rythme cardiaque, la tension de la mâchoire, la profondeur de la respiration, la position des épaules, la vitesse de vos pensées. Ils produisent des données en ce moment même, pendant que vous lisez cette phrase. Mais le bulletin météo plein d’assurance que le corps établit sur le monde n’est qu’un brouillon.</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="E102" s="11" t="n"/>
@@ -3072,46 +3072,46 @@
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>excerpt.quote</t>
+          <t>cases.items[0].quote</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
+          <t>“Something is off.”</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>« ayez confiance en vos instruments et ne tenez aucun compte des signaux contradictoires que vous envoie votre corps. »</t>
+          <t>« Quelque chose cloche. »</t>
         </is>
       </c>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
     </row>
-    <row r="104" ht="135" customHeight="1">
+    <row r="104" ht="30" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closing</t>
+          <t>cases.items[0].inputLabel</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Ce livre parle de la même erreur à l’échelle de la cuisine. La version qui arrive tous les mardis. La version où votre corps écrit une histoire à propos d’un message, d’un silence, d’un regard, et où votre esprit retouche cette histoire sous la supervision de ce que votre corps ressent à ce moment-là. Personne ne meurt, mais des décisions se prennent. Des relations changent. Des jugements sur soi se forment. Et rien de tout cela n’avait à se passer ainsi, parce que les données étaient là depuis le début.</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E104" s="11" t="n"/>
@@ -3120,22 +3120,22 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closingSource</t>
+          <t>cases.items[0].input</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>Two minutes before the alarm.</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>Deux minutes avant le réveil.</t>
         </is>
       </c>
       <c r="E105" s="11" t="n"/>
@@ -3144,22 +3144,22 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>excerpt.endNote</t>
+          <t>cases.items[0].verifiedLabel</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
+          <t>Verified event</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Vient ensuite le chapitre zéro : Une journée qui aurait dû bien se passer.</t>
+          <t>Événement vérifié</t>
         </is>
       </c>
       <c r="E106" s="11" t="n"/>
@@ -3168,22 +3168,22 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>excerpt.unavailable</t>
+          <t>cases.items[0].verified</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>The extract in this language will follow.</t>
+          <t>Nothing has happened.</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>L’extrait en français est à venir.</t>
+          <t>Il ne s’est rien passé.</t>
         </is>
       </c>
       <c r="E107" s="11" t="n"/>
@@ -3192,22 +3192,22 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[0]</t>
+          <t>cases.items[1].quote</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>“ok.”</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>« ok. »</t>
         </is>
       </c>
       <c r="E108" s="11" t="n"/>
@@ -3216,22 +3216,22 @@
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[1]</t>
+          <t>cases.items[1].inputLabel</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E109" s="11" t="n"/>
@@ -3240,38 +3240,50 @@
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[2]</t>
+          <t>cases.items[1].input</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Two letters. One full stop.</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Deux lettres. Un point.</t>
         </is>
       </c>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
     </row>
-    <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>CASE EVIDENCE CARDS</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="n"/>
-      <c r="C111" s="8" t="n"/>
-      <c r="D111" s="8" t="n"/>
-      <c r="E111" s="8" t="n"/>
-      <c r="F111" s="8" t="n"/>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>Case evidence cards</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>cases.items[1].verifiedLabel</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Verified tone</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>Ton vérifié</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n"/>
+      <c r="F111" s="11" t="n"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
@@ -3281,17 +3293,17 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>cases.eyebrow</t>
+          <t>cases.items[1].verified</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Case evidence</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Pièces du dossier</t>
+          <t>Aucun.</t>
         </is>
       </c>
       <c r="E112" s="11" t="n"/>
@@ -3305,17 +3317,17 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>cases.pageLabel</t>
+          <t>cases.items[2].quote</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>“Something is wrong with my life.”</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>« Quelque chose ne va pas dans ma vie. »</t>
         </is>
       </c>
       <c r="E113" s="11" t="n"/>
@@ -3329,17 +3341,17 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].quote</t>
+          <t>cases.items[2].inputLabel</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>“Something is off.”</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>« Quelque chose cloche. »</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E114" s="11" t="n"/>
@@ -3353,17 +3365,17 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].inputLabel</t>
+          <t>cases.items[2].input</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Six ordinary events. One depleted day.</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Six événements ordinaires. Une journée à plat.</t>
         </is>
       </c>
       <c r="E115" s="11" t="n"/>
@@ -3377,17 +3389,17 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].input</t>
+          <t>cases.items[2].verifiedLabel</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Two minutes before the alarm.</t>
+          <t>Verified crisis</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Deux minutes avant le réveil.</t>
+          <t>Crise vérifiée</t>
         </is>
       </c>
       <c r="E116" s="11" t="n"/>
@@ -3401,17 +3413,17 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verifiedLabel</t>
+          <t>cases.items[2].verified</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Verified event</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Événement vérifié</t>
+          <t>Aucune.</t>
         </is>
       </c>
       <c r="E117" s="11" t="n"/>
@@ -3425,17 +3437,17 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verified</t>
+          <t>cases.items[3].quote</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Nothing has happened.</t>
+          <t>“This is state, not situation.”</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Il ne s’est rien passé.</t>
+          <t>« C’est l’état, pas la situation. »</t>
         </is>
       </c>
       <c r="E118" s="11" t="n"/>
@@ -3449,17 +3461,17 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].quote</t>
+          <t>cases.items[3].inputLabel</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>“ok.”</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>« ok. »</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E119" s="11" t="n"/>
@@ -3473,17 +3485,17 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].inputLabel</t>
+          <t>cases.items[3].input</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Low fuel. Dead light. A sound on grit.</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Réservoir bas. Néon mort. Un bruit sur le gravier.</t>
         </is>
       </c>
       <c r="E120" s="11" t="n"/>
@@ -3497,17 +3509,17 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].input</t>
+          <t>cases.items[3].verifiedLabel</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Two letters. One full stop.</t>
+          <t>Verified threat</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Deux lettres. Un point.</t>
+          <t>Menace vérifiée</t>
         </is>
       </c>
       <c r="E121" s="11" t="n"/>
@@ -3521,17 +3533,17 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verifiedLabel</t>
+          <t>cases.items[3].verified</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Verified tone</t>
+          <t>Not yet visible.</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Ton vérifié</t>
+          <t>Pas encore visible.</t>
         </is>
       </c>
       <c r="E122" s="11" t="n"/>
@@ -3545,17 +3557,17 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verified</t>
+          <t>cases.closing</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>It said I am failing; the data was I am tired.</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>Aucun.</t>
+          <t>Ça disait je suis en train d’échouer ; les données, c’était je suis fatiguée.</t>
         </is>
       </c>
       <c r="E123" s="11" t="n"/>
@@ -3569,65 +3581,53 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].quote</t>
+          <t>cases.closingSource</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>“Something is wrong with my life.”</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>« Quelque chose ne va pas dans ma vie. »</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
     </row>
-    <row r="125" ht="30" customHeight="1">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>cases.items[2].inputLabel</t>
-        </is>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="D125" s="10" t="inlineStr">
-        <is>
-          <t>Entrée</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="n"/>
-      <c r="F125" s="11" t="n"/>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].input</t>
+          <t>listen.eyebrow</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Six ordinary events. One depleted day.</t>
+          <t>Listen</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Six événements ordinaires. Une journée à plat.</t>
+          <t>Écouter</t>
         </is>
       </c>
       <c r="E126" s="11" t="n"/>
@@ -3636,22 +3636,22 @@
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verifiedLabel</t>
+          <t>listen.title</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Verified crisis</t>
+          <t>Listen to an extract</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Crise vérifiée</t>
+          <t>Écouter un extrait</t>
         </is>
       </c>
       <c r="E127" s="11" t="n"/>
@@ -3660,22 +3660,22 @@
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verified</t>
+          <t>listen.subtitle</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Read by the author</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Aucune.</t>
+          <t>Lu par l’autrice</t>
         </is>
       </c>
       <c r="E128" s="11" t="n"/>
@@ -3684,22 +3684,22 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].quote</t>
+          <t>listen.play</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>“This is state, not situation.”</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>« C’est l’état, pas la situation. »</t>
+          <t>Écouter</t>
         </is>
       </c>
       <c r="E129" s="11" t="n"/>
@@ -3708,22 +3708,22 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].inputLabel</t>
+          <t>listen.pause</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="E130" s="11" t="n"/>
@@ -3732,22 +3732,22 @@
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].input</t>
+          <t>listen.progress</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Low fuel. Dead light. A sound on grit.</t>
+          <t>Playback position</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Réservoir bas. Néon mort. Un bruit sur le gravier.</t>
+          <t>Position dans l’enregistrement</t>
         </is>
       </c>
       <c r="E131" s="11" t="n"/>
@@ -3756,22 +3756,22 @@
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verifiedLabel</t>
+          <t>listen.elapsed</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Verified threat</t>
+          <t>Elapsed</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Menace vérifiée</t>
+          <t>Écoulé</t>
         </is>
       </c>
       <c r="E132" s="11" t="n"/>
@@ -3780,22 +3780,22 @@
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verified</t>
+          <t>listen.duration</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Not yet visible.</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>Pas encore visible.</t>
+          <t>Durée</t>
         </is>
       </c>
       <c r="E133" s="11" t="n"/>
@@ -3804,82 +3804,82 @@
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>cases.closing</t>
+          <t>listen.unavailable</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>It said I am failing; the data was I am tired.</t>
+          <t>The recording will be added here.</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Ça disait je suis en train d’échouer ; les données, c’était je suis fatiguée.</t>
+          <t>L’enregistrement sera ajouté ici.</t>
         </is>
       </c>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
     </row>
-    <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="inlineStr">
-        <is>
-          <t>cases.closingSource</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>Page 20</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>Page 20</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="n"/>
-      <c r="F135" s="11" t="n"/>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="n"/>
-      <c r="C136" s="8" t="n"/>
-      <c r="D136" s="8" t="n"/>
-      <c r="E136" s="8" t="n"/>
-      <c r="F136" s="8" t="n"/>
-    </row>
-    <row r="137" ht="30" customHeight="1">
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>THE INVESTIGATION (PAGE 11), “BEFORE WE BEGIN” (PAGE 13 MARKERS), THE THREE SYSTEMS, PAGE 226</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n"/>
+      <c r="C135" s="8" t="n"/>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="8" t="n"/>
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>map.eyebrow</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>A map of the book</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>Une carte du livre</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="n"/>
+      <c r="F136" s="11" t="n"/>
+    </row>
+    <row r="137" ht="90" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>listen.eyebrow</t>
+          <t>map.sortingTool</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Écouter</t>
+          <t>Les chapitres qui suivent sont organisés autour de trois systèmes qui règlent le poids que prennent les signaux de votre corps avant que votre esprit ne construise une histoire. Ce ne sont pas des régions du cerveau ni des voies neuronales. C’est un outil de tri, une façon de poser trois questions quand tout semble aller de travers en même temps.</t>
         </is>
       </c>
       <c r="E137" s="11" t="n"/>
@@ -3888,46 +3888,46 @@
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>listen.title</t>
+          <t>map.loops[0].name</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Listen to an extract</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Écouter un extrait</t>
+          <t>Temps</t>
         </is>
       </c>
       <c r="E138" s="11" t="n"/>
       <c r="F138" s="11" t="n"/>
     </row>
-    <row r="139" ht="30" customHeight="1">
+    <row r="139" ht="45" customHeight="1">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>listen.subtitle</t>
+          <t>map.loops[0].body</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Read by the author</t>
+          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Lu par l’autrice</t>
+          <t>Sommeil, alimentation, caféine, phase circadienne, récupération. Quand le rythme est décalé, la sensibilité de base augmente. Le même monde paraît plus dur.</t>
         </is>
       </c>
       <c r="E139" s="11" t="n"/>
@@ -3936,46 +3936,46 @@
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>listen.play</t>
+          <t>map.loops[1].name</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Écouter</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="E140" s="11" t="n"/>
       <c r="F140" s="11" t="n"/>
     </row>
-    <row r="141" ht="30" customHeight="1">
+    <row r="141" ht="60" customHeight="1">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>listen.pause</t>
+          <t>map.loops[1].body</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Le système qui suit la récompense, la nouveauté et le prochain déclencheur. Quand il est accaparé, l’attention se resserre sur ce qu’il y a de moins exigeant à portée de main, et le travail exigeant paraît difficile.</t>
         </is>
       </c>
       <c r="E141" s="11" t="n"/>
@@ -3984,46 +3984,46 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>listen.progress</t>
+          <t>map.loops[2].name</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Playback position</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Position dans l’enregistrement</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="E142" s="11" t="n"/>
       <c r="F142" s="11" t="n"/>
     </row>
-    <row r="143" ht="30" customHeight="1">
+    <row r="143" ht="75" customHeight="1">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>listen.elapsed</t>
+          <t>map.loops[2].body</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Elapsed</t>
+          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>Écoulé</t>
+          <t>Le système qui surveille la menace, et surtout la menace sociale. Des choses comme l’évaluation sociale, l’exclusion, l’ambiguïté, le statut. Il est rapide, il est ancien, et il penche du côté des fausses alertes. Il produit des interprétations qui ressemblent à des faits.</t>
         </is>
       </c>
       <c r="E143" s="11" t="n"/>
@@ -4032,130 +4032,142 @@
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>listen.duration</t>
+          <t>map.evidenceEyebrow</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Before we begin</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>Durée</t>
+          <t>Avant de commencer</t>
         </is>
       </c>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
     </row>
-    <row r="145" ht="30" customHeight="1">
+    <row r="145" ht="120" customHeight="1">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>listen.unavailable</t>
+          <t>map.evidenceIntro</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>The recording will be added here.</t>
+          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>L’enregistrement sera ajouté ici.</t>
+          <t>Ce livre avance des affirmations sur le cerveau et sur le corps, et ces affirmations ne sont pas toutes également étayées. Certaines s’appuient sur des décennies de recherches répliquées. Certaines s’appuient sur des résultats plus récents, prometteurs mais pas encore consolidés. Certaines sont des prolongements plausibles d’une science établie, qui n’ont pas été testés directement sous la forme précise que décrit ce livre. Vous devriez savoir lesquelles sont lesquelles.</t>
         </is>
       </c>
       <c r="E145" s="11" t="n"/>
       <c r="F145" s="11" t="n"/>
     </row>
-    <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>“BEFORE WE BEGIN” (PAGE 13 MARKERS) AND THE MAP — THE THREE SYSTEMS, THE SIXTEEN CHAPTERS, PAGE 226</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="8" t="n"/>
-      <c r="D146" s="8" t="n"/>
-      <c r="E146" s="8" t="n"/>
-      <c r="F146" s="8" t="n"/>
+    <row r="146" ht="180" customHeight="1">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>map.evidenceMarkers</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>Tout au long du livre, les affirmations scientifiques portent un marqueur de confiance. Quand un résultat est solidement étayé et répliqué, vous verrez un repère indiquant un niveau de preuve élevé, sous la forme d’un pouls rouge profond dans la marge. Quand les preuves vont dans le sens de l’affirmation mais restent incomplètes, le niveau de preuve est noté moyen, avec un pouls orange. Quand une affirmation est une hypothèse plausible qui demande des tests plus poussés, elle est marquée faible, en gris délavé. Ces marqueurs existent parce que le risque que court ce livre est celui-là même qu’il décrit. Il ne veut pas traiter une histoire plausible comme une vérité établie. Ces marqueurs sont un frein à cela.</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="n"/>
+      <c r="F146" s="11" t="n"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>map.eyebrow</t>
+          <t>map.grades[0].label</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>A map of the book</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>Une carte du livre</t>
+          <t>Élevé</t>
         </is>
       </c>
       <c r="E147" s="11" t="n"/>
       <c r="F147" s="11" t="n"/>
     </row>
-    <row r="148" ht="90" customHeight="1">
+    <row r="148" ht="30" customHeight="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>map.systemsIntro</t>
+          <t>map.grades[1].label</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Three systems ran through Katrin’s morning. Time started at 06:38 and never stopped. Attention took the phone at 06:52. Safety wrote the email’s meaning at 07:25. She can name none of them. The only thing she can name is David, and David is the smallest part of it.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>Trois systèmes ont tourné pendant toute la matinée de Katrin. Le Temps a démarré à 06:38 et ne s’est jamais arrêté. L’Attention a pris le téléphone à 06:52. La Sécurité a écrit le sens de l’e-mail à 07:25. Elle ne peut en nommer aucun. La seule chose qu’elle peut nommer, c’est David, et David en est la plus petite part.</t>
+          <t>Moyen</t>
         </is>
       </c>
       <c r="E148" s="11" t="n"/>
       <c r="F148" s="11" t="n"/>
     </row>
-    <row r="149" ht="90" customHeight="1">
+    <row r="149" ht="30" customHeight="1">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>map.sortingTool</t>
+          <t>map.grades[2].label</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Les chapitres qui suivent sont organisés autour de trois systèmes qui règlent le poids que prennent les signaux de votre corps avant que votre esprit ne construise une histoire. Ce ne sont pas des régions du cerveau ni des voies neuronales. C’est un outil de tri, une façon de poser trois questions quand tout semble aller de travers en même temps.</t>
+          <t>Faible</t>
         </is>
       </c>
       <c r="E149" s="11" t="n"/>
@@ -4164,46 +4176,46 @@
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].name</t>
+          <t>map.investigationTitle</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>The Investigation</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>Temps</t>
+          <t>L’enquête</t>
         </is>
       </c>
       <c r="E150" s="11" t="n"/>
       <c r="F150" s="11" t="n"/>
     </row>
-    <row r="151" ht="45" customHeight="1">
+    <row r="151" ht="30" customHeight="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].body</t>
+          <t>map.mapLine</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>Sommeil, alimentation, caféine, phase circadienne, récupération. Quand le rythme est décalé, la sensibilité de base augmente. Le même monde paraît plus dur.</t>
+          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
         </is>
       </c>
       <c r="E151" s="11" t="n"/>
@@ -4212,46 +4224,46 @@
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].name</t>
+          <t>map.pageColumn</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="E152" s="11" t="n"/>
       <c r="F152" s="11" t="n"/>
     </row>
-    <row r="153" ht="60" customHeight="1">
+    <row r="153" ht="30" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].body</t>
+          <t>map.chapters[0].title</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
+          <t>A Day That Should Have Been Fine</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Le système qui suit la récompense, la nouveauté et le prochain déclencheur. Quand il est accaparé, l’attention se resserre sur ce qu’il y a de moins exigeant à portée de main, et le travail exigeant paraît difficile.</t>
+          <t>Une journée qui aurait dû bien se passer</t>
         </is>
       </c>
       <c r="E153" s="11" t="n"/>
@@ -4260,46 +4272,46 @@
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].name</t>
+          <t>map.chapters[1].title</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>The Radar Was Right</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Le radar avait raison</t>
         </is>
       </c>
       <c r="E154" s="11" t="n"/>
       <c r="F154" s="11" t="n"/>
     </row>
-    <row r="155" ht="75" customHeight="1">
+    <row r="155" ht="30" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].body</t>
+          <t>map.chapters[2].title</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
+          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Le système qui surveille la menace, et surtout la menace sociale. Des choses comme l’évaluation sociale, l’exclusion, l’ambiguïté, le statut. Il est rapide, il est ancien, et il penche du côté des fausses alertes. Il produit des interprétations qui ressemblent à des faits.</t>
+          <t>Pourquoi le manque de sommeil fait paraître hostile ce qui est neutre</t>
         </is>
       </c>
       <c r="E155" s="11" t="n"/>
@@ -4308,70 +4320,70 @@
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceEyebrow</t>
+          <t>map.chapters[3].title</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>Before we begin</t>
+          <t>The Relief That Becomes Itch</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Avant de commencer</t>
+          <t>Le soulagement qui tourne à la démangeaison</t>
         </is>
       </c>
       <c r="E156" s="11" t="n"/>
       <c r="F156" s="11" t="n"/>
     </row>
-    <row r="157" ht="120" customHeight="1">
+    <row r="157" ht="30" customHeight="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceIntro</t>
+          <t>map.chapters[4].title</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
+          <t>The Predictable Cue</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Ce livre avance des affirmations sur le cerveau et sur le corps, et ces affirmations ne sont pas toutes également étayées. Certaines s’appuient sur des décennies de recherches répliquées. Certaines s’appuient sur des résultats plus récents, prometteurs mais pas encore consolidés. Certaines sont des prolongements plausibles d’une science établie, qui n’ont pas été testés directement sous la forme précise que décrit ce livre. Vous devriez savoir lesquelles sont lesquelles.</t>
+          <t>Le déclencheur prévisible</t>
         </is>
       </c>
       <c r="E157" s="11" t="n"/>
       <c r="F157" s="11" t="n"/>
     </row>
-    <row r="158" ht="180" customHeight="1">
+    <row r="158" ht="30" customHeight="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceMarkers</t>
+          <t>map.chapters[5].title</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
+          <t>Why Evenings Stretch and Mornings Shrink</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>Tout au long du livre, les affirmations scientifiques portent un marqueur de confiance. Quand un résultat est solidement étayé et répliqué, vous verrez un repère indiquant un niveau de preuve élevé, sous la forme d’un pouls rouge profond dans la marge. Quand les preuves vont dans le sens de l’affirmation mais restent incomplètes, le niveau de preuve est noté moyen, avec un pouls orange. Quand une affirmation est une hypothèse plausible qui demande des tests plus poussés, elle est marquée faible, en gris délavé. Ces marqueurs existent parce que le risque que court ce livre est celui-là même qu’il décrit. Il ne veut pas traiter une histoire plausible comme une vérité établie. Ces marqueurs sont un frein à cela.</t>
+          <t>Pourquoi les soirées s’étirent et les matins rétrécissent</t>
         </is>
       </c>
       <c r="E158" s="11" t="n"/>
@@ -4380,22 +4392,22 @@
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>map.grades[0].label</t>
+          <t>map.chapters[6].title</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Why Rest Doesn’t Always Restore</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>Élevé</t>
+          <t>Pourquoi le repos ne ressource pas toujours</t>
         </is>
       </c>
       <c r="E159" s="11" t="n"/>
@@ -4404,22 +4416,22 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>map.grades[1].label</t>
+          <t>map.chapters[7].title</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Why You Cannot Start the Thing That Matters</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Pourquoi vous n’arrivez pas à commencer ce qui compte</t>
         </is>
       </c>
       <c r="E160" s="11" t="n"/>
@@ -4428,22 +4440,22 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>map.grades[2].label</t>
+          <t>map.chapters[8].title</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>The Open File</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>Faible</t>
+          <t>Le dossier ouvert</t>
         </is>
       </c>
       <c r="E161" s="11" t="n"/>
@@ -4452,22 +4464,22 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>map.investigationTitle</t>
+          <t>map.chapters[9].title</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>The Investigation</t>
+          <t>Two Nervous Systems Walk Into a Kitchen</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>L’enquête</t>
+          <t>Deux systèmes nerveux entrent dans une cuisine</t>
         </is>
       </c>
       <c r="E162" s="11" t="n"/>
@@ -4476,22 +4488,22 @@
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>map.mapLine</t>
+          <t>map.chapters[10].title</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>The Argument That Was Tuesday</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
+          <t>La dispute qui était mardi</t>
         </is>
       </c>
       <c r="E163" s="11" t="n"/>
@@ -4500,22 +4512,22 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>map.pageColumn</t>
+          <t>map.chapters[11].title</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>The Thursday That Was Wednesday Night</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Le jeudi qui était mercredi soir</t>
         </is>
       </c>
       <c r="E164" s="11" t="n"/>
@@ -4524,22 +4536,22 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[0].title</t>
+          <t>map.chapters[12].title</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>A Day That Should Have Been Fine</t>
+          <t>The Clean Panel</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Une journée qui aurait dû bien se passer</t>
+          <t>Le tableau de bord au vert</t>
         </is>
       </c>
       <c r="E165" s="11" t="n"/>
@@ -4548,22 +4560,22 @@
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[1].title</t>
+          <t>map.chapters[13].title</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>The Radar Was Right</t>
+          <t>The Time the Body Was Right</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>Le radar avait raison</t>
+          <t>La fois où le corps avait raison</t>
         </is>
       </c>
       <c r="E166" s="11" t="n"/>
@@ -4572,22 +4584,22 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[2].title</t>
+          <t>map.chapters[14].title</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
+          <t>Not About Me</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi le manque de sommeil fait paraître hostile ce qui est neutre</t>
+          <t>Rien à voir avec moi</t>
         </is>
       </c>
       <c r="E167" s="11" t="n"/>
@@ -4596,22 +4608,22 @@
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[3].title</t>
+          <t>map.chapters[15].title</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>The Relief That Becomes Itch</t>
+          <t>The Forecast</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>Le soulagement qui tourne à la démangeaison</t>
+          <t>La prévision</t>
         </is>
       </c>
       <c r="E168" s="11" t="n"/>
@@ -4620,46 +4632,46 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[4].title</t>
+          <t>map.mapFooter</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>The Predictable Cue</t>
+          <t>The Scientific Heartbeat follows the chapters.</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>Le déclencheur prévisible</t>
+          <t>Le pouls scientifique suit les chapitres.</t>
         </is>
       </c>
       <c r="E169" s="11" t="n"/>
       <c r="F169" s="11" t="n"/>
     </row>
-    <row r="170" ht="30" customHeight="1">
+    <row r="170" ht="75" customHeight="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[5].title</t>
+          <t>map.heartbeat[0]</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>Why Evenings Stretch and Mornings Shrink</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi les soirées s’étirent et les matins rétrécissent</t>
+          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
         </is>
       </c>
       <c r="E170" s="11" t="n"/>
@@ -4668,22 +4680,22 @@
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[6].title</t>
+          <t>map.heartbeat[1]</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Why Rest Doesn’t Always Restore</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi le repos ne ressource pas toujours</t>
+          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
         </is>
       </c>
       <c r="E171" s="11" t="n"/>
@@ -4692,70 +4704,58 @@
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[7].title</t>
+          <t>map.heartbeatSource</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>Why You Cannot Start the Thing That Matters</t>
+          <t>Page 226</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi vous n’arrivez pas à commencer ce qui compte</t>
+          <t>Page 226</t>
         </is>
       </c>
       <c r="E172" s="11" t="n"/>
       <c r="F172" s="11" t="n"/>
     </row>
-    <row r="173" ht="30" customHeight="1">
-      <c r="A173" s="9" t="inlineStr">
-        <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
-        </is>
-      </c>
-      <c r="B173" s="9" t="inlineStr">
-        <is>
-          <t>map.chapters[8].title</t>
-        </is>
-      </c>
-      <c r="C173" s="10" t="inlineStr">
-        <is>
-          <t>The Open File</t>
-        </is>
-      </c>
-      <c r="D173" s="10" t="inlineStr">
-        <is>
-          <t>Le dossier ouvert</t>
-        </is>
-      </c>
-      <c r="E173" s="11" t="n"/>
-      <c r="F173" s="11" t="n"/>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>ABOUT THE AUTHOR</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="n"/>
+      <c r="C173" s="8" t="n"/>
+      <c r="D173" s="8" t="n"/>
+      <c r="E173" s="8" t="n"/>
+      <c r="F173" s="8" t="n"/>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[9].title</t>
+          <t>author.eyebrow</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>Two Nervous Systems Walk Into a Kitchen</t>
+          <t>The author</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>Deux systèmes nerveux entrent dans une cuisine</t>
+          <t>L’autrice</t>
         </is>
       </c>
       <c r="E174" s="11" t="n"/>
@@ -4764,22 +4764,22 @@
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[10].title</t>
+          <t>author.title</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>The Argument That Was Tuesday</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>La dispute qui était mardi</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E175" s="11" t="n"/>
@@ -4788,22 +4788,22 @@
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[11].title</t>
+          <t>author.photoAlt</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>The Thursday That Was Wednesday Night</t>
+          <t>Ivana Budišin, photographed against a dark grey background.</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>Le jeudi qui était mercredi soir</t>
+          <t>Ivana Budišin, photographiée sur fond gris foncé.</t>
         </is>
       </c>
       <c r="E176" s="11" t="n"/>
@@ -4812,22 +4812,22 @@
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[12].title</t>
+          <t>author.photoPlaceholder</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>The Clean Panel</t>
+          <t>Author photograph to follow</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>Le tableau de bord au vert</t>
+          <t>Photographie de l’autrice à venir</t>
         </is>
       </c>
       <c r="E177" s="11" t="n"/>
@@ -4836,22 +4836,22 @@
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[13].title</t>
+          <t>author.bio</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>The Time the Body Was Right</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>La fois où le corps avait raison</t>
+          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
         </is>
       </c>
       <c r="E178" s="11" t="n"/>
@@ -4860,22 +4860,22 @@
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[14].title</t>
+          <t>author.websiteLabel</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Not About Me</t>
+          <t>Practice website</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>Rien à voir avec moi</t>
+          <t>Site du cabinet</t>
         </is>
       </c>
       <c r="E179" s="11" t="n"/>
@@ -4884,22 +4884,22 @@
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[15].title</t>
+          <t>author.contactLabel</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>The Forecast</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>La prévision</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E180" s="11" t="n"/>
@@ -4908,70 +4908,58 @@
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>map.mapFooter</t>
+          <t>author.pressLabel</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>The Scientific Heartbeat follows the chapters.</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Le pouls scientifique suit les chapitres.</t>
+          <t>Dossier de presse</t>
         </is>
       </c>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
     </row>
-    <row r="182" ht="75" customHeight="1">
-      <c r="A182" s="9" t="inlineStr">
-        <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
-        </is>
-      </c>
-      <c r="B182" s="9" t="inlineStr">
-        <is>
-          <t>map.heartbeat[0]</t>
-        </is>
-      </c>
-      <c r="C182" s="10" t="inlineStr">
-        <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
-        </is>
-      </c>
-      <c r="D182" s="10" t="inlineStr">
-        <is>
-          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
-        </is>
-      </c>
-      <c r="E182" s="11" t="n"/>
-      <c r="F182" s="11" t="n"/>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="n"/>
+      <c r="C182" s="8" t="n"/>
+      <c r="D182" s="8" t="n"/>
+      <c r="E182" s="8" t="n"/>
+      <c r="F182" s="8" t="n"/>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The book’s last sentence, above the notify form</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[1]</t>
+          <t>closing.question</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Is this the situation? Or is this their state?</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
+          <t>Est-ce la situation ? Ou est-ce leur état ?</t>
         </is>
       </c>
       <c r="E183" s="11" t="n"/>
@@ -4980,22 +4968,22 @@
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The book’s last sentence, above the notify form</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeatSource</t>
+          <t>closing.source</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Page 225</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Page 225</t>
         </is>
       </c>
       <c r="E184" s="11" t="n"/>
@@ -5004,7 +4992,7 @@
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>ABOUT THE AUTHOR</t>
+          <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
         </is>
       </c>
       <c r="B185" s="8" t="n"/>
@@ -5016,70 +5004,58 @@
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Companion tool (currently hidden)</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>author.eyebrow</t>
+          <t>companion.eyebrow</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>The author</t>
+          <t>Alongside the book</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>L’autrice</t>
+          <t>En complément du livre</t>
         </is>
       </c>
       <c r="E186" s="11" t="n"/>
       <c r="F186" s="11" t="n"/>
     </row>
-    <row r="187" ht="30" customHeight="1">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>About the author</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
-        <is>
-          <t>author.title</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="D187" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="E187" s="11" t="n"/>
-      <c r="F187" s="11" t="n"/>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>PRESS PAGE</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="n"/>
+      <c r="C187" s="8" t="n"/>
+      <c r="D187" s="8" t="n"/>
+      <c r="E187" s="8" t="n"/>
+      <c r="F187" s="8" t="n"/>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>author.photoAlt</t>
+          <t>press.eyebrow</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographed against a dark grey background.</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographiée sur fond gris foncé.</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E188" s="11" t="n"/>
@@ -5088,46 +5064,46 @@
     <row r="189" ht="30" customHeight="1">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>author.photoPlaceholder</t>
+          <t>press.title</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>Author photograph to follow</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice à venir</t>
+          <t>Dossier de presse</t>
         </is>
       </c>
       <c r="E189" s="11" t="n"/>
       <c r="F189" s="11" t="n"/>
     </row>
-    <row r="190" ht="30" customHeight="1">
+    <row r="190" ht="45" customHeight="1">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>author.bio</t>
+          <t>press.intro</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
+          <t>Des exemplaires de presse, papier et numérique, sont disponibles sur demande. Reproduction d’extraits, entretiens et rencontres à convenir.</t>
         </is>
       </c>
       <c r="E190" s="11" t="n"/>
@@ -5136,22 +5112,22 @@
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>author.websiteLabel</t>
+          <t>press.contactHeading</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>Practice website</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>Site du cabinet</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E191" s="11" t="n"/>
@@ -5160,22 +5136,22 @@
     <row r="192" ht="30" customHeight="1">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>author.contactLabel</t>
+          <t>press.assetsHeading</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Téléchargements</t>
         </is>
       </c>
       <c r="E192" s="11" t="n"/>
@@ -5184,58 +5160,70 @@
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>author.pressLabel</t>
+          <t>press.assets[0].label</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Front cover, high resolution</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>Dossier de presse</t>
+          <t>Première de couverture, haute résolution</t>
         </is>
       </c>
       <c r="E193" s="11" t="n"/>
       <c r="F193" s="11" t="n"/>
     </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="7" t="inlineStr">
-        <is>
-          <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
-        </is>
-      </c>
-      <c r="B194" s="8" t="n"/>
-      <c r="C194" s="8" t="n"/>
-      <c r="D194" s="8" t="n"/>
-      <c r="E194" s="8" t="n"/>
-      <c r="F194" s="8" t="n"/>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="inlineStr">
+        <is>
+          <t>press.assets[0].note</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>JPEG, 2400 px wide</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="inlineStr">
+        <is>
+          <t>JPEG, 2400 px de large</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="n"/>
+      <c r="F194" s="11" t="n"/>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>The book’s last sentence, above the notify form</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>closing.question</t>
+          <t>press.assets[1].label</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this their state?</t>
+          <t>Author photograph</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>Est-ce la situation ? Ou est-ce leur état ?</t>
+          <t>Photographie de l’autrice</t>
         </is>
       </c>
       <c r="E195" s="11" t="n"/>
@@ -5244,74 +5232,98 @@
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>The book’s last sentence, above the notify form</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
         <is>
-          <t>closing.source</t>
+          <t>press.assets[1].note</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="E196" s="11" t="n"/>
       <c r="F196" s="11" t="n"/>
     </row>
-    <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="7" t="inlineStr">
-        <is>
-          <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="n"/>
-      <c r="C197" s="8" t="n"/>
-      <c r="D197" s="8" t="n"/>
-      <c r="E197" s="8" t="n"/>
-      <c r="F197" s="8" t="n"/>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>press.assets[2].label</t>
+        </is>
+      </c>
+      <c r="C197" s="10" t="inlineStr">
+        <is>
+          <t>Book render, transparent background</t>
+        </is>
+      </c>
+      <c r="D197" s="10" t="inlineStr">
+        <is>
+          <t>Rendu du livre, fond transparent</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="n"/>
+      <c r="F197" s="11" t="n"/>
     </row>
     <row r="198" ht="30" customHeight="1">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>Companion tool (currently hidden)</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
         <is>
-          <t>companion.eyebrow</t>
+          <t>press.assets[2].note</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>Alongside the book</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>En complément du livre</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="E198" s="11" t="n"/>
       <c r="F198" s="11" t="n"/>
     </row>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="7" t="inlineStr">
-        <is>
-          <t>PRESS PAGE</t>
-        </is>
-      </c>
-      <c r="B199" s="8" t="n"/>
-      <c r="C199" s="8" t="n"/>
-      <c r="D199" s="8" t="n"/>
-      <c r="E199" s="8" t="n"/>
-      <c r="F199" s="8" t="n"/>
+    <row r="199" ht="30" customHeight="1">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B199" s="9" t="inlineStr">
+        <is>
+          <t>press.assets[3].label</t>
+        </is>
+      </c>
+      <c r="C199" s="10" t="inlineStr">
+        <is>
+          <t>Web banner</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <t>Bannière web</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="n"/>
+      <c r="F199" s="11" t="n"/>
     </row>
     <row r="200" ht="30" customHeight="1">
       <c r="A200" s="9" t="inlineStr">
@@ -5321,17 +5333,17 @@
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>press.eyebrow</t>
+          <t>press.assets[3].note</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>Presse</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="E200" s="11" t="n"/>
@@ -5345,23 +5357,23 @@
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>press.title</t>
+          <t>press.assets[4].label</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Social image, square</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>Dossier de presse</t>
+          <t>Image pour les réseaux, carrée</t>
         </is>
       </c>
       <c r="E201" s="11" t="n"/>
       <c r="F201" s="11" t="n"/>
     </row>
-    <row r="202" ht="45" customHeight="1">
+    <row r="202" ht="30" customHeight="1">
       <c r="A202" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5369,17 +5381,17 @@
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>press.intro</t>
+          <t>press.assets[4].note</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>Des exemplaires de presse, papier et numérique, sont disponibles sur demande. Reproduction d’extraits, entretiens et rencontres à convenir.</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="E202" s="11" t="n"/>
@@ -5393,17 +5405,17 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>press.contactHeading</t>
+          <t>press.assets[5].label</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Social image, portrait</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Image pour les réseaux, portrait</t>
         </is>
       </c>
       <c r="E203" s="11" t="n"/>
@@ -5417,17 +5429,17 @@
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>press.assetsHeading</t>
+          <t>press.assets[5].note</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>Téléchargements</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="E204" s="11" t="n"/>
@@ -5441,17 +5453,17 @@
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].label</t>
+          <t>press.assets[6].label</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>Front cover, high resolution</t>
+          <t>Social image, landscape</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>Première de couverture, haute résolution</t>
+          <t>Image pour les réseaux, paysage</t>
         </is>
       </c>
       <c r="E205" s="11" t="n"/>
@@ -5465,17 +5477,17 @@
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].note</t>
+          <t>press.assets[6].note</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px wide</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px de large</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="E206" s="11" t="n"/>
@@ -5489,17 +5501,17 @@
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].label</t>
+          <t>press.assets[7].label</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>Author photograph</t>
+          <t>The opening extract</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice</t>
+          <t>L’extrait d’ouverture</t>
         </is>
       </c>
       <c r="E207" s="11" t="n"/>
@@ -5513,17 +5525,17 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].note</t>
+          <t>press.assets[7].note</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>PDF, four pages</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>PDF, quatre pages</t>
         </is>
       </c>
       <c r="E208" s="11" t="n"/>
@@ -5537,17 +5549,17 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].label</t>
+          <t>press.photoUnavailable</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>Book render, transparent background</t>
+          <t>Author photograph available on request.</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>Rendu du livre, fond transparent</t>
+          <t>Photographie de l’autrice disponible sur demande.</t>
         </is>
       </c>
       <c r="E209" s="11" t="n"/>
@@ -5561,17 +5573,17 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].note</t>
+          <t>press.bioHeading</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Biographie</t>
         </is>
       </c>
       <c r="E210" s="11" t="n"/>
@@ -5585,17 +5597,17 @@
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].label</t>
+          <t>press.bios[0].label</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>Web banner</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>Bannière web</t>
+          <t>Courte</t>
         </is>
       </c>
       <c r="E211" s="11" t="n"/>
@@ -5609,17 +5621,17 @@
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].note</t>
+          <t>press.bios[0].text</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
         </is>
       </c>
       <c r="E212" s="11" t="n"/>
@@ -5633,17 +5645,17 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].label</t>
+          <t>press.bios[1].label</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>Social image, square</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, carrée</t>
+          <t>Longue</t>
         </is>
       </c>
       <c r="E213" s="11" t="n"/>
@@ -5657,17 +5669,17 @@
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].note</t>
+          <t>press.factsHeading</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="E214" s="11" t="n"/>
@@ -5681,17 +5693,17 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].label</t>
+          <t>press.facts[0].label</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>Social image, portrait</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, portrait</t>
+          <t>Titre</t>
         </is>
       </c>
       <c r="E215" s="11" t="n"/>
@@ -5705,17 +5717,17 @@
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].note</t>
+          <t>press.facts[0].value</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="E216" s="11" t="n"/>
@@ -5729,17 +5741,17 @@
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].label</t>
+          <t>press.facts[1].label</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>Social image, landscape</t>
+          <t>Subtitle</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, paysage</t>
+          <t>Sous-titre</t>
         </is>
       </c>
       <c r="E217" s="11" t="n"/>
@@ -5753,17 +5765,17 @@
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].note</t>
+          <t>press.facts[1].value</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité</t>
         </is>
       </c>
       <c r="E218" s="11" t="n"/>
@@ -5777,17 +5789,17 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].label</t>
+          <t>press.facts[2].label</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>The opening extract</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>L’extrait d’ouverture</t>
+          <t>Autrice</t>
         </is>
       </c>
       <c r="E219" s="11" t="n"/>
@@ -5801,17 +5813,17 @@
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].note</t>
+          <t>press.facts[2].value</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>PDF, four pages</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>PDF, quatre pages</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E220" s="11" t="n"/>
@@ -5825,17 +5837,17 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>press.photoUnavailable</t>
+          <t>press.facts[3].label</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>Author photograph available on request.</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice disponible sur demande.</t>
+          <t>Éditeur</t>
         </is>
       </c>
       <c r="E221" s="11" t="n"/>
@@ -5849,17 +5861,17 @@
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>press.bioHeading</t>
+          <t>press.facts[3].value</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Budisin Publishing, Luxembourg</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>Biographie</t>
+          <t>Budisin Publishing, Luxembourg</t>
         </is>
       </c>
       <c r="E222" s="11" t="n"/>
@@ -5873,17 +5885,17 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].label</t>
+          <t>press.facts[4].label</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>Courte</t>
+          <t>Parution</t>
         </is>
       </c>
       <c r="E223" s="11" t="n"/>
@@ -5897,17 +5909,17 @@
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].text</t>
+          <t>press.facts[4].value</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E224" s="11" t="n"/>
@@ -5921,17 +5933,17 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>press.bios[1].label</t>
+          <t>press.facts[5].label</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>Longue</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="E225" s="11" t="n"/>
@@ -5945,17 +5957,17 @@
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>press.factsHeading</t>
+          <t>press.facts[5].value</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Paperback, 6 × 9 in</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Broché, 15,2 × 22,9 cm (6 × 9 pouces)</t>
         </is>
       </c>
       <c r="E226" s="11" t="n"/>
@@ -5969,17 +5981,17 @@
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].label</t>
+          <t>press.facts[6].label</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Extent</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>Titre</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E227" s="11" t="n"/>
@@ -5993,17 +6005,17 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].value</t>
+          <t>press.facts[6].value</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>278 pages</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>278 pages</t>
         </is>
       </c>
       <c r="E228" s="11" t="n"/>
@@ -6017,17 +6029,17 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].label</t>
+          <t>press.facts[7].label</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
         <is>
-          <t>Subtitle</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>Sous-titre</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="E229" s="11" t="n"/>
@@ -6041,17 +6053,17 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].value</t>
+          <t>press.facts[7].value</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="E230" s="11" t="n"/>
@@ -6065,17 +6077,17 @@
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].label</t>
+          <t>press.facts[8].label</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>Autrice</t>
+          <t>Catégorie</t>
         </is>
       </c>
       <c r="E231" s="11" t="n"/>
@@ -6089,17 +6101,17 @@
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].value</t>
+          <t>press.facts[8].value</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Psychology / Cognitive psychology</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Psychologie / Psychologie cognitive</t>
         </is>
       </c>
       <c r="E232" s="11" t="n"/>
@@ -6113,17 +6125,17 @@
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].label</t>
+          <t>press.facts[9].label</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>Éditeur</t>
+          <t>Langue</t>
         </is>
       </c>
       <c r="E233" s="11" t="n"/>
@@ -6137,17 +6149,17 @@
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].value</t>
+          <t>press.facts[9].value</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>English. French and German editions to follow.</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>Anglais. Éditions française et allemande à venir.</t>
         </is>
       </c>
       <c r="E234" s="11" t="n"/>
@@ -6161,17 +6173,17 @@
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].label</t>
+          <t>press.facts[10].label</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Legal deposit</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>Parution</t>
+          <t>Dépôt légal</t>
         </is>
       </c>
       <c r="E235" s="11" t="n"/>
@@ -6185,17 +6197,17 @@
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].value</t>
+          <t>press.facts[10].value</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Une notice CIP est disponible à la Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="E236" s="11" t="n"/>
@@ -6209,23 +6221,23 @@
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].label</t>
+          <t>press.descriptionHeading</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>About the book</t>
         </is>
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>À propos du livre</t>
         </is>
       </c>
       <c r="E237" s="11" t="n"/>
       <c r="F237" s="11" t="n"/>
     </row>
-    <row r="238" ht="30" customHeight="1">
+    <row r="238" ht="45" customHeight="1">
       <c r="A238" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6233,17 +6245,17 @@
       </c>
       <c r="B238" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].value</t>
+          <t>press.description[0]</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 in</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>Broché, 15,2 × 22,9 cm (6 × 9 pouces)</t>
+          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
         </is>
       </c>
       <c r="E238" s="11" t="n"/>
@@ -6257,23 +6269,23 @@
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].label</t>
+          <t>press.description[1]</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>Extent</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
         </is>
       </c>
       <c r="E239" s="11" t="n"/>
       <c r="F239" s="11" t="n"/>
     </row>
-    <row r="240" ht="30" customHeight="1">
+    <row r="240" ht="75" customHeight="1">
       <c r="A240" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6281,17 +6293,17 @@
       </c>
       <c r="B240" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].value</t>
+          <t>press.description[2]</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
         </is>
       </c>
       <c r="E240" s="11" t="n"/>
@@ -6305,17 +6317,17 @@
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].label</t>
+          <t>press.description[3]</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
         </is>
       </c>
       <c r="E241" s="11" t="n"/>
@@ -6329,17 +6341,17 @@
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].value</t>
+          <t>press.creditsHeading</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Crédits</t>
         </is>
       </c>
       <c r="E242" s="11" t="n"/>
@@ -6353,17 +6365,17 @@
       </c>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].label</t>
+          <t>press.credits[0].label</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Cover design</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>Catégorie</t>
+          <t>Conception de la couverture</t>
         </is>
       </c>
       <c r="E243" s="11" t="n"/>
@@ -6377,17 +6389,17 @@
       </c>
       <c r="B244" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].value</t>
+          <t>press.credits[0].value</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
         <is>
-          <t>Psychology / Cognitive psychology</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="D244" s="10" t="inlineStr">
         <is>
-          <t>Psychologie / Psychologie cognitive</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="E244" s="11" t="n"/>
@@ -6401,17 +6413,17 @@
       </c>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].label</t>
+          <t>press.credits[1].label</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Book design and typesetting</t>
         </is>
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>Langue</t>
+          <t>Conception graphique et mise en page</t>
         </is>
       </c>
       <c r="E245" s="11" t="n"/>
@@ -6425,17 +6437,17 @@
       </c>
       <c r="B246" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].value</t>
+          <t>press.credits[1].value</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
         <is>
-          <t>English. French and German editions to follow.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D246" s="10" t="inlineStr">
         <is>
-          <t>Anglais. Éditions française et allemande à venir.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E246" s="11" t="n"/>
@@ -6449,17 +6461,17 @@
       </c>
       <c r="B247" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].label</t>
+          <t>press.credits[2].label</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
         <is>
-          <t>Legal deposit</t>
+          <t>Published by</t>
         </is>
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>Dépôt légal</t>
+          <t>Publié par</t>
         </is>
       </c>
       <c r="E247" s="11" t="n"/>
@@ -6473,17 +6485,17 @@
       </c>
       <c r="B248" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].value</t>
+          <t>press.credits[2].value</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
         <is>
-          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>Une notice CIP est disponible à la Bibliothèque nationale du Luxembourg.</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="E248" s="11" t="n"/>
@@ -6497,65 +6509,53 @@
       </c>
       <c r="B249" s="9" t="inlineStr">
         <is>
-          <t>press.descriptionHeading</t>
+          <t>press.back</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
         <is>
-          <t>About the book</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D249" s="10" t="inlineStr">
         <is>
-          <t>À propos du livre</t>
+          <t>Retour au livre</t>
         </is>
       </c>
       <c r="E249" s="11" t="n"/>
       <c r="F249" s="11" t="n"/>
     </row>
-    <row r="250" ht="135" customHeight="1">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B250" s="9" t="inlineStr">
-        <is>
-          <t>press.description[0]</t>
-        </is>
-      </c>
-      <c r="C250" s="10" t="inlineStr">
-        <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
-        </is>
-      </c>
-      <c r="D250" s="10" t="inlineStr">
-        <is>
-          <t>Pendant seize jours, Katrin traverse des situations ordinaires où sa première lecture de ce qui se passe n’est pas toujours celle qui tient, à y regarder de plus près. Chaque chapitre suit l’un de ces moments jusque dans la psychologie qui le sous-tend, de l’attention et de la prédiction à la mémoire, à la menace, à l’incertitude et à l’inférence sociale. Le livre ne promet pas un meilleur instinct. Il demande ce qui devient possible quand nous apprenons d’où venait notre première lecture.</t>
-        </is>
-      </c>
-      <c r="E250" s="11" t="n"/>
-      <c r="F250" s="11" t="n"/>
-    </row>
-    <row r="251" ht="45" customHeight="1">
+    <row r="250" ht="22" customHeight="1">
+      <c r="A250" s="7" t="inlineStr">
+        <is>
+          <t>FOOT OF EVERY PAGE</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="n"/>
+      <c r="C250" s="8" t="n"/>
+      <c r="D250" s="8" t="n"/>
+      <c r="E250" s="8" t="n"/>
+      <c r="F250" s="8" t="n"/>
+    </row>
+    <row r="251" ht="30" customHeight="1">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
         <is>
-          <t>press.description[1]</t>
+          <t>footer.band</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Before you believe the story.</t>
         </is>
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
+          <t>Avant de croire l’histoire.</t>
         </is>
       </c>
       <c r="E251" s="11" t="n"/>
@@ -6564,46 +6564,46 @@
     <row r="252" ht="30" customHeight="1">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
         <is>
-          <t>press.description[2]</t>
+          <t>footer.method[0]</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>Read the dashboard.</t>
         </is>
       </c>
       <c r="D252" s="10" t="inlineStr">
         <is>
-          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
+          <t>Lisez le tableau de bord.</t>
         </is>
       </c>
       <c r="E252" s="11" t="n"/>
       <c r="F252" s="11" t="n"/>
     </row>
-    <row r="253" ht="75" customHeight="1">
+    <row r="253" ht="30" customHeight="1">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
         <is>
-          <t>press.description[3]</t>
+          <t>footer.method[1]</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>Delay the story.</t>
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
+          <t>Différez l’histoire.</t>
         </is>
       </c>
       <c r="E253" s="11" t="n"/>
@@ -6612,22 +6612,22 @@
     <row r="254" ht="30" customHeight="1">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
         <is>
-          <t>press.description[4]</t>
+          <t>footer.method[2]</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Take the reading again.</t>
         </is>
       </c>
       <c r="D254" s="10" t="inlineStr">
         <is>
-          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
+          <t>Refaites la lecture.</t>
         </is>
       </c>
       <c r="E254" s="11" t="n"/>
@@ -6636,22 +6636,22 @@
     <row r="255" ht="30" customHeight="1">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>press.creditsHeading</t>
+          <t>footer.rights</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>Crédits</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="E255" s="11" t="n"/>
@@ -6660,22 +6660,22 @@
     <row r="256" ht="30" customHeight="1">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].label</t>
+          <t>footer.pressLink</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
         <is>
-          <t>Cover design</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D256" s="10" t="inlineStr">
         <is>
-          <t>Conception de la couverture</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E256" s="11" t="n"/>
@@ -6684,22 +6684,22 @@
     <row r="257" ht="30" customHeight="1">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].value</t>
+          <t>footer.contactLink</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E257" s="11" t="n"/>
@@ -6708,70 +6708,58 @@
     <row r="258" ht="30" customHeight="1">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
         <is>
-          <t>press.credits[1].label</t>
+          <t>footer.madeLine</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
         <is>
-          <t>Book design and typesetting</t>
+          <t>Same life. Different instrument settings.</t>
         </is>
       </c>
       <c r="D258" s="10" t="inlineStr">
         <is>
-          <t>Conception graphique et mise en page</t>
+          <t>Même vie. Instruments réglés autrement.</t>
         </is>
       </c>
       <c r="E258" s="11" t="n"/>
       <c r="F258" s="11" t="n"/>
     </row>
-    <row r="259" ht="30" customHeight="1">
-      <c r="A259" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B259" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[1].value</t>
-        </is>
-      </c>
-      <c r="C259" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="D259" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="E259" s="11" t="n"/>
-      <c r="F259" s="11" t="n"/>
+    <row r="259" ht="22" customHeight="1">
+      <c r="A259" s="7" t="inlineStr">
+        <is>
+          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="n"/>
+      <c r="C259" s="8" t="n"/>
+      <c r="D259" s="8" t="n"/>
+      <c r="E259" s="8" t="n"/>
+      <c r="F259" s="8" t="n"/>
     </row>
     <row r="260" ht="30" customHeight="1">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].label</t>
+          <t>a11y.mainLandmark</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
         <is>
-          <t>Published by</t>
+          <t>Main content</t>
         </is>
       </c>
       <c r="D260" s="10" t="inlineStr">
         <is>
-          <t>Publié par</t>
+          <t>Contenu principal</t>
         </is>
       </c>
       <c r="E260" s="11" t="n"/>
@@ -6780,22 +6768,22 @@
     <row r="261" ht="30" customHeight="1">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].value</t>
+          <t>a11y.coverFigure</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>Le livre</t>
         </is>
       </c>
       <c r="E261" s="11" t="n"/>
@@ -6804,58 +6792,70 @@
     <row r="262" ht="30" customHeight="1">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
         <is>
-          <t>press.back</t>
+          <t>a11y.languageSwitcher</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Choose language</t>
         </is>
       </c>
       <c r="D262" s="10" t="inlineStr">
         <is>
-          <t>Retour au livre</t>
+          <t>Choisir la langue</t>
         </is>
       </c>
       <c r="E262" s="11" t="n"/>
       <c r="F262" s="11" t="n"/>
     </row>
-    <row r="263" ht="22" customHeight="1">
-      <c r="A263" s="7" t="inlineStr">
-        <is>
-          <t>FOOT OF EVERY PAGE</t>
-        </is>
-      </c>
-      <c r="B263" s="8" t="n"/>
-      <c r="C263" s="8" t="n"/>
-      <c r="D263" s="8" t="n"/>
-      <c r="E263" s="8" t="n"/>
-      <c r="F263" s="8" t="n"/>
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B263" s="9" t="inlineStr">
+        <is>
+          <t>a11y.languageComing</t>
+        </is>
+      </c>
+      <c r="C263" s="10" t="inlineStr">
+        <is>
+          <t>edition to follow</t>
+        </is>
+      </c>
+      <c r="D263" s="10" t="inlineStr">
+        <is>
+          <t>édition à venir</t>
+        </is>
+      </c>
+      <c r="E263" s="11" t="n"/>
+      <c r="F263" s="11" t="n"/>
     </row>
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
         <is>
-          <t>footer.band</t>
+          <t>a11y.casesRegion</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
         <is>
-          <t>Before you believe the story.</t>
+          <t>Case evidence pages from the book</t>
         </is>
       </c>
       <c r="D264" s="10" t="inlineStr">
         <is>
-          <t>Avant de croire l’histoire.</t>
+          <t>Pièces du dossier tirées du livre</t>
         </is>
       </c>
       <c r="E264" s="11" t="n"/>
@@ -6864,22 +6864,22 @@
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>footer.method[0]</t>
+          <t>a11y.bookOpening</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
         <is>
-          <t>Read the dashboard.</t>
+          <t>The book, opening</t>
         </is>
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>Lisez le tableau de bord.</t>
+          <t>Le livre qui s’ouvre</t>
         </is>
       </c>
       <c r="E265" s="11" t="n"/>
@@ -6888,22 +6888,22 @@
     <row r="266" ht="30" customHeight="1">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
         <is>
-          <t>footer.method[1]</t>
+          <t>a11y.misreadingRegion</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
         <is>
-          <t>Delay the story.</t>
+          <t>Page 10 of the book</t>
         </is>
       </c>
       <c r="D266" s="10" t="inlineStr">
         <is>
-          <t>Différez l’histoire.</t>
+          <t>Page 10 du livre</t>
         </is>
       </c>
       <c r="E266" s="11" t="n"/>
@@ -6912,22 +6912,22 @@
     <row r="267" ht="30" customHeight="1">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
         <is>
-          <t>footer.method[2]</t>
+          <t>a11y.mapRegion</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
         <is>
-          <t>Take the reading again.</t>
+          <t>A map of the book</t>
         </is>
       </c>
       <c r="D267" s="10" t="inlineStr">
         <is>
-          <t>Refaites la lecture.</t>
+          <t>Une carte du livre</t>
         </is>
       </c>
       <c r="E267" s="11" t="n"/>
@@ -6936,329 +6936,29 @@
     <row r="268" ht="30" customHeight="1">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
         <is>
-          <t>footer.rights</t>
+          <t>a11y.evidenceRegion</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Confidence markers, page 13</t>
         </is>
       </c>
       <c r="D268" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Marqueurs de confiance, page 13</t>
         </is>
       </c>
       <c r="E268" s="11" t="n"/>
       <c r="F268" s="11" t="n"/>
     </row>
-    <row r="269" ht="30" customHeight="1">
-      <c r="A269" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B269" s="9" t="inlineStr">
-        <is>
-          <t>footer.pressLink</t>
-        </is>
-      </c>
-      <c r="C269" s="10" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
-      <c r="D269" s="10" t="inlineStr">
-        <is>
-          <t>Presse</t>
-        </is>
-      </c>
-      <c r="E269" s="11" t="n"/>
-      <c r="F269" s="11" t="n"/>
-    </row>
-    <row r="270" ht="30" customHeight="1">
-      <c r="A270" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B270" s="9" t="inlineStr">
-        <is>
-          <t>footer.contactLink</t>
-        </is>
-      </c>
-      <c r="C270" s="10" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D270" s="10" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="E270" s="11" t="n"/>
-      <c r="F270" s="11" t="n"/>
-    </row>
-    <row r="271" ht="30" customHeight="1">
-      <c r="A271" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B271" s="9" t="inlineStr">
-        <is>
-          <t>footer.madeLine</t>
-        </is>
-      </c>
-      <c r="C271" s="10" t="inlineStr">
-        <is>
-          <t>Same life. Different instrument settings.</t>
-        </is>
-      </c>
-      <c r="D271" s="10" t="inlineStr">
-        <is>
-          <t>Même vie. Instruments réglés autrement.</t>
-        </is>
-      </c>
-      <c r="E271" s="11" t="n"/>
-      <c r="F271" s="11" t="n"/>
-    </row>
-    <row r="272" ht="22" customHeight="1">
-      <c r="A272" s="7" t="inlineStr">
-        <is>
-          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
-        </is>
-      </c>
-      <c r="B272" s="8" t="n"/>
-      <c r="C272" s="8" t="n"/>
-      <c r="D272" s="8" t="n"/>
-      <c r="E272" s="8" t="n"/>
-      <c r="F272" s="8" t="n"/>
-    </row>
-    <row r="273" ht="30" customHeight="1">
-      <c r="A273" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B273" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mainLandmark</t>
-        </is>
-      </c>
-      <c r="C273" s="10" t="inlineStr">
-        <is>
-          <t>Main content</t>
-        </is>
-      </c>
-      <c r="D273" s="10" t="inlineStr">
-        <is>
-          <t>Contenu principal</t>
-        </is>
-      </c>
-      <c r="E273" s="11" t="n"/>
-      <c r="F273" s="11" t="n"/>
-    </row>
-    <row r="274" ht="30" customHeight="1">
-      <c r="A274" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B274" s="9" t="inlineStr">
-        <is>
-          <t>a11y.coverFigure</t>
-        </is>
-      </c>
-      <c r="C274" s="10" t="inlineStr">
-        <is>
-          <t>The book</t>
-        </is>
-      </c>
-      <c r="D274" s="10" t="inlineStr">
-        <is>
-          <t>Le livre</t>
-        </is>
-      </c>
-      <c r="E274" s="11" t="n"/>
-      <c r="F274" s="11" t="n"/>
-    </row>
-    <row r="275" ht="30" customHeight="1">
-      <c r="A275" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B275" s="9" t="inlineStr">
-        <is>
-          <t>a11y.languageSwitcher</t>
-        </is>
-      </c>
-      <c r="C275" s="10" t="inlineStr">
-        <is>
-          <t>Choose language</t>
-        </is>
-      </c>
-      <c r="D275" s="10" t="inlineStr">
-        <is>
-          <t>Choisir la langue</t>
-        </is>
-      </c>
-      <c r="E275" s="11" t="n"/>
-      <c r="F275" s="11" t="n"/>
-    </row>
-    <row r="276" ht="30" customHeight="1">
-      <c r="A276" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B276" s="9" t="inlineStr">
-        <is>
-          <t>a11y.languageComing</t>
-        </is>
-      </c>
-      <c r="C276" s="10" t="inlineStr">
-        <is>
-          <t>edition to follow</t>
-        </is>
-      </c>
-      <c r="D276" s="10" t="inlineStr">
-        <is>
-          <t>édition à venir</t>
-        </is>
-      </c>
-      <c r="E276" s="11" t="n"/>
-      <c r="F276" s="11" t="n"/>
-    </row>
-    <row r="277" ht="30" customHeight="1">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
-        <is>
-          <t>a11y.casesRegion</t>
-        </is>
-      </c>
-      <c r="C277" s="10" t="inlineStr">
-        <is>
-          <t>Case evidence pages from the book</t>
-        </is>
-      </c>
-      <c r="D277" s="10" t="inlineStr">
-        <is>
-          <t>Pièces du dossier tirées du livre</t>
-        </is>
-      </c>
-      <c r="E277" s="11" t="n"/>
-      <c r="F277" s="11" t="n"/>
-    </row>
-    <row r="278" ht="30" customHeight="1">
-      <c r="A278" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B278" s="9" t="inlineStr">
-        <is>
-          <t>a11y.bookOpening</t>
-        </is>
-      </c>
-      <c r="C278" s="10" t="inlineStr">
-        <is>
-          <t>The book, opening</t>
-        </is>
-      </c>
-      <c r="D278" s="10" t="inlineStr">
-        <is>
-          <t>Le livre qui s’ouvre</t>
-        </is>
-      </c>
-      <c r="E278" s="11" t="n"/>
-      <c r="F278" s="11" t="n"/>
-    </row>
-    <row r="279" ht="30" customHeight="1">
-      <c r="A279" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B279" s="9" t="inlineStr">
-        <is>
-          <t>a11y.misreadingRegion</t>
-        </is>
-      </c>
-      <c r="C279" s="10" t="inlineStr">
-        <is>
-          <t>Page 10 of the book</t>
-        </is>
-      </c>
-      <c r="D279" s="10" t="inlineStr">
-        <is>
-          <t>Page 10 du livre</t>
-        </is>
-      </c>
-      <c r="E279" s="11" t="n"/>
-      <c r="F279" s="11" t="n"/>
-    </row>
-    <row r="280" ht="30" customHeight="1">
-      <c r="A280" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B280" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mapRegion</t>
-        </is>
-      </c>
-      <c r="C280" s="10" t="inlineStr">
-        <is>
-          <t>A map of the book</t>
-        </is>
-      </c>
-      <c r="D280" s="10" t="inlineStr">
-        <is>
-          <t>Une carte du livre</t>
-        </is>
-      </c>
-      <c r="E280" s="11" t="n"/>
-      <c r="F280" s="11" t="n"/>
-    </row>
-    <row r="281" ht="30" customHeight="1">
-      <c r="A281" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B281" s="9" t="inlineStr">
-        <is>
-          <t>a11y.evidenceRegion</t>
-        </is>
-      </c>
-      <c r="C281" s="10" t="inlineStr">
-        <is>
-          <t>Confidence markers, page 13</t>
-        </is>
-      </c>
-      <c r="D281" s="10" t="inlineStr">
-        <is>
-          <t>Marqueurs de confiance, page 13</t>
-        </is>
-      </c>
-      <c r="E281" s="11" t="n"/>
-      <c r="F281" s="11" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F281"/>
+  <autoFilter ref="A1:F268"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/State-Not-Situation-French-review.xlsx
+++ b/review/State-Not-Situation-French-review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="French review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'French review'!$A$1:$F$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'French review'!$A$1:$F$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F268"/>
+  <dimension ref="A1:F242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -813,7 +813,7 @@
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="11" t="n"/>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Browser tab, Google result, link previews</t>
@@ -826,12 +826,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality. Sixteen cases. Three readings. One question: state or situation? By Ivana Budišin.</t>
+          <t>A field guide to the moment before interpretation becomes reality. Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité. Seize cas. Trois lectures. Une question : état ou situation ? Par Ivana Budišin.</t>
+          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité. Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
         </is>
       </c>
       <c r="E5" s="11" t="n"/>
@@ -850,12 +850,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>The cover of State. Not Situation. by Ivana Budišin: the word STATE set large in red above NOT SITUATION in black, on cream.</t>
+          <t>State. Not Situation. by Ivana Budišin. A field guide to the moment before interpretation becomes reality.</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>La couverture de State. Not Situation. d’Ivana Budišin : le mot STATE en grand, en rouge, au-dessus de NOT SITUATION en noir, sur fond crème.</t>
+          <t>State. Not Situation. par Ivana Budišin. Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité.</t>
         </is>
       </c>
       <c r="E6" s="11" t="n"/>
@@ -885,7 +885,7 @@
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="11" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Browser tab, Google result, link previews</t>
@@ -898,12 +898,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>The opening pages of State. Not Situation. by Ivana Budišin: a pilot, haze over open water, and one sentence from the Federal Aviation Administration.</t>
+          <t>The opening pages of State. Not Situation. by Ivana Budišin.</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Les premières pages de State. Not Situation. d’Ivana Budišin : un pilote, de la brume au large, et une phrase de la Federal Aviation Administration.</t>
+          <t>Les premières pages de State. Not Situation. d’Ivana Budišin.</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Press materials for State. Not Situation. by Ivana Budišin: cover art, author photograph, biography, publication details and contact.</t>
+          <t>Press materials for State. Not Situation. by Ivana Budišin: cover, author photograph, publication details, extract.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Dossier de presse de State. Not Situation. d’Ivana Budišin : couverture, photographie de l’autrice, biographie, informations de publication et contact.</t>
+          <t>Dossier de presse de State. Not Situation. d’Ivana Budišin : couverture, photographie de l’autrice, informations de publication, extrait.</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -960,7 +960,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>TOP NAVIGATION BAR</t>
+          <t>TOP NAVIGATION BAR AND THE PHONE MENU</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -972,22 +972,22 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>nav.book</t>
+          <t>nav.home</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>State. Not Situation., home</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Le livre</t>
+          <t>State. Not Situation., accueil</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -996,22 +996,22 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>nav.read</t>
+          <t>nav.book</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Lire</t>
+          <t>Le livre</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1020,22 +1020,22 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>nav.listen</t>
+          <t>nav.read</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>Extract</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Écouter</t>
+          <t>L’extrait</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -1044,7 +1044,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1068,7 +1068,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1092,22 +1092,22 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>nav.skipToContent</t>
+          <t>nav.listen</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Skip to content</t>
+          <t>Listen</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Aller au contenu</t>
+          <t>Écouter</t>
         </is>
       </c>
       <c r="E17" s="11" t="n"/>
@@ -1116,86 +1116,86 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>nav.home</t>
+          <t>nav.skipToContent</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation. Home</t>
+          <t>Skip to content</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation. Accueil</t>
+          <t>Aller au contenu</t>
         </is>
       </c>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>PUBLICATION STATUS AND THE NOTIFY FORM</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Top navigation bar and the phone menu</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>nav.menu</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Publication status and the notify form</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>status.forthcoming</t>
+          <t>nav.closeMenu</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Publishing soon</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>À paraître</t>
+          <t>Fermer</t>
         </is>
       </c>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="11" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Publication status and the notify form</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>status.published</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Out now</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>PUBLICATION STATUS AND THE NOTIFY FORM</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>status.publicationDatePrefix</t>
+          <t>status.forthcoming</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Publishing soon</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Parution</t>
+          <t>À paraître</t>
         </is>
       </c>
       <c r="E22" s="11" t="n"/>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>status.buy</t>
+          <t>status.published</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Buy on Amazon</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Acheter sur Amazon</t>
+          <t>Paru</t>
         </is>
       </c>
       <c r="E23" s="11" t="n"/>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>status.notifyHeading</t>
+          <t>status.publicationDatePrefix</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Be notified when the book is released.</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Être prévenu à la parution du livre.</t>
+          <t>Parution</t>
         </is>
       </c>
       <c r="E24" s="11" t="n"/>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>status.notifyCta</t>
+          <t>status.buy</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Be notified</t>
+          <t>Buy on Amazon</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Être prévenu</t>
+          <t>Acheter sur Amazon</t>
         </is>
       </c>
       <c r="E25" s="11" t="n"/>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>status.emailLabel</t>
+          <t>status.notifyCta</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Email address</t>
+          <t>Publication updates</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Adresse e-mail</t>
+          <t>Avis de parution</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -1325,17 +1325,17 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>status.emailPlaceholder</t>
+          <t>status.emailLabel</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>your@email.com</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>votre@email.com</t>
+          <t>Adresse e-mail</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -1349,17 +1349,17 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>status.submit</t>
+          <t>status.emailPlaceholder</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Notify me</t>
+          <t>your@email.com</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Prévenez-moi</t>
+          <t>votre@email.com</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>
@@ -1373,17 +1373,17 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>status.success</t>
+          <t>status.submit</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Thank you. You will hear from me when the book is out.</t>
+          <t>Notify me</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Merci. Vous aurez de mes nouvelles à la sortie du livre.</t>
+          <t>Prévenez-moi</t>
         </is>
       </c>
       <c r="E29" s="11" t="n"/>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>status.error</t>
+          <t>status.success</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>That did not send. Please try again, or write to me directly.</t>
+          <t>Thank you. You will hear once, when the book is out.</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>L’envoi n’a pas abouti. Réessayez, ou écrivez-moi directement.</t>
+          <t>Merci. Vous recevrez un seul message, à la sortie du livre.</t>
         </is>
       </c>
       <c r="E30" s="11" t="n"/>
@@ -1421,17 +1421,17 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>status.privacyNote</t>
+          <t>status.error</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Used for this notification only.</t>
+          <t>That did not send. Please try again, or email me directly.</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Utilisée uniquement pour cette notification.</t>
+          <t>L’envoi n’a pas abouti. Réessayez, ou écrivez-moi directement.</t>
         </is>
       </c>
       <c r="E31" s="11" t="n"/>
@@ -1445,17 +1445,17 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>status.mailtoLabel</t>
+          <t>status.privacyNote</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Email me to be notified</t>
+          <t>Used for this notification only.</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>M’écrire pour être prévenu</t>
+          <t>Adresse utilisée uniquement pour cette notification.</t>
         </is>
       </c>
       <c r="E32" s="11" t="n"/>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Tell me when State. Not Situation. is out</t>
+          <t>State. Not Situation. — publication updates</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Prévenez-moi de la sortie de State. Not Situation.</t>
+          <t>State. Not Situation., avis de parution</t>
         </is>
       </c>
       <c r="E33" s="11" t="n"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Please let me know when State. Not Situation. is available.</t>
+          <t>Please let me know when the book is published.</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Merci de me prévenir quand State. Not Situation. sera disponible.</t>
+          <t>Merci de me prévenir quand le livre paraîtra.</t>
         </is>
       </c>
       <c r="E34" s="11" t="n"/>
@@ -1512,7 +1512,7 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>FIRST SCREEN — THE BOOK AND TITLE</t>
+          <t>FIRST SCREEN — THE COVER AND THE TITLE</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
@@ -1524,22 +1524,22 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>hero.eyebrow</t>
+          <t>hero.titleA</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Time · Attention · Safety</t>
+          <t>State.</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Temps · Attention · Sécurité</t>
+          <t>State.</t>
         </is>
       </c>
       <c r="E36" s="11" t="n"/>
@@ -1548,22 +1548,22 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>hero.titleA</t>
+          <t>hero.titleB</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>State.</t>
+          <t>Not Situation</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>State.</t>
+          <t>Not Situation</t>
         </is>
       </c>
       <c r="E37" s="11" t="n"/>
@@ -1572,22 +1572,22 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>hero.titleB</t>
+          <t>hero.subtitle</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Not Situation</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Not Situation</t>
+          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité</t>
         </is>
       </c>
       <c r="E38" s="11" t="n"/>
@@ -1596,22 +1596,22 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>hero.subtitle</t>
+          <t>hero.strap</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>Your first reading is not the whole story.</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité</t>
+          <t>Votre première lecture n’est pas toute l’histoire.</t>
         </is>
       </c>
       <c r="E39" s="11" t="n"/>
@@ -1620,118 +1620,106 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>hero.strap</t>
+          <t>hero.authorPrefix</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Your first reading is not the whole story.</t>
+          <t>by</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Votre première lecture n’est pas toute l’histoire.</t>
+          <t>par</t>
         </is>
       </c>
       <c r="E40" s="11" t="n"/>
       <c r="F40" s="11" t="n"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>hero.authorPrefix</t>
+          <t>hero.coverAlt</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>by</t>
+          <t>Front cover of State. Not Situation. The word STATE set large in red above NOT SITUATION in black, on a cream ground printed with faint struck-through sentences and small instrument readings.</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>par</t>
+          <t>Première de couverture de State. Not Situation. Le mot STATE en grand, en rouge, au-dessus de NOT SITUATION en noir, sur un fond crème imprimé de phrases barrées, à peine visibles, et de petits relevés d’instruments.</t>
         </is>
       </c>
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="11" t="n"/>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>hero.coverAlt</t>
+          <t>hero.readCta</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Front cover of State. Not Situation. The word STATE set large in red above NOT SITUATION in black, on a cream ground printed with faint struck-through sentences and small instrument readings.</t>
+          <t>Read an extract</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Première de couverture de State. Not Situation. Le mot STATE en grand, en rouge, au-dessus de NOT SITUATION en noir, sur un fond crème imprimé de phrases barrées, à peine visibles, et de petits relevés d’instruments.</t>
+          <t>Lire un extrait</t>
         </is>
       </c>
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="11" t="n"/>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>First screen — the book and title</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>hero.openAlt</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>The book open at its title page, which reads State. Not Situation.</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Le livre ouvert à sa page de titre, où l’on lit State. Not Situation.</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>THE PREMISE — PAGE 181, PAGE 10 AND THE BACK COVER</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>hero.readCta</t>
+          <t>premise.eyebrow</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>The first misreading</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Lire un extrait</t>
+          <t>La première erreur de lecture</t>
         </is>
       </c>
       <c r="E44" s="11" t="n"/>
@@ -1740,58 +1728,70 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>hero.scrollHint</t>
+          <t>premise.sensorLine</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>The body is a sensor before it is a narrator.</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Défiler</t>
+          <t>Le corps est un capteur avant d’être un narrateur.</t>
         </is>
       </c>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>“THE FIRST MISREADING” — PAGE 10, THE FIVE READINGS</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>The premise — page 181, page 10 and the back cover</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>premise.lines[0]</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Nothing went wrong on this day.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Ce jour-là, rien ne s’est mal passé.</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>misreading.eyebrow</t>
+          <t>premise.lines[1]</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>The first misreading</t>
+          <t>The instruments were working.</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>La première erreur de lecture</t>
+          <t>Les instruments fonctionnaient.</t>
         </is>
       </c>
       <c r="E47" s="11" t="n"/>
@@ -1800,46 +1800,46 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>misreading.lines[0]</t>
+          <t>premise.lines[2]</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Nothing went wrong on this day.</t>
+          <t>The data was there the whole time.</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Ce jour-là, rien ne s’est mal passé.</t>
+          <t>Les données étaient là depuis le début.</t>
         </is>
       </c>
       <c r="E48" s="11" t="n"/>
       <c r="F48" s="11" t="n"/>
     </row>
-    <row r="49" ht="30" customHeight="1">
+    <row r="49" ht="45" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>misreading.lines[1]</t>
+          <t>premise.mechanism[0]</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>The instruments were working.</t>
+          <t>We usually treat these moments as information about life: the person, the task, the relationship, the day.</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Les instruments fonctionnaient.</t>
+          <t>D’habitude, nous traitons ces moments comme des informations sur la vie : la personne, la tâche, la relation, la journée.</t>
         </is>
       </c>
       <c r="E49" s="11" t="n"/>
@@ -1848,46 +1848,46 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>misreading.lines[2]</t>
+          <t>premise.mechanism[1]</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>The data was there the whole time.</t>
+          <t>But the first reading is often not the whole story.</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Les données étaient là depuis le début.</t>
+          <t>Mais souvent, la première lecture n’est pas toute l’histoire.</t>
         </is>
       </c>
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="11" t="n"/>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>misreading.investigationLabel</t>
+          <t>premise.mechanism[2]</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>This book is the</t>
+          <t>Before the mind explains, the body has already voted. Sleep pressure, hunger, timing, attention, threat detection, memory, and prediction quietly shape what feels true.</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Ce livre est</t>
+          <t>Avant que l’esprit n’explique, le corps a déjà voté. La pression de sommeil, la faim, le rythme, l’attention, la détection de la menace, la mémoire et la prédiction façonnent discrètement ce qui paraît vrai.</t>
         </is>
       </c>
       <c r="E51" s="11" t="n"/>
@@ -1896,22 +1896,22 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>misreading.investigation</t>
+          <t>premise.mechanism[3]</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Investigation.</t>
+          <t>Then the mind arrives second and gives that feeling a reason.</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>L’enquête.</t>
+          <t>Puis l’esprit arrive en second et donne une raison à cette sensation.</t>
         </is>
       </c>
       <c r="E52" s="11" t="n"/>
@@ -1920,70 +1920,58 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>misreading.readingsLabel</t>
+          <t>premise.folio</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>The same day, five readings</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Le même jour, cinq lectures</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="11" t="n"/>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>“The first misreading” — page 10, the five readings</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>misreading.readings[0].text</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>A heaviness arrives before the day does.</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>Une lourdeur arrive avant la journée.</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="11" t="n"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>misreading.readings[1].text</t>
+          <t>reading.eyebrow</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>A two-line email reads like a verdict.</t>
+          <t>Try something right now</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Un e-mail de deux lignes se lit comme un verdict.</t>
+          <t>Essayez quelque chose tout de suite</t>
         </is>
       </c>
       <c r="E55" s="11" t="n"/>
@@ -1992,22 +1980,22 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>misreading.readings[2].text</t>
+          <t>reading.lead</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Five neutral words tighten a jaw.</t>
+          <t>Whatever you are feeling as you read this sentence.</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Cinq mots neutres crispent une mâchoire.</t>
+          <t>Quoi que vous ressentiez en lisant cette phrase.</t>
         </is>
       </c>
       <c r="E56" s="11" t="n"/>
@@ -2016,22 +2004,22 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>misreading.readings[3].text</t>
+          <t>reading.steps[0]</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>An unanswered message starts charging rent.</t>
+          <t>Check your jaw.</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Un message sans réponse se met à réclamer un loyer.</t>
+          <t>Observez votre mâchoire.</t>
         </is>
       </c>
       <c r="E57" s="11" t="n"/>
@@ -2040,22 +2028,22 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>misreading.readings[4].text</t>
+          <t>reading.steps[1]</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Two letters and a full stop feel hostile.</t>
+          <t>Check your breath.</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Deux lettres et un point ont l’air hostiles.</t>
+          <t>Observez votre respiration.</t>
         </is>
       </c>
       <c r="E58" s="11" t="n"/>
@@ -2064,22 +2052,22 @@
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>misreading.closing[0]</t>
+          <t>reading.steps[2]</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>The body speaks first.</t>
+          <t>Check your shoulders.</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Le corps parle d’abord.</t>
+          <t>Observez vos épaules.</t>
         </is>
       </c>
       <c r="E59" s="11" t="n"/>
@@ -2088,82 +2076,82 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>misreading.closing[1]</t>
+          <t>reading.result</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>The mind explains second.</t>
+          <t>What you found is a reading.</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>L’esprit explique ensuite.</t>
+          <t>Ce que vous avez trouvé, c’est une lecture.</t>
         </is>
       </c>
       <c r="E60" s="11" t="n"/>
       <c r="F60" s="11" t="n"/>
     </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>reading.eyebrow</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>Try something right now</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>Essayez quelque chose tout de suite</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="n"/>
-      <c r="F62" s="11" t="n"/>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>reading.folio</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>TIME. ATTENTION. SAFETY. — THE THREE VARIABLES</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>reading.lead</t>
+          <t>variables.sortingLines[0]</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Whatever you are feeling as you read this sentence.</t>
+          <t>They are not brain regions or neural pathways.</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Quoi que vous ressentiez en lisant cette phrase.</t>
+          <t>Ce ne sont pas des régions du cerveau ni des voies neuronales.</t>
         </is>
       </c>
       <c r="E63" s="11" t="n"/>
@@ -2172,22 +2160,22 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[0]</t>
+          <t>variables.sortingLines[1]</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Check your jaw.</t>
+          <t>They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Observez votre mâchoire.</t>
+          <t>C’est un outil de tri, une façon de poser trois questions quand tout semble aller de travers en même temps.</t>
         </is>
       </c>
       <c r="E64" s="11" t="n"/>
@@ -2196,46 +2184,46 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[1]</t>
+          <t>variables.loops[0].name</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Check your breath.</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Observez votre respiration.</t>
+          <t>Temps</t>
         </is>
       </c>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
     </row>
-    <row r="66" ht="30" customHeight="1">
+    <row r="66" ht="45" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[2]</t>
+          <t>variables.loops[0].body</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Check your shoulders.</t>
+          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Observez vos épaules.</t>
+          <t>Sommeil, alimentation, caféine, phase circadienne, récupération. Quand le rythme est décalé, la sensibilité de base augmente. Le même monde paraît plus dur.</t>
         </is>
       </c>
       <c r="E66" s="11" t="n"/>
@@ -2244,22 +2232,22 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>reading.result</t>
+          <t>variables.loops[1].name</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>What you found is a reading.</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Ce que vous avez trouvé, c’est une lecture.</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="E67" s="11" t="n"/>
@@ -2268,22 +2256,22 @@
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>reading.afterResult</t>
+          <t>variables.loops[1].body</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
+          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Une lecture de l’instrument qui interprète tout ce qui vous entoure, en ce moment, y compris ces mots. La lecture est peut-être exacte. Peut-être pas. Vous ne pouvez pas le savoir tant que vous n’avez pas vu les réglages.</t>
+          <t>Le système qui suit la récompense, la nouveauté et le prochain déclencheur. Quand il est accaparé, l’attention se resserre sur ce qu’il y a de moins exigeant à portée de main, et le travail exigeant paraît difficile.</t>
         </is>
       </c>
       <c r="E68" s="11" t="n"/>
@@ -2292,166 +2280,178 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>reading.question</t>
+          <t>variables.loops[2].name</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this the state?</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Est-ce la situation ? Ou est-ce l’état ?</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
     </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>THE BOOK — THE AUTHOR’S LINE, WHO IT IS FOR</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
-      <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="n"/>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Time. Attention. Safety. — the three variables</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>variables.loops[2].body</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>The system that monitors threat, and especially social threat. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Le système qui surveille la menace, et surtout la menace sociale. Il est rapide, il est ancien, et il penche du côté des fausses alertes. Il produit des interprétations qui donnent l’impression d’être des faits.</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="n"/>
+      <c r="F70" s="11" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>The book — the author’s line, who it is for</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>book.eyebrow</t>
+          <t>variables.folio</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Le livre</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E71" s="11" t="n"/>
       <c r="F71" s="11" t="n"/>
     </row>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>The book — the author’s line, who it is for</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>book.paragraphs[0]</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="n"/>
-      <c r="F72" s="11" t="n"/>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>THREE MOMENTS — THE PRINTED CASE PAGES</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>The book — the author’s line, who it is for</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>book.readersEyebrow</t>
+          <t>moments.line</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Who it is for</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>À qui il s’adresse</t>
+          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
         </is>
       </c>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
     </row>
-    <row r="74" ht="75" customHeight="1">
+    <row r="74" ht="30" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>The book — the author’s line, who it is for</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>book.readers</t>
+          <t>moments.label</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+          <t>Case evidence</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Pour quiconque a déjà été certain du sens d’une situation, puis a découvert qu’il se passait autre chose. Et pour les lecteurs qui s’intéressent à la psychologie de notre façon de remarquer, d’interpréter et de revoir le monde qui nous entoure.</t>
+          <t>Pièces du dossier</t>
         </is>
       </c>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="n"/>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Three moments — the printed case pages</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>moments.pageLabel</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="11" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>excerpt.eyebrow</t>
+          <t>moments.items[0].quote</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>“Something is off.”</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Lire</t>
+          <t>« Quelque chose cloche. »</t>
         </is>
       </c>
       <c r="E76" s="11" t="n"/>
@@ -2460,22 +2460,22 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>excerpt.title</t>
+          <t>moments.items[0].inputLabel</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Before the chapters</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Avant les chapitres</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E77" s="11" t="n"/>
@@ -2484,22 +2484,22 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>excerpt.sectionLabel</t>
+          <t>moments.items[0].input</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>The pilot</t>
+          <t>Two minutes before the alarm.</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Le pilote</t>
+          <t>Deux minutes avant le réveil.</t>
         </is>
       </c>
       <c r="E78" s="11" t="n"/>
@@ -2508,22 +2508,22 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>excerpt.runningHead</t>
+          <t>moments.items[0].verifiedLabel</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>Verified event</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>Événement vérifié</t>
         </is>
       </c>
       <c r="E79" s="11" t="n"/>
@@ -2532,22 +2532,22 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>excerpt.cta</t>
+          <t>moments.items[0].verified</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>Nothing has happened.</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Lire un extrait</t>
+          <t>Il ne s’est rien passé.</t>
         </is>
       </c>
       <c r="E80" s="11" t="n"/>
@@ -2556,22 +2556,22 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>excerpt.continueCta</t>
+          <t>moments.items[1].quote</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Continue reading</t>
+          <t>“ok.”</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Lire la suite</t>
+          <t>« ok. »</t>
         </is>
       </c>
       <c r="E81" s="11" t="n"/>
@@ -2580,22 +2580,22 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>excerpt.back</t>
+          <t>moments.items[1].inputLabel</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Retour au livre</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E82" s="11" t="n"/>
@@ -2604,214 +2604,214 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>excerpt.readingModeLabel</t>
+          <t>moments.items[1].input</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Reading mode</t>
+          <t>Two letters. One full stop.</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Mode lecture</t>
+          <t>Deux lettres. Un point.</t>
         </is>
       </c>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
     </row>
-    <row r="84" ht="105" customHeight="1">
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[0]</t>
+          <t>moments.items[1].verifiedLabel</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
+          <t>Verified tone</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Le soir du 16 juillet 1999, un petit avion monomoteur décolla du New Jersey. Il faisait route vers Martha’s Vineyard. Le pilote avait assez d’expérience pour être sûr de lui, et assez peu pour se tromper sur ce que valait cette assurance. Il avait environ 300 heures de vol. Il n’avait pas terminé la formation qui l’aurait qualifié pour voler aux seuls instruments.</t>
+          <t>Ton vérifié</t>
         </is>
       </c>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
     </row>
-    <row r="85" ht="225" customHeight="1">
+    <row r="85" ht="30" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[1]</t>
+          <t>moments.items[1].verified</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Le ciel était dégagé au départ, alors il en conclut qu’il n’avait pas besoin d’instruments. Le temps qu’il atteigne la côte, il ne l’était plus. Une brume s’était posée sur l’eau. Le genre de brume qui efface la limite entre la mer et le ciel si progressivement que vous ne remarquez pas que l’horizon a disparu, jusqu’au moment où vous le cherchez et où il n’est plus là. Au-dessus des terres, cela n’a pas d’importance. Il y a des lumières en dessous. Vous voyez des routes, des bâtiments, une géométrie qui dit à vos yeux où est le bas. Au large, la nuit, avec la brume posée sur la surface comme une seconde obscurité, il n’y a rien. Hors du cockpit, le monde devient un gris uniforme dans toutes les directions. Le haut ressemble au bas. Un léger virage donne la sensation d’un vol en palier. Une descente lente donne la sensation de tenir l’altitude.</t>
+          <t>Aucun.</t>
         </is>
       </c>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
     </row>
-    <row r="86" ht="150" customHeight="1">
+    <row r="86" ht="30" customHeight="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[2]</t>
+          <t>moments.items[2].quote</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+          <t>“Something is wrong with my life.”</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>L’oreille interne du pilote, l’organe qui dit au cerveau dans quel sens le corps est orienté dans l’espace, fonctionne en détectant les changements de mouvement. Quand vous entrez en virage, le liquide à l’intérieur de l’oreille se déplace, et le cerveau enregistre une rotation. Mais si le virage se maintient pendant quinze ou vingt secondes, le liquide de l’oreille interne se stabilise. Il ne bouge plus. Le cerveau, qui suit le mouvement et non la position, en conclut que le virage est terminé. Vous vous sentez en palier, mais vous ne l’êtes pas.</t>
+          <t>« Quelque chose ne va pas dans ma vie. »</t>
         </is>
       </c>
       <c r="E86" s="11" t="n"/>
       <c r="F86" s="11" t="n"/>
     </row>
-    <row r="87" ht="150" customHeight="1">
+    <row r="87" ht="30" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[3]</t>
+          <t>moments.items[2].inputLabel</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Quelque part au-dessus de l’eau sombre, l’avion s’engagea dans un léger virage à gauche. Les instruments du pilote, les cadrans du tableau de bord devant lui, indiquaient le virage. L’horizon artificiel, un petit cadran gyroscopique qui montre l’angle de l’appareil par rapport au sol, lui disait qu’il s’inclinait. L’altimètre lui disait qu’il descendait. L’indicateur de vitesse lui disait qu’il accélérait. Son corps lui disait autre chose. Son corps lui disait qu’il volait droit et en palier. Son corps sonnait juste. Ses instruments sonnaient faux. Il fit confiance à son corps.</t>
+          <t>Entrée</t>
         </is>
       </c>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="11" t="n"/>
     </row>
-    <row r="88" ht="120" customHeight="1">
+    <row r="88" ht="30" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[4]</t>
+          <t>moments.items[2].input</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
+          <t>Six ordinary events. One depleted day.</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Le virage se resserra. Le nez tomba. La vitesse augmenta. Dans les dernières secondes, l’avion descendait à plus de 4 700 pieds par minute, près d’un kilomètre et demi toutes les soixante secondes, dans une spirale de plus en plus serrée que les pilotes appellent, avec la précision sinistre d’un métier qui a donné un nom aux façons dont il perd les siens, une spirale de la mort. Il percuta l’eau à pleine vitesse. Lui et ses deux passagers furent tués sur le coup.</t>
+          <t>Six événements ordinaires. Une journée à plat.</t>
         </is>
       </c>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
     </row>
-    <row r="89" ht="135" customHeight="1">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[5]</t>
+          <t>moments.items[2].verifiedLabel</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
+          <t>Verified crisis</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>L’enquête ne releva aucune défaillance mécanique. Le moteur tournait. Les instruments fonctionnaient. Les données étaient là, sur le tableau de bord, à quinze centimètres de ses yeux, depuis le début, mais il ne les lut pas. Il lut son corps à la place. La consigne que la Federal Aviation Administration américaine donne aux pilotes qui se retrouvent dans cette situation tient en une phrase. C’est une consigne à prendre au pied de la lettre, et elle s’applique à votre vie aussi directement qu’à un cockpit :</t>
+          <t>Crise vérifiée</t>
         </is>
       </c>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
     </row>
-    <row r="90" ht="60" customHeight="1">
+    <row r="90" ht="30" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[6]</t>
+          <t>moments.items[2].verified</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Le pilote s’appelait John F. Kennedy Jr. C’était le fils d’un président américain. On lui avait déconseillé de voler ce soir-là sans son instructeur. Il avait dit à son instructeur qu’il voulait le faire seul. Il avait trente-huit ans.</t>
+          <t>Aucune.</t>
         </is>
       </c>
       <c r="E90" s="11" t="n"/>
       <c r="F90" s="11" t="n"/>
     </row>
-    <row r="91" ht="240" customHeight="1">
+    <row r="91" ht="30" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[7]</t>
+          <t>moments.closing</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
+          <t>It said I am failing; the data was I am tired.</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Vous pilotez un corps qui produit des signaux, et votre esprit prend souvent ces signaux pour la vérité. Les signaux se trompent parfois autant que le système vestibulaire de l’oreille interne au-dessus de l’eau sombre. La fatigue qui se présente comme une question sur votre carrière. Le pic de caféine qui se présente comme de l’anxiété à propos d’un e-mail. Le manque de sucre dans le sang qui se présente comme la preuve que votre relation est en train de se défaire. Votre corps parle d’abord et votre esprit explique ensuite. L’explication, parce qu’elle arrive avec tout le poids de la conviction physique, la mâchoire serrée, le cœur qui bat vite, la chaleur derrière les oreilles, donne l’impression d’un savoir profond. Vous avez l’impression de lire la situation. Mais vous ne lisez que l’instrument qui lit la situation, et les réglages de l’instrument étaient faussés avant que la situation n’arrive. Ces instruments existent. Vous les avez. Le rythme cardiaque, la tension de la mâchoire, la profondeur de la respiration, la position des épaules, la vitesse de vos pensées. Ils produisent des données en ce moment même, pendant que vous lisez cette phrase. Mais le bulletin météo plein d’assurance que le corps établit sur le monde n’est qu’un brouillon.</t>
+          <t>Ça disait je suis en train d’échouer ; les données, c’était je suis fatiguée.</t>
         </is>
       </c>
       <c r="E91" s="11" t="n"/>
@@ -2820,70 +2820,58 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>excerpt.quote</t>
+          <t>moments.closingSource</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>« ayez confiance en vos instruments et ne tenez aucun compte des signaux contradictoires que vous envoie votre corps. »</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
     </row>
-    <row r="93" ht="135" customHeight="1">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>excerpt.closing</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>Ce livre parle de la même erreur à l’échelle de la cuisine. La version qui arrive tous les mardis. La version où votre corps écrit une histoire à propos d’un message, d’un silence, d’un regard, et où votre esprit retouche cette histoire sous la supervision de ce que votre corps ressent à ce moment-là. Personne ne meurt, mais des décisions se prennent. Des relations changent. Des jugements sur soi se forment. Et rien de tout cela n’avait à se passer ainsi, parce que les données étaient là depuis le début.</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="n"/>
-      <c r="F93" s="11" t="n"/>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>EVIDENCE — THE BOOK'S CONFIDENCE MARKERS</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closingSource</t>
+          <t>evidence.title</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>Niveau de preuve</t>
         </is>
       </c>
       <c r="E94" s="11" t="n"/>
@@ -2892,22 +2880,22 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>excerpt.endNote</t>
+          <t>evidence.grades[0].label</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Vient ensuite le chapitre zéro : Une journée qui aurait dû bien se passer.</t>
+          <t>Élevé</t>
         </is>
       </c>
       <c r="E95" s="11" t="n"/>
@@ -2916,22 +2904,22 @@
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>excerpt.unavailable</t>
+          <t>evidence.grades[0].description</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>The extract in this language will follow.</t>
+          <t>Replicated or robust evidence.</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>L’extrait en français est à venir.</t>
+          <t>Résultats répliqués ou robustes.</t>
         </is>
       </c>
       <c r="E96" s="11" t="n"/>
@@ -2940,22 +2928,22 @@
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[0]</t>
+          <t>evidence.grades[1].label</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Moyen</t>
         </is>
       </c>
       <c r="E97" s="11" t="n"/>
@@ -2964,22 +2952,22 @@
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[1]</t>
+          <t>evidence.grades[1].description</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Suggestive evidence with meaningful uncertainty.</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Preuves partielles, incertitude réelle.</t>
         </is>
       </c>
       <c r="E98" s="11" t="n"/>
@@ -2988,58 +2976,70 @@
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[2]</t>
+          <t>evidence.grades[2].label</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Faible</t>
         </is>
       </c>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
     </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>CASE EVIDENCE CARDS</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Evidence — the book's confidence markers</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>evidence.grades[2].description</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Plausible hypothesis or emerging evidence.</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Hypothèse plausible ou premiers résultats.</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="11" t="n"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>cases.eyebrow</t>
+          <t>evidence.closing</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Case evidence</t>
+          <t>These markers exist because the book’s own risk is the same risk it describes.</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Pièces du dossier</t>
+          <t>Ces marqueurs existent parce que le risque que court ce livre est celui-là même qu’il décrit.</t>
         </is>
       </c>
       <c r="E101" s="11" t="n"/>
@@ -3048,70 +3048,58 @@
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>cases.pageLabel</t>
+          <t>evidence.folio</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
     </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>cases.items[0].quote</t>
-        </is>
-      </c>
-      <c r="C103" s="10" t="inlineStr">
-        <is>
-          <t>“Something is off.”</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>« Quelque chose cloche. »</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="n"/>
-      <c r="F103" s="11" t="n"/>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>THE EXTRACT — THE OPENING PAGES OF THE BOOK</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="8" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].inputLabel</t>
+          <t>excerpt.title</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Before the chapters</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Avant les chapitres</t>
         </is>
       </c>
       <c r="E104" s="11" t="n"/>
@@ -3120,238 +3108,238 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].input</t>
+          <t>excerpt.sectionLabel</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Two minutes before the alarm.</t>
+          <t>The pilot</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Deux minutes avant le réveil.</t>
+          <t>Le pilote</t>
         </is>
       </c>
       <c r="E105" s="11" t="n"/>
       <c r="F105" s="11" t="n"/>
     </row>
-    <row r="106" ht="30" customHeight="1">
+    <row r="106" ht="45" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verifiedLabel</t>
+          <t>excerpt.lead</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Verified event</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Événement vérifié</t>
+          <t>Ce livre cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
         </is>
       </c>
       <c r="E106" s="11" t="n"/>
       <c r="F106" s="11" t="n"/>
     </row>
-    <row r="107" ht="30" customHeight="1">
+    <row r="107" ht="105" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verified</t>
+          <t>excerpt.paragraphs[0]</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Nothing has happened.</t>
+          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>Il ne s’est rien passé.</t>
+          <t>Le soir du 16 juillet 1999, un petit avion monomoteur décolla du New Jersey. Il faisait route vers Martha’s Vineyard. Le pilote avait assez d’expérience pour être sûr de lui, et assez peu pour se tromper sur ce que valait cette assurance. Il avait environ 300 heures de vol. Il n’avait pas terminé la formation qui l’aurait qualifié pour voler aux seuls instruments.</t>
         </is>
       </c>
       <c r="E107" s="11" t="n"/>
       <c r="F107" s="11" t="n"/>
     </row>
-    <row r="108" ht="30" customHeight="1">
+    <row r="108" ht="225" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].quote</t>
+          <t>excerpt.paragraphs[1]</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>“ok.”</t>
+          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>« ok. »</t>
+          <t>Le ciel était dégagé au départ, alors il en conclut qu’il n’avait pas besoin d’instruments. Le temps qu’il atteigne la côte, il ne l’était plus. Une brume s’était posée sur l’eau. Le genre de brume qui efface la limite entre la mer et le ciel si progressivement que vous ne remarquez pas que l’horizon a disparu, jusqu’au moment où vous le cherchez et où il n’est plus là. Au-dessus des terres, cela n’a pas d’importance. Il y a des lumières en dessous. Vous voyez des routes, des bâtiments, une géométrie qui dit à vos yeux où est le bas. Au large, la nuit, avec la brume posée sur la surface comme une seconde obscurité, il n’y a rien. Hors du cockpit, le monde devient un gris uniforme dans toutes les directions. Le haut ressemble au bas. Un léger virage donne la sensation d’un vol en palier. Une descente lente donne la sensation de tenir l’altitude.</t>
         </is>
       </c>
       <c r="E108" s="11" t="n"/>
       <c r="F108" s="11" t="n"/>
     </row>
-    <row r="109" ht="30" customHeight="1">
+    <row r="109" ht="150" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].inputLabel</t>
+          <t>excerpt.paragraphs[2]</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>L’oreille interne du pilote, l’organe qui dit au cerveau dans quel sens le corps est orienté dans l’espace, fonctionne en détectant les changements de mouvement. Quand vous entrez en virage, le liquide à l’intérieur de l’oreille se déplace, et le cerveau enregistre une rotation. Mais si le virage se maintient pendant quinze ou vingt secondes, le liquide de l’oreille interne se stabilise. Il ne bouge plus. Le cerveau, qui suit le mouvement et non la position, en conclut que le virage est terminé. Vous vous sentez en palier, mais vous ne l’êtes pas.</t>
         </is>
       </c>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
     </row>
-    <row r="110" ht="30" customHeight="1">
+    <row r="110" ht="150" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].input</t>
+          <t>excerpt.paragraphs[3]</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Two letters. One full stop.</t>
+          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Deux lettres. Un point.</t>
+          <t>Quelque part au-dessus de l’eau sombre, l’avion s’engagea dans un léger virage à gauche. Les instruments du pilote, les cadrans du tableau de bord devant lui, indiquaient le virage. L’horizon artificiel, un petit cadran gyroscopique qui montre l’angle de l’appareil par rapport au sol, lui disait qu’il s’inclinait. L’altimètre lui disait qu’il descendait. L’indicateur de vitesse lui disait qu’il accélérait. Son corps lui disait autre chose. Son corps lui disait qu’il volait droit et en palier. Son corps sonnait juste. Ses instruments sonnaient faux. Il fit confiance à son corps.</t>
         </is>
       </c>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
     </row>
-    <row r="111" ht="30" customHeight="1">
+    <row r="111" ht="120" customHeight="1">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verifiedLabel</t>
+          <t>excerpt.paragraphs[4]</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Verified tone</t>
+          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Ton vérifié</t>
+          <t>Le virage se resserra. Le nez tomba. La vitesse augmenta. Dans les dernières secondes, l’avion descendait à plus de 4 700 pieds par minute, près d’un kilomètre et demi toutes les soixante secondes, dans une spirale de plus en plus serrée que les pilotes appellent, avec la précision sinistre d’un métier qui a donné un nom aux façons dont il perd les siens, une spirale de la mort. Il percuta l’eau à pleine vitesse. Lui et ses deux passagers furent tués sur le coup.</t>
         </is>
       </c>
       <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
     </row>
-    <row r="112" ht="30" customHeight="1">
+    <row r="112" ht="135" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verified</t>
+          <t>excerpt.paragraphs[5]</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Aucun.</t>
+          <t>L’enquête ne releva aucune défaillance mécanique. Le moteur tournait. Les instruments fonctionnaient. Les données étaient là, sur le tableau de bord, à quinze centimètres de ses yeux, depuis le début, mais il ne les lut pas. Il lut son corps à la place. La consigne que la Federal Aviation Administration américaine donne aux pilotes qui se retrouvent dans cette situation tient en une phrase. C’est une consigne à prendre au pied de la lettre, et elle s’applique à votre vie aussi directement qu’à un cockpit :</t>
         </is>
       </c>
       <c r="E112" s="11" t="n"/>
       <c r="F112" s="11" t="n"/>
     </row>
-    <row r="113" ht="30" customHeight="1">
+    <row r="113" ht="60" customHeight="1">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].quote</t>
+          <t>excerpt.paragraphs[6]</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>“Something is wrong with my life.”</t>
+          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>« Quelque chose ne va pas dans ma vie. »</t>
+          <t>Le pilote s’appelait John F. Kennedy Jr. C’était le fils d’un président américain. On lui avait déconseillé de voler ce soir-là sans son instructeur. Il avait dit à son instructeur qu’il voulait le faire seul. Il avait trente-huit ans.</t>
         </is>
       </c>
       <c r="E113" s="11" t="n"/>
       <c r="F113" s="11" t="n"/>
     </row>
-    <row r="114" ht="30" customHeight="1">
+    <row r="114" ht="240" customHeight="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].inputLabel</t>
+          <t>excerpt.paragraphs[7]</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Vous pilotez un corps qui produit des signaux, et votre esprit prend souvent ces signaux pour la vérité. Les signaux se trompent parfois autant que le système vestibulaire de l’oreille interne au-dessus de l’eau sombre. La fatigue qui se présente comme une question sur votre carrière. Le pic de caféine qui se présente comme de l’anxiété à propos d’un e-mail. Le manque de sucre dans le sang qui se présente comme la preuve que votre relation est en train de se défaire. Votre corps parle d’abord et votre esprit explique ensuite. L’explication, parce qu’elle arrive avec tout le poids de la conviction physique, la mâchoire serrée, le cœur qui bat vite, la chaleur derrière les oreilles, donne l’impression d’un savoir profond. Vous avez l’impression de lire la situation. Mais vous ne lisez que l’instrument qui lit la situation, et les réglages de l’instrument étaient faussés avant que la situation n’arrive. Ces instruments existent. Vous les avez. Le rythme cardiaque, la tension de la mâchoire, la profondeur de la respiration, la position des épaules, la vitesse de vos pensées. Ils produisent des données en ce moment même, pendant que vous lisez cette phrase. Mais le bulletin météo plein d’assurance que le corps établit sur le monde n’est qu’un brouillon.</t>
         </is>
       </c>
       <c r="E114" s="11" t="n"/>
@@ -3360,22 +3348,22 @@
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].input</t>
+          <t>excerpt.quote</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Six ordinary events. One depleted day.</t>
+          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Six événements ordinaires. Une journée à plat.</t>
+          <t>« ayez confiance en vos instruments et ne tenez aucun compte des signaux contradictoires que vous envoie votre corps. »</t>
         </is>
       </c>
       <c r="E115" s="11" t="n"/>
@@ -3384,22 +3372,22 @@
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verifiedLabel</t>
+          <t>excerpt.continueCta</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Verified crisis</t>
+          <t>Continue reading</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Crise vérifiée</t>
+          <t>Lire la suite</t>
         </is>
       </c>
       <c r="E116" s="11" t="n"/>
@@ -3408,22 +3396,22 @@
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verified</t>
+          <t>excerpt.back</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Aucune.</t>
+          <t>Retour au livre</t>
         </is>
       </c>
       <c r="E117" s="11" t="n"/>
@@ -3432,46 +3420,46 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].quote</t>
+          <t>excerpt.readingModeLabel</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>“This is state, not situation.”</t>
+          <t>Reading mode</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>« C’est l’état, pas la situation. »</t>
+          <t>Mode lecture</t>
         </is>
       </c>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="11" t="n"/>
     </row>
-    <row r="119" ht="30" customHeight="1">
+    <row r="119" ht="135" customHeight="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].inputLabel</t>
+          <t>excerpt.closing</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Entrée</t>
+          <t>Ce livre parle de la même erreur à l’échelle de la cuisine. La version qui arrive tous les mardis. La version où votre corps écrit une histoire à propos d’un message, d’un silence, d’un regard, et où votre esprit retouche cette histoire sous la supervision de ce que votre corps ressent à ce moment-là. Personne ne meurt, mais des décisions se prennent. Des relations changent. Des jugements sur soi se forment. Et rien de tout cela n’avait à se passer ainsi, parce que les données étaient là depuis le début.</t>
         </is>
       </c>
       <c r="E119" s="11" t="n"/>
@@ -3480,22 +3468,22 @@
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].input</t>
+          <t>excerpt.closingSource</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Low fuel. Dead light. A sound on grit.</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Réservoir bas. Néon mort. Un bruit sur le gravier.</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="E120" s="11" t="n"/>
@@ -3504,22 +3492,22 @@
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verifiedLabel</t>
+          <t>excerpt.endNote</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Verified threat</t>
+          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Menace vérifiée</t>
+          <t>Vient ensuite le chapitre zéro : Une journée qui aurait dû bien se passer.</t>
         </is>
       </c>
       <c r="E121" s="11" t="n"/>
@@ -3528,22 +3516,22 @@
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verified</t>
+          <t>excerpt.unavailable</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Not yet visible.</t>
+          <t>The extract in this language will follow.</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Pas encore visible.</t>
+          <t>L’extrait en français est à venir.</t>
         </is>
       </c>
       <c r="E122" s="11" t="n"/>
@@ -3552,22 +3540,22 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>cases.closing</t>
+          <t>excerpt.folios[0]</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>It said I am failing; the data was I am tired.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>Ça disait je suis en train d’échouer ; les données, c’était je suis fatiguée.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E123" s="11" t="n"/>
@@ -3576,62 +3564,62 @@
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>cases.closingSource</t>
+          <t>excerpt.folios[1]</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
     </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>The extract — the opening pages of the book</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.folios[2]</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n"/>
+      <c r="F125" s="11" t="n"/>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="n"/>
-      <c r="C125" s="8" t="n"/>
-      <c r="D125" s="8" t="n"/>
-      <c r="E125" s="8" t="n"/>
-      <c r="F125" s="8" t="n"/>
-    </row>
-    <row r="126" ht="30" customHeight="1">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>Audio player (hidden until a recording exists)</t>
-        </is>
-      </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>listen.eyebrow</t>
-        </is>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
-        <is>
-          <t>Listen</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
-        <is>
-          <t>Écouter</t>
-        </is>
-      </c>
-      <c r="E126" s="11" t="n"/>
-      <c r="F126" s="11" t="n"/>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="8" t="n"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="9" t="inlineStr">
@@ -3641,17 +3629,17 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>listen.title</t>
+          <t>listen.eyebrow</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Listen to an extract</t>
+          <t>Listen</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Écouter un extrait</t>
+          <t>Écouter</t>
         </is>
       </c>
       <c r="E127" s="11" t="n"/>
@@ -3665,17 +3653,17 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>listen.subtitle</t>
+          <t>listen.title</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Read by the author</t>
+          <t>Listen to an extract</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Lu par l’autrice</t>
+          <t>Écouter un extrait</t>
         </is>
       </c>
       <c r="E128" s="11" t="n"/>
@@ -3689,17 +3677,17 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>listen.play</t>
+          <t>listen.subtitle</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Read by the author</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Écouter</t>
+          <t>Lu par l’autrice</t>
         </is>
       </c>
       <c r="E129" s="11" t="n"/>
@@ -3713,17 +3701,17 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>listen.pause</t>
+          <t>listen.play</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Écouter</t>
         </is>
       </c>
       <c r="E130" s="11" t="n"/>
@@ -3737,17 +3725,17 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>listen.progress</t>
+          <t>listen.pause</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Playback position</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Position dans l’enregistrement</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="E131" s="11" t="n"/>
@@ -3761,17 +3749,17 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>listen.elapsed</t>
+          <t>listen.progress</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Elapsed</t>
+          <t>Playback position</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Écoulé</t>
+          <t>Position dans l’enregistrement</t>
         </is>
       </c>
       <c r="E132" s="11" t="n"/>
@@ -3785,17 +3773,17 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>listen.duration</t>
+          <t>listen.elapsed</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Elapsed</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>Durée</t>
+          <t>Écoulé</t>
         </is>
       </c>
       <c r="E133" s="11" t="n"/>
@@ -3809,77 +3797,77 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>listen.unavailable</t>
+          <t>listen.duration</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>The recording will be added here.</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>L’enregistrement sera ajouté ici.</t>
+          <t>Durée</t>
         </is>
       </c>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
     </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>THE INVESTIGATION (PAGE 11), “BEFORE WE BEGIN” (PAGE 13 MARKERS), THE THREE SYSTEMS, PAGE 226</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="n"/>
-      <c r="C135" s="8" t="n"/>
-      <c r="D135" s="8" t="n"/>
-      <c r="E135" s="8" t="n"/>
-      <c r="F135" s="8" t="n"/>
-    </row>
-    <row r="136" ht="30" customHeight="1">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="inlineStr">
-        <is>
-          <t>map.eyebrow</t>
-        </is>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>A map of the book</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Une carte du livre</t>
-        </is>
-      </c>
-      <c r="E136" s="11" t="n"/>
-      <c r="F136" s="11" t="n"/>
-    </row>
-    <row r="137" ht="90" customHeight="1">
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Audio player (hidden until a recording exists)</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>listen.unavailable</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>The recording will be added here.</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>L’enregistrement sera ajouté ici.</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="n"/>
+      <c r="F135" s="11" t="n"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>ABOUT THE AUTHOR</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n"/>
+      <c r="C136" s="8" t="n"/>
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="8" t="n"/>
+      <c r="F136" s="8" t="n"/>
+    </row>
+    <row r="137" ht="30" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>map.sortingTool</t>
+          <t>author.title</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Les chapitres qui suivent sont organisés autour de trois systèmes qui règlent le poids que prennent les signaux de votre corps avant que votre esprit ne construise une histoire. Ce ne sont pas des régions du cerveau ni des voies neuronales. C’est un outil de tri, une façon de poser trois questions quand tout semble aller de travers en même temps.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E137" s="11" t="n"/>
@@ -3888,46 +3876,46 @@
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].name</t>
+          <t>author.photoAlt</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Ivana Budišin, photographed against a dark grey background.</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Temps</t>
+          <t>Ivana Budišin, photographiée sur fond gris foncé.</t>
         </is>
       </c>
       <c r="E138" s="11" t="n"/>
       <c r="F138" s="11" t="n"/>
     </row>
-    <row r="139" ht="45" customHeight="1">
+    <row r="139" ht="30" customHeight="1">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].body</t>
+          <t>author.photoPlaceholder</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
+          <t>Author photograph to follow</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Sommeil, alimentation, caféine, phase circadienne, récupération. Quand le rythme est décalé, la sensibilité de base augmente. Le même monde paraît plus dur.</t>
+          <t>Photographie de l’autrice à venir</t>
         </is>
       </c>
       <c r="E139" s="11" t="n"/>
@@ -3936,46 +3924,46 @@
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].name</t>
+          <t>author.bio</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
         </is>
       </c>
       <c r="E140" s="11" t="n"/>
       <c r="F140" s="11" t="n"/>
     </row>
-    <row r="141" ht="60" customHeight="1">
+    <row r="141" ht="75" customHeight="1">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].body</t>
+          <t>author.readers</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Le système qui suit la récompense, la nouveauté et le prochain déclencheur. Quand il est accaparé, l’attention se resserre sur ce qu’il y a de moins exigeant à portée de main, et le travail exigeant paraît difficile.</t>
+          <t>Pour quiconque a déjà été certain du sens d’une situation, puis a découvert qu’il se passait autre chose. Et pour les lecteurs qui s’intéressent à la psychologie de notre façon de remarquer, d’interpréter et de revoir le monde qui nous entoure.</t>
         </is>
       </c>
       <c r="E141" s="11" t="n"/>
@@ -3984,166 +3972,142 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].name</t>
+          <t>author.pressLabel</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Dossier de presse</t>
         </is>
       </c>
       <c r="E142" s="11" t="n"/>
       <c r="F142" s="11" t="n"/>
     </row>
-    <row r="143" ht="75" customHeight="1">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>map.loops[2].body</t>
-        </is>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
-        <is>
-          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
-        <is>
-          <t>Le système qui surveille la menace, et surtout la menace sociale. Des choses comme l’évaluation sociale, l’exclusion, l’ambiguïté, le statut. Il est rapide, il est ancien, et il penche du côté des fausses alertes. Il produit des interprétations qui ressemblent à des faits.</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="n"/>
-      <c r="F143" s="11" t="n"/>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>THE CLOSING QUESTION AND THE PUBLICATION UPDATES FORM</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="n"/>
+      <c r="C143" s="8" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="8" t="n"/>
+      <c r="F143" s="8" t="n"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>The closing question and the publication updates form</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceEyebrow</t>
+          <t>closing.question</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Before we begin</t>
+          <t>Is this the situation? Or is this their state?</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>Avant de commencer</t>
+          <t>Est-ce la situation ? Ou est-ce leur état ?</t>
         </is>
       </c>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
     </row>
-    <row r="145" ht="120" customHeight="1">
+    <row r="145" ht="30" customHeight="1">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>The closing question and the publication updates form</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceIntro</t>
+          <t>closing.source</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
+          <t>Page 225</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>Ce livre avance des affirmations sur le cerveau et sur le corps, et ces affirmations ne sont pas toutes également étayées. Certaines s’appuient sur des décennies de recherches répliquées. Certaines s’appuient sur des résultats plus récents, prometteurs mais pas encore consolidés. Certaines sont des prolongements plausibles d’une science établie, qui n’ont pas été testés directement sous la forme précise que décrit ce livre. Vous devriez savoir lesquelles sont lesquelles.</t>
+          <t>Page 225</t>
         </is>
       </c>
       <c r="E145" s="11" t="n"/>
       <c r="F145" s="11" t="n"/>
     </row>
-    <row r="146" ht="180" customHeight="1">
+    <row r="146" ht="30" customHeight="1">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>The closing question and the publication updates form</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceMarkers</t>
+          <t>closing.line</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
+          <t>Same life. Different instrument settings.</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>Tout au long du livre, les affirmations scientifiques portent un marqueur de confiance. Quand un résultat est solidement étayé et répliqué, vous verrez un repère indiquant un niveau de preuve élevé, sous la forme d’un pouls rouge profond dans la marge. Quand les preuves vont dans le sens de l’affirmation mais restent incomplètes, le niveau de preuve est noté moyen, avec un pouls orange. Quand une affirmation est une hypothèse plausible qui demande des tests plus poussés, elle est marquée faible, en gris délavé. Ces marqueurs existent parce que le risque que court ce livre est celui-là même qu’il décrit. Il ne veut pas traiter une histoire plausible comme une vérité établie. Ces marqueurs sont un frein à cela.</t>
+          <t>Même vie. Instruments réglés autrement.</t>
         </is>
       </c>
       <c r="E146" s="11" t="n"/>
       <c r="F146" s="11" t="n"/>
     </row>
-    <row r="147" ht="30" customHeight="1">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>map.grades[0].label</t>
-        </is>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D147" s="10" t="inlineStr">
-        <is>
-          <t>Élevé</t>
-        </is>
-      </c>
-      <c r="E147" s="11" t="n"/>
-      <c r="F147" s="11" t="n"/>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>PRESS PAGE</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n"/>
+      <c r="C147" s="8" t="n"/>
+      <c r="D147" s="8" t="n"/>
+      <c r="E147" s="8" t="n"/>
+      <c r="F147" s="8" t="n"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>map.grades[1].label</t>
+          <t>press.eyebrow</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E148" s="11" t="n"/>
@@ -4152,46 +4116,46 @@
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>map.grades[2].label</t>
+          <t>press.title</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Faible</t>
+          <t>Dossier de presse</t>
         </is>
       </c>
       <c r="E149" s="11" t="n"/>
       <c r="F149" s="11" t="n"/>
     </row>
-    <row r="150" ht="30" customHeight="1">
+    <row r="150" ht="45" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>map.investigationTitle</t>
+          <t>press.intro</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>The Investigation</t>
+          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>L’enquête</t>
+          <t>Des exemplaires de presse, papier et numérique, sont disponibles sur demande. Reproduction d’extraits, entretiens et rencontres à convenir.</t>
         </is>
       </c>
       <c r="E150" s="11" t="n"/>
@@ -4200,22 +4164,22 @@
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>map.mapLine</t>
+          <t>press.contactHeading</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E151" s="11" t="n"/>
@@ -4224,22 +4188,22 @@
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>map.pageColumn</t>
+          <t>press.assetsHeading</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Téléchargements</t>
         </is>
       </c>
       <c r="E152" s="11" t="n"/>
@@ -4248,22 +4212,22 @@
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[0].title</t>
+          <t>press.kitLabel</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>A Day That Should Have Been Fine</t>
+          <t>Download complete press kit</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Une journée qui aurait dû bien se passer</t>
+          <t>Télécharger le dossier complet</t>
         </is>
       </c>
       <c r="E153" s="11" t="n"/>
@@ -4272,22 +4236,22 @@
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[1].title</t>
+          <t>press.assets[0].label</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>The Radar Was Right</t>
+          <t>Front cover, high resolution</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Le radar avait raison</t>
+          <t>Première de couverture, haute résolution</t>
         </is>
       </c>
       <c r="E154" s="11" t="n"/>
@@ -4296,22 +4260,22 @@
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[2].title</t>
+          <t>press.assets[0].note</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
+          <t>JPEG, 2400 px wide</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi le manque de sommeil fait paraître hostile ce qui est neutre</t>
+          <t>JPEG, 2400 px de large</t>
         </is>
       </c>
       <c r="E155" s="11" t="n"/>
@@ -4320,22 +4284,22 @@
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[3].title</t>
+          <t>press.assets[1].label</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>The Relief That Becomes Itch</t>
+          <t>Author photograph</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Le soulagement qui tourne à la démangeaison</t>
+          <t>Photographie de l’autrice</t>
         </is>
       </c>
       <c r="E156" s="11" t="n"/>
@@ -4344,22 +4308,22 @@
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[4].title</t>
+          <t>press.assets[1].note</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>The Predictable Cue</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Le déclencheur prévisible</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="E157" s="11" t="n"/>
@@ -4368,22 +4332,22 @@
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[5].title</t>
+          <t>press.assets[2].label</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Why Evenings Stretch and Mornings Shrink</t>
+          <t>Book render, transparent background</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi les soirées s’étirent et les matins rétrécissent</t>
+          <t>Rendu du livre, fond transparent</t>
         </is>
       </c>
       <c r="E158" s="11" t="n"/>
@@ -4392,22 +4356,22 @@
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[6].title</t>
+          <t>press.assets[2].note</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Why Rest Doesn’t Always Restore</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi le repos ne ressource pas toujours</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="E159" s="11" t="n"/>
@@ -4416,22 +4380,22 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[7].title</t>
+          <t>press.assets[3].label</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Why You Cannot Start the Thing That Matters</t>
+          <t>Web banner</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Pourquoi vous n’arrivez pas à commencer ce qui compte</t>
+          <t>Bannière web</t>
         </is>
       </c>
       <c r="E160" s="11" t="n"/>
@@ -4440,22 +4404,22 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[8].title</t>
+          <t>press.assets[3].note</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>The Open File</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>Le dossier ouvert</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="E161" s="11" t="n"/>
@@ -4464,22 +4428,22 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[9].title</t>
+          <t>press.assets[4].label</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Two Nervous Systems Walk Into a Kitchen</t>
+          <t>Social image, square</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>Deux systèmes nerveux entrent dans une cuisine</t>
+          <t>Image pour les réseaux, carrée</t>
         </is>
       </c>
       <c r="E162" s="11" t="n"/>
@@ -4488,22 +4452,22 @@
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[10].title</t>
+          <t>press.assets[4].note</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>The Argument That Was Tuesday</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>La dispute qui était mardi</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="E163" s="11" t="n"/>
@@ -4512,22 +4476,22 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[11].title</t>
+          <t>press.assets[5].label</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>The Thursday That Was Wednesday Night</t>
+          <t>Social image, portrait</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>Le jeudi qui était mercredi soir</t>
+          <t>Image pour les réseaux, portrait</t>
         </is>
       </c>
       <c r="E164" s="11" t="n"/>
@@ -4536,22 +4500,22 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[12].title</t>
+          <t>press.assets[5].note</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>The Clean Panel</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Le tableau de bord au vert</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="E165" s="11" t="n"/>
@@ -4560,22 +4524,22 @@
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[13].title</t>
+          <t>press.assets[6].label</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>The Time the Body Was Right</t>
+          <t>Social image, landscape</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>La fois où le corps avait raison</t>
+          <t>Image pour les réseaux, paysage</t>
         </is>
       </c>
       <c r="E166" s="11" t="n"/>
@@ -4584,22 +4548,22 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[14].title</t>
+          <t>press.assets[6].note</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Not About Me</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Rien à voir avec moi</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="E167" s="11" t="n"/>
@@ -4608,22 +4572,22 @@
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[15].title</t>
+          <t>press.assets[7].label</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>The Forecast</t>
+          <t>The opening extract</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>La prévision</t>
+          <t>L’extrait d’ouverture</t>
         </is>
       </c>
       <c r="E168" s="11" t="n"/>
@@ -4632,46 +4596,46 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>map.mapFooter</t>
+          <t>press.assets[7].note</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>The Scientific Heartbeat follows the chapters.</t>
+          <t>PDF, four pages</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>Le pouls scientifique suit les chapitres.</t>
+          <t>PDF, quatre pages</t>
         </is>
       </c>
       <c r="E169" s="11" t="n"/>
       <c r="F169" s="11" t="n"/>
     </row>
-    <row r="170" ht="75" customHeight="1">
+    <row r="170" ht="30" customHeight="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[0]</t>
+          <t>press.photoUnavailable</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>Author photograph available on request.</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
+          <t>Photographie de l’autrice disponible sur demande.</t>
         </is>
       </c>
       <c r="E170" s="11" t="n"/>
@@ -4680,22 +4644,22 @@
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[1]</t>
+          <t>press.bioHeading</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
+          <t>Biographie</t>
         </is>
       </c>
       <c r="E171" s="11" t="n"/>
@@ -4704,58 +4668,70 @@
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeatSource</t>
+          <t>press.bios[0].label</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Courte</t>
         </is>
       </c>
       <c r="E172" s="11" t="n"/>
       <c r="F172" s="11" t="n"/>
     </row>
-    <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
-        <is>
-          <t>ABOUT THE AUTHOR</t>
-        </is>
-      </c>
-      <c r="B173" s="8" t="n"/>
-      <c r="C173" s="8" t="n"/>
-      <c r="D173" s="8" t="n"/>
-      <c r="E173" s="8" t="n"/>
-      <c r="F173" s="8" t="n"/>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>press.bios[0].text</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="n"/>
+      <c r="F173" s="11" t="n"/>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>author.eyebrow</t>
+          <t>press.bios[1].label</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>The author</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>L’autrice</t>
+          <t>Longue</t>
         </is>
       </c>
       <c r="E174" s="11" t="n"/>
@@ -4764,22 +4740,22 @@
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>author.title</t>
+          <t>press.factsHeading</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="E175" s="11" t="n"/>
@@ -4788,22 +4764,22 @@
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>author.photoAlt</t>
+          <t>press.facts[0].label</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographed against a dark grey background.</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographiée sur fond gris foncé.</t>
+          <t>Titre</t>
         </is>
       </c>
       <c r="E176" s="11" t="n"/>
@@ -4812,22 +4788,22 @@
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>author.photoPlaceholder</t>
+          <t>press.facts[0].value</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Author photograph to follow</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice à venir</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="E177" s="11" t="n"/>
@@ -4836,22 +4812,22 @@
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>author.bio</t>
+          <t>press.facts[1].label</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Subtitle</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
+          <t>Sous-titre</t>
         </is>
       </c>
       <c r="E178" s="11" t="n"/>
@@ -4860,22 +4836,22 @@
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>author.websiteLabel</t>
+          <t>press.facts[1].value</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Practice website</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>Site du cabinet</t>
+          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité</t>
         </is>
       </c>
       <c r="E179" s="11" t="n"/>
@@ -4884,22 +4860,22 @@
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
         <is>
-          <t>author.contactLabel</t>
+          <t>press.facts[2].label</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Autrice</t>
         </is>
       </c>
       <c r="E180" s="11" t="n"/>
@@ -4908,58 +4884,70 @@
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>author.pressLabel</t>
+          <t>press.facts[2].value</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Dossier de presse</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
     </row>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
-        </is>
-      </c>
-      <c r="B182" s="8" t="n"/>
-      <c r="C182" s="8" t="n"/>
-      <c r="D182" s="8" t="n"/>
-      <c r="E182" s="8" t="n"/>
-      <c r="F182" s="8" t="n"/>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>press.facts[3].label</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>Parution</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="n"/>
+      <c r="F182" s="11" t="n"/>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>The book’s last sentence, above the notify form</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>closing.question</t>
+          <t>press.facts[3].value</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this their state?</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Est-ce la situation ? Ou est-ce leur état ?</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" s="11" t="n"/>
@@ -4968,74 +4956,98 @@
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>The book’s last sentence, above the notify form</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
         <is>
-          <t>closing.source</t>
+          <t>press.facts[4].label</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="E184" s="11" t="n"/>
       <c r="F184" s="11" t="n"/>
     </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="7" t="inlineStr">
-        <is>
-          <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
-        </is>
-      </c>
-      <c r="B185" s="8" t="n"/>
-      <c r="C185" s="8" t="n"/>
-      <c r="D185" s="8" t="n"/>
-      <c r="E185" s="8" t="n"/>
-      <c r="F185" s="8" t="n"/>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>press.facts[4].value</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>Paperback, 6 × 9 in</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>Broché, 15,2 × 22,9 cm (6 × 9 pouces)</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="n"/>
+      <c r="F185" s="11" t="n"/>
     </row>
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>Companion tool (currently hidden)</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>companion.eyebrow</t>
+          <t>press.facts[5].label</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>Alongside the book</t>
+          <t>Extent</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>En complément du livre</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E186" s="11" t="n"/>
       <c r="F186" s="11" t="n"/>
     </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t>PRESS PAGE</t>
-        </is>
-      </c>
-      <c r="B187" s="8" t="n"/>
-      <c r="C187" s="8" t="n"/>
-      <c r="D187" s="8" t="n"/>
-      <c r="E187" s="8" t="n"/>
-      <c r="F187" s="8" t="n"/>
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>press.facts[5].value</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>278 pages</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>278 pages</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="n"/>
+      <c r="F187" s="11" t="n"/>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="9" t="inlineStr">
@@ -5045,17 +5057,17 @@
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>press.eyebrow</t>
+          <t>press.facts[6].label</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Presse</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="E188" s="11" t="n"/>
@@ -5069,23 +5081,23 @@
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>press.title</t>
+          <t>press.facts[6].value</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>Dossier de presse</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="E189" s="11" t="n"/>
       <c r="F189" s="11" t="n"/>
     </row>
-    <row r="190" ht="45" customHeight="1">
+    <row r="190" ht="30" customHeight="1">
       <c r="A190" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5093,17 +5105,17 @@
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>press.intro</t>
+          <t>press.facts[7].label</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Des exemplaires de presse, papier et numérique, sont disponibles sur demande. Reproduction d’extraits, entretiens et rencontres à convenir.</t>
+          <t>Catégorie</t>
         </is>
       </c>
       <c r="E190" s="11" t="n"/>
@@ -5117,17 +5129,17 @@
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>press.contactHeading</t>
+          <t>press.facts[7].value</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Psychology / Cognitive psychology</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Psychologie / Psychologie cognitive</t>
         </is>
       </c>
       <c r="E191" s="11" t="n"/>
@@ -5141,17 +5153,17 @@
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>press.assetsHeading</t>
+          <t>press.facts[8].label</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Téléchargements</t>
+          <t>Langue</t>
         </is>
       </c>
       <c r="E192" s="11" t="n"/>
@@ -5165,17 +5177,17 @@
       </c>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].label</t>
+          <t>press.facts[8].value</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>Front cover, high resolution</t>
+          <t>English. French and German editions to follow.</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>Première de couverture, haute résolution</t>
+          <t>Anglais. Éditions française et allemande à venir.</t>
         </is>
       </c>
       <c r="E193" s="11" t="n"/>
@@ -5189,17 +5201,17 @@
       </c>
       <c r="B194" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].note</t>
+          <t>press.facts[9].label</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px wide</t>
+          <t>Legal deposit</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px de large</t>
+          <t>Dépôt légal</t>
         </is>
       </c>
       <c r="E194" s="11" t="n"/>
@@ -5213,17 +5225,17 @@
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].label</t>
+          <t>press.facts[9].value</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Author photograph</t>
+          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice</t>
+          <t>Une notice CIP est disponible à la Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="E195" s="11" t="n"/>
@@ -5237,23 +5249,23 @@
       </c>
       <c r="B196" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].note</t>
+          <t>press.descriptionHeading</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>About the book</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>À propos du livre</t>
         </is>
       </c>
       <c r="E196" s="11" t="n"/>
       <c r="F196" s="11" t="n"/>
     </row>
-    <row r="197" ht="30" customHeight="1">
+    <row r="197" ht="45" customHeight="1">
       <c r="A197" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5261,23 +5273,23 @@
       </c>
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].label</t>
+          <t>press.description[0]</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>Book render, transparent background</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>Rendu du livre, fond transparent</t>
+          <t>Ce livre cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
         </is>
       </c>
       <c r="E197" s="11" t="n"/>
       <c r="F197" s="11" t="n"/>
     </row>
-    <row r="198" ht="30" customHeight="1">
+    <row r="198" ht="75" customHeight="1">
       <c r="A198" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5285,17 +5297,17 @@
       </c>
       <c r="B198" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].note</t>
+          <t>press.description[1]</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Pour quiconque a déjà été certain du sens d’une situation, puis a découvert qu’il se passait autre chose. Et pour les lecteurs qui s’intéressent à la psychologie de notre façon de remarquer, d’interpréter et de revoir le monde qui nous entoure.</t>
         </is>
       </c>
       <c r="E198" s="11" t="n"/>
@@ -5309,17 +5321,17 @@
       </c>
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].label</t>
+          <t>press.mapHeading</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>Web banner</t>
+          <t>The chapters</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>Bannière web</t>
+          <t>Les chapitres</t>
         </is>
       </c>
       <c r="E199" s="11" t="n"/>
@@ -5333,17 +5345,17 @@
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].note</t>
+          <t>press.mapLabel</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>This book is the</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Ce livre mène</t>
         </is>
       </c>
       <c r="E200" s="11" t="n"/>
@@ -5357,17 +5369,17 @@
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].label</t>
+          <t>press.mapTitle</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Social image, square</t>
+          <t>Investigation.</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, carrée</t>
+          <t>L’enquête.</t>
         </is>
       </c>
       <c r="E201" s="11" t="n"/>
@@ -5381,17 +5393,17 @@
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].note</t>
+          <t>press.mapLine</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
         </is>
       </c>
       <c r="E202" s="11" t="n"/>
@@ -5405,17 +5417,17 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].label</t>
+          <t>press.pageColumn</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Social image, portrait</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, portrait</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="E203" s="11" t="n"/>
@@ -5429,17 +5441,17 @@
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].note</t>
+          <t>press.chapters[0].title</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>A Day That Should Have Been Fine</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>Une journée qui aurait dû bien se passer</t>
         </is>
       </c>
       <c r="E204" s="11" t="n"/>
@@ -5453,17 +5465,17 @@
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].label</t>
+          <t>press.chapters[1].title</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>Social image, landscape</t>
+          <t>The Radar Was Right</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>Image pour les réseaux, paysage</t>
+          <t>Le radar avait raison</t>
         </is>
       </c>
       <c r="E205" s="11" t="n"/>
@@ -5477,17 +5489,17 @@
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].note</t>
+          <t>press.chapters[2].title</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Pourquoi le manque de sommeil fait paraître hostile ce qui est neutre</t>
         </is>
       </c>
       <c r="E206" s="11" t="n"/>
@@ -5501,17 +5513,17 @@
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].label</t>
+          <t>press.chapters[3].title</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>The opening extract</t>
+          <t>The Relief That Becomes Itch</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>L’extrait d’ouverture</t>
+          <t>Le soulagement qui tourne à la démangeaison</t>
         </is>
       </c>
       <c r="E207" s="11" t="n"/>
@@ -5525,17 +5537,17 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].note</t>
+          <t>press.chapters[4].title</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>PDF, four pages</t>
+          <t>The Predictable Cue</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>PDF, quatre pages</t>
+          <t>Le déclencheur prévisible</t>
         </is>
       </c>
       <c r="E208" s="11" t="n"/>
@@ -5549,17 +5561,17 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>press.photoUnavailable</t>
+          <t>press.chapters[5].title</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>Author photograph available on request.</t>
+          <t>Why Evenings Stretch and Mornings Shrink</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>Photographie de l’autrice disponible sur demande.</t>
+          <t>Pourquoi les soirées s’étirent et les matins rétrécissent</t>
         </is>
       </c>
       <c r="E209" s="11" t="n"/>
@@ -5573,17 +5585,17 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>press.bioHeading</t>
+          <t>press.chapters[6].title</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Why Rest Doesn’t Always Restore</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>Biographie</t>
+          <t>Pourquoi le repos ne ressource pas toujours</t>
         </is>
       </c>
       <c r="E210" s="11" t="n"/>
@@ -5597,17 +5609,17 @@
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].label</t>
+          <t>press.chapters[7].title</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Why You Cannot Start the Thing That Matters</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>Courte</t>
+          <t>Pourquoi vous n’arrivez pas à commencer ce qui compte</t>
         </is>
       </c>
       <c r="E211" s="11" t="n"/>
@@ -5621,17 +5633,17 @@
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].text</t>
+          <t>press.chapters[8].title</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>The Open File</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>Psychologue clinicienne, Ivana Budišin vit et travaille au Luxembourg. State. Not Situation. est son premier livre.</t>
+          <t>Le dossier ouvert</t>
         </is>
       </c>
       <c r="E212" s="11" t="n"/>
@@ -5645,17 +5657,17 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>press.bios[1].label</t>
+          <t>press.chapters[9].title</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Two Nervous Systems Walk Into a Kitchen</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>Longue</t>
+          <t>Deux systèmes nerveux entrent dans une cuisine</t>
         </is>
       </c>
       <c r="E213" s="11" t="n"/>
@@ -5669,17 +5681,17 @@
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>press.factsHeading</t>
+          <t>press.chapters[10].title</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>The Argument That Was Tuesday</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>La dispute qui était mardi</t>
         </is>
       </c>
       <c r="E214" s="11" t="n"/>
@@ -5693,17 +5705,17 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].label</t>
+          <t>press.chapters[11].title</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>The Thursday That Was Wednesday Night</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>Titre</t>
+          <t>Le jeudi qui était mercredi soir</t>
         </is>
       </c>
       <c r="E215" s="11" t="n"/>
@@ -5717,17 +5729,17 @@
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].value</t>
+          <t>press.chapters[12].title</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>The Clean Panel</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>Le tableau de bord au vert</t>
         </is>
       </c>
       <c r="E216" s="11" t="n"/>
@@ -5741,17 +5753,17 @@
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].label</t>
+          <t>press.chapters[13].title</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>Subtitle</t>
+          <t>The Time the Body Was Right</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>Sous-titre</t>
+          <t>La fois où le corps avait raison</t>
         </is>
       </c>
       <c r="E217" s="11" t="n"/>
@@ -5765,17 +5777,17 @@
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].value</t>
+          <t>press.chapters[14].title</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>Not About Me</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>Un guide de terrain de l’instant où l’interprétation n’est pas encore devenue réalité</t>
+          <t>Rien à voir avec moi</t>
         </is>
       </c>
       <c r="E218" s="11" t="n"/>
@@ -5789,23 +5801,23 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].label</t>
+          <t>press.chapters[15].title</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>The Forecast</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>Autrice</t>
+          <t>La prévision</t>
         </is>
       </c>
       <c r="E219" s="11" t="n"/>
       <c r="F219" s="11" t="n"/>
     </row>
-    <row r="220" ht="30" customHeight="1">
+    <row r="220" ht="90" customHeight="1">
       <c r="A220" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5813,17 +5825,17 @@
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].value</t>
+          <t>press.sortingTool</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Les chapitres qui suivent sont organisés autour de trois systèmes qui règlent le poids que prennent les signaux de votre corps avant que votre esprit ne construise une histoire. Ce ne sont pas des régions du cerveau ni des voies neuronales. C’est un outil de tri, une façon de poser trois questions quand tout semble aller de travers en même temps.</t>
         </is>
       </c>
       <c r="E220" s="11" t="n"/>
@@ -5837,23 +5849,23 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].label</t>
+          <t>press.sourcesHeading</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Sources and evidence</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>Éditeur</t>
+          <t>Sources et preuves</t>
         </is>
       </c>
       <c r="E221" s="11" t="n"/>
       <c r="F221" s="11" t="n"/>
     </row>
-    <row r="222" ht="30" customHeight="1">
+    <row r="222" ht="75" customHeight="1">
       <c r="A222" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5861,17 +5873,17 @@
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].value</t>
+          <t>press.sources[0]</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
         </is>
       </c>
       <c r="E222" s="11" t="n"/>
@@ -5885,17 +5897,17 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].label</t>
+          <t>press.sources[1]</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>Parution</t>
+          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
         </is>
       </c>
       <c r="E223" s="11" t="n"/>
@@ -5909,17 +5921,17 @@
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].value</t>
+          <t>press.sourcesLabel</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>The Scientific Heartbeat, page 226</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Le pouls scientifique, page 226</t>
         </is>
       </c>
       <c r="E224" s="11" t="n"/>
@@ -5933,17 +5945,17 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].label</t>
+          <t>press.creditsHeading</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Crédits</t>
         </is>
       </c>
       <c r="E225" s="11" t="n"/>
@@ -5957,17 +5969,17 @@
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].value</t>
+          <t>press.credits[0].label</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 in</t>
+          <t>Cover design</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>Broché, 15,2 × 22,9 cm (6 × 9 pouces)</t>
+          <t>Conception de la couverture</t>
         </is>
       </c>
       <c r="E226" s="11" t="n"/>
@@ -5981,17 +5993,17 @@
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].label</t>
+          <t>press.credits[0].value</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>Extent</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="E227" s="11" t="n"/>
@@ -6005,17 +6017,17 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].value</t>
+          <t>press.credits[1].label</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Book design and typesetting</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Conception graphique et mise en page</t>
         </is>
       </c>
       <c r="E228" s="11" t="n"/>
@@ -6029,17 +6041,17 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].label</t>
+          <t>press.credits[1].value</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E229" s="11" t="n"/>
@@ -6053,17 +6065,17 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].value</t>
+          <t>press.credits[2].label</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Published by</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Publié par</t>
         </is>
       </c>
       <c r="E230" s="11" t="n"/>
@@ -6077,17 +6089,17 @@
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].label</t>
+          <t>press.credits[2].value</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>Catégorie</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="E231" s="11" t="n"/>
@@ -6101,65 +6113,53 @@
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].value</t>
+          <t>press.back</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>Psychology / Cognitive psychology</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>Psychologie / Psychologie cognitive</t>
+          <t>Retour au livre</t>
         </is>
       </c>
       <c r="E232" s="11" t="n"/>
       <c r="F232" s="11" t="n"/>
     </row>
-    <row r="233" ht="30" customHeight="1">
-      <c r="A233" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B233" s="9" t="inlineStr">
-        <is>
-          <t>press.facts[9].label</t>
-        </is>
-      </c>
-      <c r="C233" s="10" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="D233" s="10" t="inlineStr">
-        <is>
-          <t>Langue</t>
-        </is>
-      </c>
-      <c r="E233" s="11" t="n"/>
-      <c r="F233" s="11" t="n"/>
+    <row r="233" ht="22" customHeight="1">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>FOOT OF EVERY PAGE</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="n"/>
+      <c r="C233" s="8" t="n"/>
+      <c r="D233" s="8" t="n"/>
+      <c r="E233" s="8" t="n"/>
+      <c r="F233" s="8" t="n"/>
     </row>
     <row r="234" ht="30" customHeight="1">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].value</t>
+          <t>footer.band</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
         <is>
-          <t>English. French and German editions to follow.</t>
+          <t>Before you believe the story.</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>Anglais. Éditions française et allemande à venir.</t>
+          <t>Avant de croire l’histoire.</t>
         </is>
       </c>
       <c r="E234" s="11" t="n"/>
@@ -6168,22 +6168,22 @@
     <row r="235" ht="30" customHeight="1">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].label</t>
+          <t>footer.pressLink</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
         <is>
-          <t>Legal deposit</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>Dépôt légal</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E235" s="11" t="n"/>
@@ -6192,22 +6192,22 @@
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].value</t>
+          <t>footer.contactLink</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
         <is>
-          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>Une notice CIP est disponible à la Bibliothèque nationale du Luxembourg.</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="E236" s="11" t="n"/>
@@ -6216,94 +6216,82 @@
     <row r="237" ht="30" customHeight="1">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>press.descriptionHeading</t>
+          <t>footer.rights</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
         <is>
-          <t>About the book</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>À propos du livre</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="E237" s="11" t="n"/>
       <c r="F237" s="11" t="n"/>
     </row>
-    <row r="238" ht="45" customHeight="1">
-      <c r="A238" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B238" s="9" t="inlineStr">
-        <is>
-          <t>press.description[0]</t>
-        </is>
-      </c>
-      <c r="C238" s="10" t="inlineStr">
-        <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
-        </is>
-      </c>
-      <c r="D238" s="10" t="inlineStr">
-        <is>
-          <t>Il cherche moins à vous apprendre à faire confiance à votre instinct qu’à vous montrer à quoi, au juste, vous faites confiance.</t>
-        </is>
-      </c>
-      <c r="E238" s="11" t="n"/>
-      <c r="F238" s="11" t="n"/>
+    <row r="238" ht="22" customHeight="1">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="n"/>
+      <c r="C238" s="8" t="n"/>
+      <c r="D238" s="8" t="n"/>
+      <c r="E238" s="8" t="n"/>
+      <c r="F238" s="8" t="n"/>
     </row>
     <row r="239" ht="30" customHeight="1">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>press.description[1]</t>
+          <t>a11y.mainLandmark</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>Main content</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>16 cas. Trois lectures. Une question : état ou situation ?</t>
+          <t>Contenu principal</t>
         </is>
       </c>
       <c r="E239" s="11" t="n"/>
       <c r="F239" s="11" t="n"/>
     </row>
-    <row r="240" ht="75" customHeight="1">
+    <row r="240" ht="30" customHeight="1">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
         <is>
-          <t>press.description[2]</t>
+          <t>a11y.coverFigure</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>Chaque chapitre a ici trois parties : une courte note sur l’origine de la réflexion, une liste des travaux sur lesquels le chapitre est construit, et une liste des travaux qui le limitent, le compliquent, ou expliquent autrement les mêmes résultats.</t>
+          <t>Le livre</t>
         </is>
       </c>
       <c r="E240" s="11" t="n"/>
@@ -6312,22 +6300,22 @@
     <row r="241" ht="30" customHeight="1">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>press.description[3]</t>
+          <t>a11y.languageSwitcher</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Choose language</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>Les laisser de côté ferait paraître l’argumentation plus nette qu’elle ne l’est.</t>
+          <t>Choisir la langue</t>
         </is>
       </c>
       <c r="E241" s="11" t="n"/>
@@ -6336,629 +6324,29 @@
     <row r="242" ht="30" customHeight="1">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>press.creditsHeading</t>
+          <t>a11y.menu</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>Crédits</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="E242" s="11" t="n"/>
       <c r="F242" s="11" t="n"/>
     </row>
-    <row r="243" ht="30" customHeight="1">
-      <c r="A243" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B243" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[0].label</t>
-        </is>
-      </c>
-      <c r="C243" s="10" t="inlineStr">
-        <is>
-          <t>Cover design</t>
-        </is>
-      </c>
-      <c r="D243" s="10" t="inlineStr">
-        <is>
-          <t>Conception de la couverture</t>
-        </is>
-      </c>
-      <c r="E243" s="11" t="n"/>
-      <c r="F243" s="11" t="n"/>
-    </row>
-    <row r="244" ht="30" customHeight="1">
-      <c r="A244" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B244" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[0].value</t>
-        </is>
-      </c>
-      <c r="C244" s="10" t="inlineStr">
-        <is>
-          <t>Zoe Larusson</t>
-        </is>
-      </c>
-      <c r="D244" s="10" t="inlineStr">
-        <is>
-          <t>Zoe Larusson</t>
-        </is>
-      </c>
-      <c r="E244" s="11" t="n"/>
-      <c r="F244" s="11" t="n"/>
-    </row>
-    <row r="245" ht="30" customHeight="1">
-      <c r="A245" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B245" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[1].label</t>
-        </is>
-      </c>
-      <c r="C245" s="10" t="inlineStr">
-        <is>
-          <t>Book design and typesetting</t>
-        </is>
-      </c>
-      <c r="D245" s="10" t="inlineStr">
-        <is>
-          <t>Conception graphique et mise en page</t>
-        </is>
-      </c>
-      <c r="E245" s="11" t="n"/>
-      <c r="F245" s="11" t="n"/>
-    </row>
-    <row r="246" ht="30" customHeight="1">
-      <c r="A246" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B246" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[1].value</t>
-        </is>
-      </c>
-      <c r="C246" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="D246" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="E246" s="11" t="n"/>
-      <c r="F246" s="11" t="n"/>
-    </row>
-    <row r="247" ht="30" customHeight="1">
-      <c r="A247" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B247" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[2].label</t>
-        </is>
-      </c>
-      <c r="C247" s="10" t="inlineStr">
-        <is>
-          <t>Published by</t>
-        </is>
-      </c>
-      <c r="D247" s="10" t="inlineStr">
-        <is>
-          <t>Publié par</t>
-        </is>
-      </c>
-      <c r="E247" s="11" t="n"/>
-      <c r="F247" s="11" t="n"/>
-    </row>
-    <row r="248" ht="30" customHeight="1">
-      <c r="A248" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B248" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[2].value</t>
-        </is>
-      </c>
-      <c r="C248" s="10" t="inlineStr">
-        <is>
-          <t>Budisin Publishing</t>
-        </is>
-      </c>
-      <c r="D248" s="10" t="inlineStr">
-        <is>
-          <t>Budisin Publishing</t>
-        </is>
-      </c>
-      <c r="E248" s="11" t="n"/>
-      <c r="F248" s="11" t="n"/>
-    </row>
-    <row r="249" ht="30" customHeight="1">
-      <c r="A249" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B249" s="9" t="inlineStr">
-        <is>
-          <t>press.back</t>
-        </is>
-      </c>
-      <c r="C249" s="10" t="inlineStr">
-        <is>
-          <t>Back to the book</t>
-        </is>
-      </c>
-      <c r="D249" s="10" t="inlineStr">
-        <is>
-          <t>Retour au livre</t>
-        </is>
-      </c>
-      <c r="E249" s="11" t="n"/>
-      <c r="F249" s="11" t="n"/>
-    </row>
-    <row r="250" ht="22" customHeight="1">
-      <c r="A250" s="7" t="inlineStr">
-        <is>
-          <t>FOOT OF EVERY PAGE</t>
-        </is>
-      </c>
-      <c r="B250" s="8" t="n"/>
-      <c r="C250" s="8" t="n"/>
-      <c r="D250" s="8" t="n"/>
-      <c r="E250" s="8" t="n"/>
-      <c r="F250" s="8" t="n"/>
-    </row>
-    <row r="251" ht="30" customHeight="1">
-      <c r="A251" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B251" s="9" t="inlineStr">
-        <is>
-          <t>footer.band</t>
-        </is>
-      </c>
-      <c r="C251" s="10" t="inlineStr">
-        <is>
-          <t>Before you believe the story.</t>
-        </is>
-      </c>
-      <c r="D251" s="10" t="inlineStr">
-        <is>
-          <t>Avant de croire l’histoire.</t>
-        </is>
-      </c>
-      <c r="E251" s="11" t="n"/>
-      <c r="F251" s="11" t="n"/>
-    </row>
-    <row r="252" ht="30" customHeight="1">
-      <c r="A252" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B252" s="9" t="inlineStr">
-        <is>
-          <t>footer.method[0]</t>
-        </is>
-      </c>
-      <c r="C252" s="10" t="inlineStr">
-        <is>
-          <t>Read the dashboard.</t>
-        </is>
-      </c>
-      <c r="D252" s="10" t="inlineStr">
-        <is>
-          <t>Lisez le tableau de bord.</t>
-        </is>
-      </c>
-      <c r="E252" s="11" t="n"/>
-      <c r="F252" s="11" t="n"/>
-    </row>
-    <row r="253" ht="30" customHeight="1">
-      <c r="A253" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B253" s="9" t="inlineStr">
-        <is>
-          <t>footer.method[1]</t>
-        </is>
-      </c>
-      <c r="C253" s="10" t="inlineStr">
-        <is>
-          <t>Delay the story.</t>
-        </is>
-      </c>
-      <c r="D253" s="10" t="inlineStr">
-        <is>
-          <t>Différez l’histoire.</t>
-        </is>
-      </c>
-      <c r="E253" s="11" t="n"/>
-      <c r="F253" s="11" t="n"/>
-    </row>
-    <row r="254" ht="30" customHeight="1">
-      <c r="A254" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B254" s="9" t="inlineStr">
-        <is>
-          <t>footer.method[2]</t>
-        </is>
-      </c>
-      <c r="C254" s="10" t="inlineStr">
-        <is>
-          <t>Take the reading again.</t>
-        </is>
-      </c>
-      <c r="D254" s="10" t="inlineStr">
-        <is>
-          <t>Refaites la lecture.</t>
-        </is>
-      </c>
-      <c r="E254" s="11" t="n"/>
-      <c r="F254" s="11" t="n"/>
-    </row>
-    <row r="255" ht="30" customHeight="1">
-      <c r="A255" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B255" s="9" t="inlineStr">
-        <is>
-          <t>footer.rights</t>
-        </is>
-      </c>
-      <c r="C255" s="10" t="inlineStr">
-        <is>
-          <t>© 2026 Budisin Publishing</t>
-        </is>
-      </c>
-      <c r="D255" s="10" t="inlineStr">
-        <is>
-          <t>© 2026 Budisin Publishing</t>
-        </is>
-      </c>
-      <c r="E255" s="11" t="n"/>
-      <c r="F255" s="11" t="n"/>
-    </row>
-    <row r="256" ht="30" customHeight="1">
-      <c r="A256" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B256" s="9" t="inlineStr">
-        <is>
-          <t>footer.pressLink</t>
-        </is>
-      </c>
-      <c r="C256" s="10" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
-      <c r="D256" s="10" t="inlineStr">
-        <is>
-          <t>Presse</t>
-        </is>
-      </c>
-      <c r="E256" s="11" t="n"/>
-      <c r="F256" s="11" t="n"/>
-    </row>
-    <row r="257" ht="30" customHeight="1">
-      <c r="A257" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B257" s="9" t="inlineStr">
-        <is>
-          <t>footer.contactLink</t>
-        </is>
-      </c>
-      <c r="C257" s="10" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D257" s="10" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="E257" s="11" t="n"/>
-      <c r="F257" s="11" t="n"/>
-    </row>
-    <row r="258" ht="30" customHeight="1">
-      <c r="A258" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B258" s="9" t="inlineStr">
-        <is>
-          <t>footer.madeLine</t>
-        </is>
-      </c>
-      <c r="C258" s="10" t="inlineStr">
-        <is>
-          <t>Same life. Different instrument settings.</t>
-        </is>
-      </c>
-      <c r="D258" s="10" t="inlineStr">
-        <is>
-          <t>Même vie. Instruments réglés autrement.</t>
-        </is>
-      </c>
-      <c r="E258" s="11" t="n"/>
-      <c r="F258" s="11" t="n"/>
-    </row>
-    <row r="259" ht="22" customHeight="1">
-      <c r="A259" s="7" t="inlineStr">
-        <is>
-          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
-        </is>
-      </c>
-      <c r="B259" s="8" t="n"/>
-      <c r="C259" s="8" t="n"/>
-      <c r="D259" s="8" t="n"/>
-      <c r="E259" s="8" t="n"/>
-      <c r="F259" s="8" t="n"/>
-    </row>
-    <row r="260" ht="30" customHeight="1">
-      <c r="A260" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B260" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mainLandmark</t>
-        </is>
-      </c>
-      <c r="C260" s="10" t="inlineStr">
-        <is>
-          <t>Main content</t>
-        </is>
-      </c>
-      <c r="D260" s="10" t="inlineStr">
-        <is>
-          <t>Contenu principal</t>
-        </is>
-      </c>
-      <c r="E260" s="11" t="n"/>
-      <c r="F260" s="11" t="n"/>
-    </row>
-    <row r="261" ht="30" customHeight="1">
-      <c r="A261" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B261" s="9" t="inlineStr">
-        <is>
-          <t>a11y.coverFigure</t>
-        </is>
-      </c>
-      <c r="C261" s="10" t="inlineStr">
-        <is>
-          <t>The book</t>
-        </is>
-      </c>
-      <c r="D261" s="10" t="inlineStr">
-        <is>
-          <t>Le livre</t>
-        </is>
-      </c>
-      <c r="E261" s="11" t="n"/>
-      <c r="F261" s="11" t="n"/>
-    </row>
-    <row r="262" ht="30" customHeight="1">
-      <c r="A262" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B262" s="9" t="inlineStr">
-        <is>
-          <t>a11y.languageSwitcher</t>
-        </is>
-      </c>
-      <c r="C262" s="10" t="inlineStr">
-        <is>
-          <t>Choose language</t>
-        </is>
-      </c>
-      <c r="D262" s="10" t="inlineStr">
-        <is>
-          <t>Choisir la langue</t>
-        </is>
-      </c>
-      <c r="E262" s="11" t="n"/>
-      <c r="F262" s="11" t="n"/>
-    </row>
-    <row r="263" ht="30" customHeight="1">
-      <c r="A263" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B263" s="9" t="inlineStr">
-        <is>
-          <t>a11y.languageComing</t>
-        </is>
-      </c>
-      <c r="C263" s="10" t="inlineStr">
-        <is>
-          <t>edition to follow</t>
-        </is>
-      </c>
-      <c r="D263" s="10" t="inlineStr">
-        <is>
-          <t>édition à venir</t>
-        </is>
-      </c>
-      <c r="E263" s="11" t="n"/>
-      <c r="F263" s="11" t="n"/>
-    </row>
-    <row r="264" ht="30" customHeight="1">
-      <c r="A264" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B264" s="9" t="inlineStr">
-        <is>
-          <t>a11y.casesRegion</t>
-        </is>
-      </c>
-      <c r="C264" s="10" t="inlineStr">
-        <is>
-          <t>Case evidence pages from the book</t>
-        </is>
-      </c>
-      <c r="D264" s="10" t="inlineStr">
-        <is>
-          <t>Pièces du dossier tirées du livre</t>
-        </is>
-      </c>
-      <c r="E264" s="11" t="n"/>
-      <c r="F264" s="11" t="n"/>
-    </row>
-    <row r="265" ht="30" customHeight="1">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
-        <is>
-          <t>a11y.bookOpening</t>
-        </is>
-      </c>
-      <c r="C265" s="10" t="inlineStr">
-        <is>
-          <t>The book, opening</t>
-        </is>
-      </c>
-      <c r="D265" s="10" t="inlineStr">
-        <is>
-          <t>Le livre qui s’ouvre</t>
-        </is>
-      </c>
-      <c r="E265" s="11" t="n"/>
-      <c r="F265" s="11" t="n"/>
-    </row>
-    <row r="266" ht="30" customHeight="1">
-      <c r="A266" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B266" s="9" t="inlineStr">
-        <is>
-          <t>a11y.misreadingRegion</t>
-        </is>
-      </c>
-      <c r="C266" s="10" t="inlineStr">
-        <is>
-          <t>Page 10 of the book</t>
-        </is>
-      </c>
-      <c r="D266" s="10" t="inlineStr">
-        <is>
-          <t>Page 10 du livre</t>
-        </is>
-      </c>
-      <c r="E266" s="11" t="n"/>
-      <c r="F266" s="11" t="n"/>
-    </row>
-    <row r="267" ht="30" customHeight="1">
-      <c r="A267" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B267" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mapRegion</t>
-        </is>
-      </c>
-      <c r="C267" s="10" t="inlineStr">
-        <is>
-          <t>A map of the book</t>
-        </is>
-      </c>
-      <c r="D267" s="10" t="inlineStr">
-        <is>
-          <t>Une carte du livre</t>
-        </is>
-      </c>
-      <c r="E267" s="11" t="n"/>
-      <c r="F267" s="11" t="n"/>
-    </row>
-    <row r="268" ht="30" customHeight="1">
-      <c r="A268" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B268" s="9" t="inlineStr">
-        <is>
-          <t>a11y.evidenceRegion</t>
-        </is>
-      </c>
-      <c r="C268" s="10" t="inlineStr">
-        <is>
-          <t>Confidence markers, page 13</t>
-        </is>
-      </c>
-      <c r="D268" s="10" t="inlineStr">
-        <is>
-          <t>Marqueurs de confiance, page 13</t>
-        </is>
-      </c>
-      <c r="E268" s="11" t="n"/>
-      <c r="F268" s="11" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F268"/>
+  <autoFilter ref="A1:F242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>